--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA64C6A-4168-4F33-A3F0-ECEF1832B292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA744A0F-D2B6-4787-95B2-423EDC62E8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,17 +16,28 @@
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
     <sheet name="Outputs" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="83">
   <si>
     <t>Parameter</t>
   </si>
@@ -53,12 +64,238 @@
   </si>
   <si>
     <t>m/s</t>
+  </si>
+  <si>
+    <t>rho</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>kg/m^3</t>
+  </si>
+  <si>
+    <t>Anderson</t>
+  </si>
+  <si>
+    <t>mu_TO</t>
+  </si>
+  <si>
+    <t>mu_L</t>
+  </si>
+  <si>
+    <t>V_C</t>
+  </si>
+  <si>
+    <t>V_TO</t>
+  </si>
+  <si>
+    <t>V_M</t>
+  </si>
+  <si>
+    <t>V_S_M</t>
+  </si>
+  <si>
+    <t>phi_C</t>
+  </si>
+  <si>
+    <t>L_D_climb</t>
+  </si>
+  <si>
+    <t>gamma</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>eta_p</t>
+  </si>
+  <si>
+    <t>eta_p_TO</t>
+  </si>
+  <si>
+    <t>CD_0</t>
+  </si>
+  <si>
+    <t>CD</t>
+  </si>
+  <si>
+    <t>CD_G</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>n_M</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>bank</t>
+  </si>
+  <si>
+    <t>Sadraey, table 4.12</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>NIST</t>
+  </si>
+  <si>
+    <t>Gudmundsson, table 18-4</t>
+  </si>
+  <si>
+    <t>Concrete, no brakes</t>
+  </si>
+  <si>
+    <t>Wet grass, no brakes</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Sadraey, table 4.11</t>
+  </si>
+  <si>
+    <t>Home-built</t>
+  </si>
+  <si>
+    <t>CL_C</t>
+  </si>
+  <si>
+    <t>Sadraey, ch. 4 pg. 132</t>
+  </si>
+  <si>
+    <t>CD_TO</t>
+  </si>
+  <si>
+    <t>Home-built/GA, fixed gear, same for TO (no flaps)</t>
+  </si>
+  <si>
+    <t>Sadraey, eqn 4.67a</t>
+  </si>
+  <si>
+    <t>Sadraey, eqn 4.40</t>
+  </si>
+  <si>
+    <t>Sadraey, eqn 4.41</t>
+  </si>
+  <si>
+    <t>CL_TO</t>
+  </si>
+  <si>
+    <t>Sadraey, ch. 4 pg. 122</t>
+  </si>
+  <si>
+    <t>Calculated</t>
+  </si>
+  <si>
+    <t>mult_V_TO</t>
+  </si>
+  <si>
+    <t>CL_R</t>
+  </si>
+  <si>
+    <t>From CL_max and mult_V_TO</t>
+  </si>
+  <si>
+    <t>Sadraey, eqn 4.68</t>
+  </si>
+  <si>
+    <t>Sadraey, eqn 4.69c</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Air density</t>
+  </si>
+  <si>
+    <t>SL air density</t>
+  </si>
+  <si>
+    <t>Gravitational constant</t>
+  </si>
+  <si>
+    <t>Takeoff friction coeff</t>
+  </si>
+  <si>
+    <t>Landing friction coeff</t>
+  </si>
+  <si>
+    <t>Oswald span efficiency</t>
+  </si>
+  <si>
+    <t>Wing aspect ratio</t>
+  </si>
+  <si>
+    <t>Inducer drag factor</t>
+  </si>
+  <si>
+    <t>Takeoff CL</t>
+  </si>
+  <si>
+    <t>Before rotation, no flaps, therefore similar to cruise</t>
+  </si>
+  <si>
+    <t>Rotation CL</t>
+  </si>
+  <si>
+    <t>Max CL (at stall)</t>
+  </si>
+  <si>
+    <t>Cruise CL</t>
+  </si>
+  <si>
+    <t>Zero lift CD</t>
+  </si>
+  <si>
+    <t>CD at cruise</t>
+  </si>
+  <si>
+    <t>CD at takeoff</t>
+  </si>
+  <si>
+    <t>Ground roll CD</t>
+  </si>
+  <si>
+    <t>Max lift efficiency</t>
+  </si>
+  <si>
+    <t>Climb lift efficiency</t>
+  </si>
+  <si>
+    <t>Stall speed</t>
+  </si>
+  <si>
+    <t>Takeoff speed multiplier</t>
+  </si>
+  <si>
+    <t>Takeoff speed</t>
+  </si>
+  <si>
+    <t>Cruise speed</t>
+  </si>
+  <si>
+    <t>From CL_max, V_S, and CL_C</t>
+  </si>
+  <si>
+    <t>Sadraey, table 5.8</t>
+  </si>
+  <si>
+    <t>Home-built/GA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -88,8 +325,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -105,6 +345,363 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>414393</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE85865D-243B-21C2-29FE-5EE213F21D6D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="542925" y="6696075"/>
+          <a:ext cx="3538593" cy="2924175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>540205</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>131989</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>308883</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>106646</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{329341C1-471F-394B-1332-039B5EDF8DA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4559755" y="6799489"/>
+          <a:ext cx="4035878" cy="2641657"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>497417</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4FD1E4C-F1AE-BD9B-09A7-1331E49EA118}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="619125" y="10077450"/>
+          <a:ext cx="3545417" cy="3190875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>593271</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>4082</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>449036</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>86494</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{451C7191-2FE1-4DBE-52CD-F9E9F6DB8379}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4838700" y="11815082"/>
+          <a:ext cx="4754336" cy="3701912"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>149678</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>176892</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>367392</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>162870</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{598D4E09-668D-3CEE-674D-583D9F625EC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5007428" y="10654392"/>
+          <a:ext cx="4503964" cy="1128978"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>182217</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>851355</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>24847</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08378201-1D51-6FE3-74CF-890B33040648}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="381000" y="13898217"/>
+          <a:ext cx="4147833" cy="1557130"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1676400</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>20003</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{298E0B5B-659D-CEE9-3A24-3693AA75A033}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="381000" y="16478250"/>
+          <a:ext cx="4962525" cy="496253"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>248180</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>57696</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36EBDD73-E8D9-03CD-63D6-2133043EFA8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6715125" y="16906875"/>
+          <a:ext cx="3801005" cy="3915321"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -370,13 +967,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -387,44 +986,438 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>9.81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>0.05</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>0.08</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="2">
+        <f>1/(PI()*B6*B7)</f>
+        <v>9.0945681766797334E-2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9">
+        <v>0.3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>1.2</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B10">
+        <v>1.5</v>
+      </c>
+      <c r="C10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11">
+        <f>B9</f>
+        <v>0.3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="1">
+        <f>B10/B20^2</f>
+        <v>1.2396694214876032</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2">
+        <f>B13+B8*B9^2</f>
+        <v>4.8185111359011761E-2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="2">
+        <f>B13+B8*B11^2</f>
+        <v>4.8185111359011761E-2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="2">
+        <f>B15-B4*B11</f>
+        <v>3.3185111359011761E-2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B17" s="1">
+        <f>B9/B14</f>
+        <v>6.2259895544247374</v>
+      </c>
+      <c r="C17" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C20" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>10.5</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="1">
+        <f>B20*B19</f>
+        <v>11.55</v>
+      </c>
+      <c r="C21" t="s">
         <v>8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="1">
+        <f>SQRT(B19^2*B10/B9)</f>
+        <v>23.478713763747791</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA744A0F-D2B6-4787-95B2-423EDC62E8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE20C6B-CECC-4348-9C23-678EAC228E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
-    <sheet name="Outputs" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="106">
   <si>
     <t>Parameter</t>
   </si>
@@ -90,18 +89,12 @@
     <t>V_TO</t>
   </si>
   <si>
-    <t>V_M</t>
-  </si>
-  <si>
     <t>V_S_M</t>
   </si>
   <si>
     <t>phi_C</t>
   </si>
   <si>
-    <t>L_D_climb</t>
-  </si>
-  <si>
     <t>gamma</t>
   </si>
   <si>
@@ -126,15 +119,9 @@
     <t>n</t>
   </si>
   <si>
-    <t>n_M</t>
-  </si>
-  <si>
     <t>e</t>
   </si>
   <si>
-    <t>bank</t>
-  </si>
-  <si>
     <t>Sadraey, table 4.12</t>
   </si>
   <si>
@@ -264,9 +251,6 @@
     <t>Max lift efficiency</t>
   </si>
   <si>
-    <t>Climb lift efficiency</t>
-  </si>
-  <si>
     <t>Stall speed</t>
   </si>
   <si>
@@ -286,6 +270,90 @@
   </si>
   <si>
     <t>Home-built/GA</t>
+  </si>
+  <si>
+    <t>Max load factor</t>
+  </si>
+  <si>
+    <t>Sadraey, table 10.9</t>
+  </si>
+  <si>
+    <t>Manuever stall speed</t>
+  </si>
+  <si>
+    <t>bank_angle</t>
+  </si>
+  <si>
+    <t>AAE 451, constraints slide 19</t>
+  </si>
+  <si>
+    <t>Cruise throttle</t>
+  </si>
+  <si>
+    <t>Climb angle</t>
+  </si>
+  <si>
+    <t>deg</t>
+  </si>
+  <si>
+    <t>Cruise propellor efficiency</t>
+  </si>
+  <si>
+    <t>Takeoff propellor efficiency</t>
+  </si>
+  <si>
+    <t>Gudmundsson, table 3-3</t>
+  </si>
+  <si>
+    <t>Sadraey, ch. 4 pg. 126</t>
+  </si>
+  <si>
+    <t>Bank angle</t>
+  </si>
+  <si>
+    <t>In range from Guimaraes</t>
+  </si>
+  <si>
+    <t>climb_alt</t>
+  </si>
+  <si>
+    <t>climb_dist</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Mission altitude</t>
+  </si>
+  <si>
+    <t>Distance for climb to alt</t>
+  </si>
+  <si>
+    <t>Estimated from mission flight path</t>
+  </si>
+  <si>
+    <t>Mission requirements</t>
+  </si>
+  <si>
+    <t>W_S</t>
+  </si>
+  <si>
+    <t>W_P</t>
+  </si>
+  <si>
+    <t>Wing loading</t>
+  </si>
+  <si>
+    <t>Power loading</t>
+  </si>
+  <si>
+    <t>N/W</t>
+  </si>
+  <si>
+    <t>N/m^2</t>
+  </si>
+  <si>
+    <t>Assumed at cruise</t>
   </si>
 </sst>
 </file>
@@ -293,10 +361,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,16 +372,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -321,17 +414,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Calculation" xfId="2" builtinId="22"/>
+    <cellStyle name="Input" xfId="1" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -353,13 +481,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>414393</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:colOff>395343</xdr:colOff>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -397,13 +525,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>540205</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>131989</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>308883</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>106646</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -441,13 +569,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>497417</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:colOff>478367</xdr:colOff>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -485,13 +613,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>593271</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>4082</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>449036</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>86494</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -529,13 +657,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>149678</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>176892</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>367392</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>162870</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -573,13 +701,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>182217</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>851355</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:colOff>832305</xdr:colOff>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>24847</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -617,13 +745,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1676400</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:colOff>1657350</xdr:colOff>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>20003</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -661,13 +789,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>248180</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>108</xdr:row>
       <xdr:rowOff>57696</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -693,6 +821,138 @@
         <a:xfrm>
           <a:off x="6715125" y="16906875"/>
           <a:ext cx="3801005" cy="3915321"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>48283</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>152820</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F04BE162-6BBA-5A7A-5CB0-4DD6DA46E42A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="723900" y="17716500"/>
+          <a:ext cx="4715533" cy="3010320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1647825</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>173513</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D8222C7-53BC-4271-33A8-EF554B773075}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="771525" y="21116925"/>
+          <a:ext cx="4543425" cy="2869088"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>139546</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFCE2E77-7396-F476-E355-AA7247FC8DC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5676900" y="21774150"/>
+          <a:ext cx="6438900" cy="1225396"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -967,10 +1227,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.85546875" customWidth="1"/>
   </cols>
@@ -986,134 +1246,134 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>1.2250000000000001</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>9.81</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>0.05</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>0.08</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="1">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2">
         <v>0.7</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="1">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2">
         <v>5</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="2">
+        <v>34</v>
+      </c>
+      <c r="B8" s="3">
         <f>1/(PI()*B6*B7)</f>
         <v>9.0945681766797334E-2</v>
       </c>
@@ -1121,113 +1381,113 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9">
+        <v>37</v>
+      </c>
+      <c r="B9" s="1">
         <v>0.3</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>1.5</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11">
+        <v>44</v>
+      </c>
+      <c r="B11" s="5">
         <f>B9</f>
         <v>0.3</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="1">
-        <f>B10/B20^2</f>
+        <v>48</v>
+      </c>
+      <c r="B12" s="6">
+        <f>B10/B19^2</f>
         <v>1.2396694214876032</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2">
+        <v>23</v>
+      </c>
+      <c r="B13" s="4">
         <v>0.04</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="2">
+        <v>24</v>
+      </c>
+      <c r="B14" s="3">
         <f>B13+B8*B9^2</f>
         <v>4.8185111359011761E-2</v>
       </c>
@@ -1235,17 +1495,17 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="2">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3">
         <f>B13+B8*B11^2</f>
         <v>4.8185111359011761E-2</v>
       </c>
@@ -1253,20 +1513,20 @@
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="2">
+        <v>25</v>
+      </c>
+      <c r="B16" s="3">
         <f>B15-B4*B11</f>
         <v>3.3185111359011761E-2</v>
       </c>
@@ -1274,17 +1534,17 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="6">
         <f>B9/B14</f>
         <v>6.2259895544247374</v>
       </c>
@@ -1292,140 +1552,258 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="F17" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>5</v>
+      </c>
+      <c r="B18" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>71</v>
+      </c>
+      <c r="E18" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="1">
-        <v>10.5</v>
+        <v>47</v>
+      </c>
+      <c r="B19" s="7">
+        <v>1.1000000000000001</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="E19" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="3">
-        <v>1.1000000000000001</v>
+        <v>16</v>
+      </c>
+      <c r="B20" s="6">
+        <f>B19*B18</f>
+        <v>11.55</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="1">
-        <f>B20*B19</f>
-        <v>11.55</v>
+        <v>15</v>
+      </c>
+      <c r="B21" s="6">
+        <f>SQRT(B18^2*B10/B9)</f>
+        <v>23.478713763747791</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" t="s">
-        <v>42</v>
+        <v>74</v>
+      </c>
+      <c r="F21" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="1">
-        <f>SQRT(B19^2*B10/B9)</f>
-        <v>23.478713763747791</v>
+        <v>17</v>
+      </c>
+      <c r="B22" s="6">
+        <f>B18*SQRT(B23)</f>
+        <v>12.859821149611683</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
-      </c>
-      <c r="F22" t="s">
         <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>26</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>81</v>
+      </c>
+      <c r="B24" s="6">
+        <f>DEGREES(ACOS(1/B23))</f>
+        <v>48.189685104221404</v>
+      </c>
+      <c r="C24" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="B25" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>21</v>
       </c>
+      <c r="B26" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="B27" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>92</v>
+      </c>
+      <c r="B28" s="1">
+        <v>30</v>
+      </c>
+      <c r="C28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>93</v>
+      </c>
+      <c r="B29" s="8">
+        <v>100</v>
+      </c>
+      <c r="C29" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>31</v>
+        <v>19</v>
+      </c>
+      <c r="B30" s="6">
+        <f>DEGREES(ATAN(30/100))</f>
+        <v>16.699244233993621</v>
+      </c>
+      <c r="C30" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4737484-ECD6-4099-B071-A6ABFA09556B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE20C6B-CECC-4348-9C23-678EAC228E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50660628-DB97-442F-8311-3185EB8E5F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Inputs" sheetId="1" r:id="rId1"/>
+    <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -612,15 +612,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>593271</xdr:colOff>
+      <xdr:colOff>297996</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>4082</xdr:rowOff>
+      <xdr:rowOff>108857</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>449036</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>86494</xdr:rowOff>
+      <xdr:colOff>153761</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>769</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -643,8 +643,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4838700" y="11815082"/>
-          <a:ext cx="4754336" cy="3701912"/>
+          <a:off x="6317796" y="12491357"/>
+          <a:ext cx="4732565" cy="3701912"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -655,16 +655,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>149678</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>176892</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>254453</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>81642</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>367392</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>162870</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>472167</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>67620</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -687,8 +687,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5007428" y="10654392"/>
-          <a:ext cx="4503964" cy="1128978"/>
+          <a:off x="6274253" y="10940142"/>
+          <a:ext cx="4484914" cy="1128978"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50660628-DB97-442F-8311-3185EB8E5F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFD7F99-B8C2-4D04-AFEF-A66B193642DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -335,12 +335,6 @@
     <t>Mission requirements</t>
   </si>
   <si>
-    <t>W_S</t>
-  </si>
-  <si>
-    <t>W_P</t>
-  </si>
-  <si>
     <t>Wing loading</t>
   </si>
   <si>
@@ -354,6 +348,12 @@
   </si>
   <si>
     <t>Assumed at cruise</t>
+  </si>
+  <si>
+    <t>W_S_design</t>
+  </si>
+  <si>
+    <t>W_P_design</t>
   </si>
 </sst>
 </file>
@@ -486,7 +486,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>395343</xdr:colOff>
+      <xdr:colOff>347718</xdr:colOff>
       <xdr:row>54</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
@@ -574,7 +574,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>478367</xdr:colOff>
+      <xdr:colOff>430742</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
@@ -706,7 +706,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>832305</xdr:colOff>
+      <xdr:colOff>784680</xdr:colOff>
       <xdr:row>83</xdr:row>
       <xdr:rowOff>24847</xdr:rowOff>
     </xdr:to>
@@ -750,7 +750,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1657350</xdr:colOff>
+      <xdr:colOff>1609725</xdr:colOff>
       <xdr:row>89</xdr:row>
       <xdr:rowOff>20003</xdr:rowOff>
     </xdr:to>
@@ -1230,7 +1230,7 @@
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.85546875" customWidth="1"/>
   </cols>
@@ -1555,7 +1555,7 @@
         <v>70</v>
       </c>
       <c r="F17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1780,26 +1780,30 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" t="s">
         <v>99</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" t="s">
-        <v>103</v>
-      </c>
-      <c r="D31" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" t="s">
         <v>100</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFD7F99-B8C2-4D04-AFEF-A66B193642DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDE7724-D03F-485E-BB28-969DD0C44742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="111">
   <si>
     <t>Parameter</t>
   </si>
@@ -354,6 +354,21 @@
   </si>
   <si>
     <t>W_P_design</t>
+  </si>
+  <si>
+    <t>V_M</t>
+  </si>
+  <si>
+    <t>Manuever speed</t>
+  </si>
+  <si>
+    <t>S_TO</t>
+  </si>
+  <si>
+    <t>Takeoff distance</t>
+  </si>
+  <si>
+    <t>RFP requirements</t>
   </si>
 </sst>
 </file>
@@ -481,13 +496,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>347718</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -525,13 +540,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>540205</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>131989</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>308883</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>106646</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -569,13 +584,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>430742</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -613,13 +628,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>297996</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>108857</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>153761</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>769</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -657,13 +672,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>254453</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>81642</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>472167</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>67620</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -701,13 +716,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>182217</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>784680</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>24847</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -745,13 +760,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1609725</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>20003</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -789,13 +804,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>248180</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>109</xdr:row>
       <xdr:rowOff>57696</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -833,13 +848,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>48283</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>109</xdr:row>
       <xdr:rowOff>152820</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -877,13 +892,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1647825</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>173513</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -921,13 +936,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>113</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>119</xdr:row>
+      <xdr:row>120</xdr:row>
       <xdr:rowOff>139546</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1227,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -1432,6 +1447,9 @@
         <f>B9</f>
         <v>0.3</v>
       </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
       <c r="D11" t="s">
         <v>61</v>
       </c>
@@ -1630,74 +1648,71 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="6">
-        <f>B18*SQRT(B23)</f>
-        <v>12.859821149611683</v>
+        <v>106</v>
+      </c>
+      <c r="B22" s="2">
+        <v>15</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1.5</v>
+        <v>17</v>
+      </c>
+      <c r="B23" s="6">
+        <f>B18*SQRT(B24)</f>
+        <v>12.859821149611683</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24" s="6">
-        <f>DEGREES(ACOS(1/B23))</f>
-        <v>48.189685104221404</v>
+        <v>26</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1.5</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>78</v>
+      </c>
+      <c r="E24" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0.75</v>
+        <v>81</v>
+      </c>
+      <c r="B25" s="6">
+        <f>DEGREES(ACOS(1/B24))</f>
+        <v>48.189685104221404</v>
       </c>
       <c r="C25" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
-      </c>
-      <c r="E25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B26" s="1">
         <v>0.75</v>
@@ -1706,24 +1721,24 @@
         <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" s="1">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s">
         <v>88</v>
@@ -1731,78 +1746,112 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="B28" s="1">
-        <v>30</v>
+        <v>0.45</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>93</v>
-      </c>
-      <c r="B29" s="8">
-        <v>100</v>
+        <v>92</v>
+      </c>
+      <c r="B29" s="1">
+        <v>30</v>
       </c>
       <c r="C29" t="s">
         <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="8">
+        <v>100</v>
+      </c>
+      <c r="C30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B31" s="6">
         <f>DEGREES(ATAN(30/100))</f>
         <v>16.699244233993621</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>85</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>104</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>101</v>
-      </c>
-      <c r="D31" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="2">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" t="s">
+        <v>109</v>
+      </c>
+      <c r="E32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>105</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B34" s="1">
         <v>0.1</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C34" t="s">
         <v>102</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D34" t="s">
         <v>100</v>
       </c>
     </row>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDE7724-D03F-485E-BB28-969DD0C44742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2CCD1B9-C8A6-43B6-BF45-FB1E8C75DCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="113">
   <si>
     <t>Parameter</t>
   </si>
@@ -369,6 +369,12 @@
   </si>
   <si>
     <t>RFP requirements</t>
+  </si>
+  <si>
+    <t>R_M</t>
+  </si>
+  <si>
+    <t>Turn radius</t>
   </si>
 </sst>
 </file>
@@ -496,13 +502,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>347718</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -584,13 +590,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>430742</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -716,13 +722,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>182217</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>784680</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>24847</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -760,13 +766,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1609725</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>20003</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -848,13 +854,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>48283</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>110</xdr:row>
       <xdr:rowOff>152820</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -892,13 +898,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1647825</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>173513</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -936,13 +942,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>114</xdr:row>
+      <xdr:row>115</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>120</xdr:row>
+      <xdr:row>121</xdr:row>
       <xdr:rowOff>139546</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1242,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -1650,8 +1656,9 @@
       <c r="A22" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="2">
-        <v>15</v>
+      <c r="B22" s="6">
+        <f>SQRT(B25*B3*SQRT(B24^2-1))</f>
+        <v>14.810748414335091</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
@@ -1697,39 +1704,39 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="1">
+        <v>20</v>
+      </c>
+      <c r="C25" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B26" s="6">
         <f>DEGREES(ACOS(1/B24))</f>
         <v>48.189685104221404</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>85</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="C26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B27" s="1">
         <v>0.75</v>
@@ -1738,24 +1745,24 @@
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28" s="1">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E28" t="s">
         <v>88</v>
@@ -1763,95 +1770,112 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="B29" s="1">
-        <v>30</v>
+        <v>0.45</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>93</v>
-      </c>
-      <c r="B30" s="8">
-        <v>100</v>
+        <v>92</v>
+      </c>
+      <c r="B30" s="1">
+        <v>30</v>
       </c>
       <c r="C30" t="s">
         <v>94</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="8">
+        <v>100</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B32" s="6">
         <f>DEGREES(ATAN(30/100))</f>
         <v>16.699244233993621</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" t="s">
         <v>85</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D32" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>108</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B33" s="2">
         <v>25</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>94</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>109</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E33" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>105</v>
-      </c>
-      <c r="B34" s="1">
-        <v>0.1</v>
+      <c r="B34" s="8">
+        <v>100</v>
       </c>
       <c r="C34" t="s">
         <v>102</v>
       </c>
       <c r="D34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C35" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" t="s">
         <v>100</v>
       </c>
     </row>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2CCD1B9-C8A6-43B6-BF45-FB1E8C75DCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B08173-8C90-4B7D-84C9-ACB9FBB4E14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -218,9 +218,6 @@
     <t>Wing aspect ratio</t>
   </si>
   <si>
-    <t>Inducer drag factor</t>
-  </si>
-  <si>
     <t>Takeoff CL</t>
   </si>
   <si>
@@ -375,6 +372,9 @@
   </si>
   <si>
     <t>Turn radius</t>
+  </si>
+  <si>
+    <t>Induced drag factor</t>
   </si>
 </sst>
 </file>
@@ -1384,10 +1384,10 @@
         <v>59</v>
       </c>
       <c r="E7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" t="s">
         <v>76</v>
-      </c>
-      <c r="F7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1402,7 +1402,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="E8" t="s">
         <v>43</v>
@@ -1419,7 +1419,7 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
@@ -1436,7 +1436,7 @@
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
         <v>35</v>
@@ -1457,13 +1457,13 @@
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
         <v>51</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1478,7 +1478,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>46</v>
@@ -1498,7 +1498,7 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
@@ -1519,7 +1519,7 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
         <v>42</v>
@@ -1537,13 +1537,13 @@
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
         <v>50</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1558,7 +1558,7 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
         <v>41</v>
@@ -1576,10 +1576,10 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1593,10 +1593,10 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1610,7 +1610,7 @@
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
         <v>38</v>
@@ -1628,7 +1628,7 @@
         <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E20" t="s">
         <v>38</v>
@@ -1646,15 +1646,15 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" t="s">
         <v>74</v>
-      </c>
-      <c r="F21" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B22" s="6">
         <f>SQRT(B25*B3*SQRT(B24^2-1))</f>
@@ -1664,7 +1664,7 @@
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1679,10 +1679,10 @@
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1696,42 +1696,42 @@
         <v>7</v>
       </c>
       <c r="D24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" t="s">
         <v>78</v>
-      </c>
-      <c r="E24" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B25" s="1">
         <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="6">
         <f>DEGREES(ACOS(1/B24))</f>
         <v>48.189685104221404</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1745,10 +1745,10 @@
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1762,10 +1762,10 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1779,44 +1779,44 @@
         <v>7</v>
       </c>
       <c r="D29" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" t="s">
         <v>87</v>
-      </c>
-      <c r="E29" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B30" s="1">
         <v>30</v>
       </c>
       <c r="C30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" t="s">
         <v>94</v>
       </c>
-      <c r="D30" t="s">
-        <v>95</v>
-      </c>
       <c r="E30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B31" s="8">
         <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D31" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" t="s">
         <v>96</v>
-      </c>
-      <c r="E31" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1828,55 +1828,55 @@
         <v>16.699244233993621</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B33" s="2">
         <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" t="s">
         <v>109</v>
-      </c>
-      <c r="E33" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B34" s="8">
         <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B35" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B08173-8C90-4B7D-84C9-ACB9FBB4E14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1D51F8-171E-4C00-B903-FD6F8A90555B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1870,7 +1870,7 @@
         <v>104</v>
       </c>
       <c r="B35" s="1">
-        <v>7.4999999999999997E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C35" t="s">
         <v>100</v>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1D51F8-171E-4C00-B903-FD6F8A90555B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{2B1D51F8-171E-4C00-B903-FD6F8A90555B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45113ED3-2F10-4018-92D1-8DA96B32B4B0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
@@ -507,9 +507,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>347718</xdr:colOff>
+      <xdr:colOff>353433</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -551,9 +551,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>308883</xdr:colOff>
+      <xdr:colOff>314598</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>106646</xdr:rowOff>
+      <xdr:rowOff>99026</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -595,9 +595,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>430742</xdr:colOff>
+      <xdr:colOff>434552</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -683,9 +683,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>472167</xdr:colOff>
+      <xdr:colOff>475977</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>67620</xdr:rowOff>
+      <xdr:rowOff>60000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -727,9 +727,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>784680</xdr:colOff>
+      <xdr:colOff>780870</xdr:colOff>
       <xdr:row>86</xdr:row>
-      <xdr:rowOff>24847</xdr:rowOff>
+      <xdr:rowOff>21037</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -771,9 +771,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1609725</xdr:colOff>
+      <xdr:colOff>1619250</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>20003</xdr:rowOff>
+      <xdr:rowOff>16193</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -815,9 +815,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>248180</xdr:colOff>
+      <xdr:colOff>244370</xdr:colOff>
       <xdr:row>109</xdr:row>
-      <xdr:rowOff>57696</xdr:rowOff>
+      <xdr:rowOff>53886</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -859,7 +859,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>48283</xdr:colOff>
+      <xdr:colOff>57808</xdr:colOff>
       <xdr:row>110</xdr:row>
       <xdr:rowOff>152820</xdr:rowOff>
     </xdr:to>
@@ -903,9 +903,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1647825</xdr:colOff>
+      <xdr:colOff>1657350</xdr:colOff>
       <xdr:row>127</xdr:row>
-      <xdr:rowOff>173513</xdr:rowOff>
+      <xdr:rowOff>169703</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -947,9 +947,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>121</xdr:row>
-      <xdr:rowOff>139546</xdr:rowOff>
+      <xdr:rowOff>135736</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1248,15 +1248,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1276,7 +1276,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1582,7 +1582,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>105</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>110</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>91</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>92</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>19</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>103</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>104</v>
       </c>
@@ -1878,6 +1878,9 @@
       <c r="D35" t="s">
         <v>99</v>
       </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B36" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,17 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF1B17B-09B2-4594-99A8-59303D560F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="INPUTS" sheetId="1" r:id="rId5"/>
+    <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -33,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="128">
   <si>
     <t>Parameter</t>
   </si>
@@ -378,30 +400,60 @@
   </si>
   <si>
     <t>Empty Weight Fraction</t>
+  </si>
+  <si>
+    <t>visc</t>
+  </si>
+  <si>
+    <t>Pa-s</t>
+  </si>
+  <si>
+    <t>Air viscosity</t>
+  </si>
+  <si>
+    <t>MTOW</t>
+  </si>
+  <si>
+    <t>MTOM</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>Takeoff mass</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Takeoff weight</t>
+  </si>
+  <si>
+    <t>S_wing</t>
+  </si>
+  <si>
+    <t>m^2</t>
+  </si>
+  <si>
+    <t>Wing area</t>
+  </si>
+  <si>
+    <t>From weight estimation code</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="59" formatCode="0.000"/>
-    <numFmt numFmtId="60" formatCode="0.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000E+00"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
@@ -411,13 +463,34 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="11"/>
       <color indexed="14"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -440,6 +513,11 @@
       <patternFill patternType="solid">
         <fgColor indexed="15"/>
         <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -541,127 +619,161 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="59" fontId="4" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="59" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="60" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Calculation" xfId="1" builtinId="22"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ff7f7f7f"/>
-      <rgbColor rgb="ff3f3f76"/>
-      <rgbColor rgb="ffffcc99"/>
-      <rgbColor rgb="fffa7d00"/>
-      <rgbColor rgb="fff2f2f2"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="FF7F7F7F"/>
+      <rgbColor rgb="FF3F3F76"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFA7D00"/>
+      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>28572</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>353433</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>91441</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -687,26 +799,30 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>540205</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>131984</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>314597</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>99025</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2" descr="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -732,26 +848,30 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>171452</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>434552</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>133356</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3" descr="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -777,26 +897,30 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>297995</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>108861</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>153761</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>778</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4" descr="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -822,26 +946,30 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>254451</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>81644</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>475977</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>60004</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="Picture 5"/>
+        <xdr:cNvPr id="6" name="Picture 5" descr="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId5">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -867,26 +995,30 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>182223</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>780870</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>21047</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="Picture 6"/>
+        <xdr:cNvPr id="7" name="Picture 6" descr="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId6">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -912,26 +1044,30 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>95262</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1619250</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>16204</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="Picture 7"/>
+        <xdr:cNvPr id="8" name="Picture 7" descr="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId7">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -957,26 +1093,30 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>142885</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>244370</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>110</xdr:row>
       <xdr:rowOff>53903</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8" descr="Picture 8"/>
+        <xdr:cNvPr id="9" name="Picture 8" descr="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId8">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1002,26 +1142,30 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>13</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>57808</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>152837</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9" descr="Picture 9"/>
+        <xdr:cNvPr id="10" name="Picture 9" descr="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId9">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1047,26 +1191,30 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>112</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>161942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1657350</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>128</xdr:row>
       <xdr:rowOff>169725</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10" descr="Picture 10"/>
+        <xdr:cNvPr id="11" name="Picture 10" descr="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId10">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1092,26 +1240,30 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>115</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>57167</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>15239</xdr:colOff>
-      <xdr:row>121</xdr:row>
+      <xdr:row>122</xdr:row>
       <xdr:rowOff>135756</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11" descr="Picture 11"/>
+        <xdr:cNvPr id="12" name="Picture 11" descr="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId11">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1137,7 +1289,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office Theme">
       <a:dk1>
@@ -1339,7 +1491,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1357,7 +1509,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1386,7 +1538,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1411,7 +1563,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1436,7 +1588,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1461,7 +1613,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1486,7 +1638,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1511,7 +1663,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1536,7 +1688,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1561,7 +1713,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1586,7 +1738,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1599,9 +1751,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -1618,7 +1776,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1636,7 +1794,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1661,7 +1819,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1686,7 +1844,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1711,7 +1869,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1736,7 +1894,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1761,7 +1919,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1786,7 +1944,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1811,7 +1969,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1836,7 +1994,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1861,7 +2019,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1874,9 +2032,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1890,7 +2054,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1908,7 +2072,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1937,7 +2101,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1962,7 +2126,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1987,7 +2151,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2012,7 +2176,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2037,7 +2201,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2062,7 +2226,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2087,7 +2251,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2112,7 +2276,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2137,7 +2301,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2150,45 +2314,53 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q128"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="14.4" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q129"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.8516" style="1" customWidth="1"/>
-    <col min="2" max="3" width="8.85156" style="1" customWidth="1"/>
-    <col min="4" max="5" width="25.8516" style="1" customWidth="1"/>
-    <col min="6" max="17" width="8.85156" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.85156" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="25.85546875" style="1" customWidth="1"/>
+    <col min="6" max="18" width="8.85546875" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.4" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="3">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="2">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="2">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="2">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="2">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4"/>
@@ -2203,23 +2375,23 @@
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
     </row>
-    <row r="2" ht="14.4" customHeight="1">
-      <c r="A2" t="s" s="5">
+    <row r="2" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="6">
-        <v>1.225</v>
-      </c>
-      <c r="C2" t="s" s="7">
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="2">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s" s="2">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s" s="2">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="4"/>
@@ -2234,23 +2406,23 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
     </row>
-    <row r="3" ht="14.4" customHeight="1">
-      <c r="A3" t="s" s="5">
-        <v>11</v>
-      </c>
-      <c r="B3" s="6">
-        <v>9.81</v>
-      </c>
-      <c r="C3" t="s" s="7">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s" s="2">
+    <row r="3" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="15">
+        <v>1.7960000000000001E-5</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="2"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -2263,25 +2435,23 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" ht="14.4" customHeight="1">
-      <c r="A4" t="s" s="5">
-        <v>15</v>
+    <row r="4" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A4" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="B4" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="C4" t="s" s="7">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>9.81</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -2294,24 +2464,24 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
     </row>
-    <row r="5" ht="14.4" customHeight="1">
-      <c r="A5" t="s" s="5">
-        <v>20</v>
+    <row r="5" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A5" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="B5" s="6">
-        <v>0.08</v>
-      </c>
-      <c r="C5" t="s" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s" s="2">
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F5" t="s" s="2">
-        <v>22</v>
+      <c r="F5" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -2325,23 +2495,25 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" ht="14.4" customHeight="1">
-      <c r="A6" t="s" s="5">
-        <v>23</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.7</v>
-      </c>
-      <c r="C6" t="s" s="7">
+    <row r="6" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="F6" s="4"/>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -2354,25 +2526,23 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
     </row>
-    <row r="7" ht="14.4" customHeight="1">
-      <c r="A7" t="s" s="5">
-        <v>26</v>
+    <row r="7" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A7" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="B7" s="8">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>29</v>
-      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -2385,24 +2555,25 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" ht="14.4" customHeight="1">
-      <c r="A8" t="s" s="5">
-        <v>30</v>
-      </c>
-      <c r="B8" s="9" cm="1">
-        <f t="array" ref="B8">1/(PI()*B6*B7)</f>
-        <v>0.09094568176679731</v>
-      </c>
-      <c r="C8" t="s" s="7">
+    <row r="8" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="8">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D8" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="F8" s="4"/>
+      <c r="D8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -2415,21 +2586,22 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" ht="14.4" customHeight="1">
-      <c r="A9" t="s" s="5">
-        <v>33</v>
-      </c>
-      <c r="B9" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="C9" t="s" s="7">
+    <row r="9" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="9" cm="1">
+        <f t="array" ref="B9">1/(PI()*B7*B8)</f>
+        <v>9.0945681766797334E-2</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D9" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>35</v>
+      <c r="D9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
@@ -2444,25 +2616,23 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" ht="14.4" customHeight="1">
-      <c r="A10" t="s" s="5">
-        <v>36</v>
+    <row r="10" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A10" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="B10" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="C10" t="s" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D10" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="F10" t="s" s="2">
-        <v>39</v>
-      </c>
+      <c r="D10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -2475,25 +2645,24 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
     </row>
-    <row r="11" ht="14.4" customHeight="1">
-      <c r="A11" t="s" s="5">
-        <v>40</v>
-      </c>
-      <c r="B11" s="10" cm="1">
-        <f t="array" ref="B11">B9</f>
-        <v>0.3</v>
-      </c>
-      <c r="C11" t="s" s="7">
+    <row r="11" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D11" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="F11" t="s" s="2">
-        <v>43</v>
+      <c r="D11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -2507,25 +2676,25 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" ht="14.4" customHeight="1">
-      <c r="A12" t="s" s="5">
-        <v>44</v>
-      </c>
-      <c r="B12" s="11" cm="1">
-        <f t="array" ref="B12">B10/B19^2</f>
-        <v>1.2396694214876</v>
-      </c>
-      <c r="C12" t="s" s="7">
+    <row r="12" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="10" cm="1">
+        <f t="array" ref="B12">B10</f>
+        <v>0.3</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D12" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="F12" t="s" s="2">
-        <v>47</v>
+      <c r="D12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -2539,24 +2708,25 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
-    <row r="13" ht="14.4" customHeight="1">
-      <c r="A13" t="s" s="5">
-        <v>48</v>
-      </c>
-      <c r="B13" s="12">
-        <v>0.04</v>
-      </c>
-      <c r="C13" t="s" s="7">
+    <row r="13" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="11" cm="1">
+        <f t="array" ref="B13">B11/B20^2</f>
+        <v>1.2396694214876032</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D13" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="F13" t="s" s="2">
-        <v>51</v>
+      <c r="D13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -2570,24 +2740,25 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" ht="14.4" customHeight="1">
-      <c r="A14" t="s" s="5">
-        <v>52</v>
-      </c>
-      <c r="B14" s="9" cm="1">
-        <f t="array" ref="B14">B13+B8*B9^2</f>
-        <v>0.0481851113590118</v>
-      </c>
-      <c r="C14" t="s" s="7">
+    <row r="14" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="12">
+        <v>0.04</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D14" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="F14" s="4"/>
+      <c r="D14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -2600,26 +2771,24 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
     </row>
-    <row r="15" ht="14.4" customHeight="1">
-      <c r="A15" t="s" s="5">
-        <v>55</v>
+    <row r="15" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A15" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="B15" s="9" cm="1">
-        <f t="array" ref="B15">B13+B8*B11^2</f>
-        <v>0.0481851113590118</v>
-      </c>
-      <c r="C15" t="s" s="7">
+        <f t="array" ref="B15">B14+B9*B10^2</f>
+        <v>4.8185111359011761E-2</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D15" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="F15" t="s" s="2">
-        <v>43</v>
-      </c>
+      <c r="D15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -2632,24 +2801,26 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
     </row>
-    <row r="16" ht="14.4" customHeight="1">
-      <c r="A16" t="s" s="5">
-        <v>58</v>
+    <row r="16" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A16" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="B16" s="9" cm="1">
-        <f t="array" ref="B16">B15-B4*B11</f>
-        <v>0.0331851113590118</v>
-      </c>
-      <c r="C16" t="s" s="7">
+        <f t="array" ref="B16">B14+B9*B12^2</f>
+        <v>4.8185111359011761E-2</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D16" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="E16" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="F16" s="4"/>
+      <c r="D16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -2662,24 +2833,24 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
     </row>
-    <row r="17" ht="14.4" customHeight="1">
-      <c r="A17" t="s" s="5">
-        <v>61</v>
-      </c>
-      <c r="B17" s="11" cm="1">
-        <f t="array" ref="B17">B9/B14</f>
-        <v>6.22598955442473</v>
-      </c>
-      <c r="C17" t="s" s="7">
+    <row r="17" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="9" cm="1">
+        <f t="array" ref="B17">B16-B5*B12</f>
+        <v>3.3185111359011761E-2</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D17" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="E17" s="4"/>
-      <c r="F17" t="s" s="2">
-        <v>63</v>
-      </c>
+      <c r="D17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -2692,23 +2863,24 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
     </row>
-    <row r="18" ht="14.4" customHeight="1">
-      <c r="A18" t="s" s="5">
-        <v>64</v>
-      </c>
-      <c r="B18" s="8">
-        <v>10.5</v>
-      </c>
-      <c r="C18" t="s" s="7">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="E18" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="F18" s="4"/>
+    <row r="18" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="11" cm="1">
+        <f t="array" ref="B18">B10/B15</f>
+        <v>6.2259895544247374</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -2721,21 +2893,21 @@
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
     </row>
-    <row r="19" ht="14.4" customHeight="1">
-      <c r="A19" t="s" s="5">
-        <v>67</v>
-      </c>
-      <c r="B19" s="13">
-        <v>1.1</v>
-      </c>
-      <c r="C19" t="s" s="7">
-        <v>16</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="E19" t="s" s="2">
-        <v>35</v>
+    <row r="19" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -2750,21 +2922,20 @@
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
     </row>
-    <row r="20" ht="14.4" customHeight="1">
-      <c r="A20" t="s" s="5">
-        <v>69</v>
-      </c>
-      <c r="B20" s="11" cm="1">
-        <f t="array" ref="B20">B19*B18</f>
-        <v>11.55</v>
-      </c>
-      <c r="C20" t="s" s="7">
-        <v>12</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="E20" t="s" s="2">
+    <row r="20" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A20" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="13">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F20" s="4"/>
@@ -2780,24 +2951,24 @@
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
     </row>
-    <row r="21" ht="14.4" customHeight="1">
-      <c r="A21" t="s" s="5">
-        <v>71</v>
+    <row r="21" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A21" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="B21" s="11" cm="1">
-        <f t="array" ref="B21">SQRT(B18^2*B10/B9)</f>
-        <v>23.4787137637478</v>
-      </c>
-      <c r="C21" t="s" s="7">
+        <f t="array" ref="B21">B20*B19</f>
+        <v>11.55</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E21" s="4"/>
-      <c r="F21" t="s" s="2">
-        <v>73</v>
-      </c>
+      <c r="D21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -2810,22 +2981,24 @@
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
     </row>
-    <row r="22" ht="14.4" customHeight="1">
-      <c r="A22" t="s" s="5">
-        <v>74</v>
+    <row r="22" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A22" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="B22" s="11" cm="1">
-        <f t="array" ref="B22">SQRT(B25*B3*SQRT(B24^2-1))</f>
-        <v>14.8107484143351</v>
-      </c>
-      <c r="C22" t="s" s="7">
+        <f t="array" ref="B22">SQRT(B19^2*B11/B10)</f>
+        <v>23.478713763747791</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D22" t="s" s="2">
-        <v>75</v>
+      <c r="D22" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+      <c r="F22" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
@@ -2838,23 +3011,21 @@
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
     </row>
-    <row r="23" ht="14.4" customHeight="1">
-      <c r="A23" t="s" s="5">
-        <v>76</v>
+    <row r="23" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A23" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="B23" s="11" cm="1">
-        <f t="array" ref="B23">B18*SQRT(B24)</f>
-        <v>12.8598211496117</v>
-      </c>
-      <c r="C23" t="s" s="7">
+        <f t="array" ref="B23">SQRT(B26*B4*SQRT(B25^2-1))</f>
+        <v>14.810748414335091</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E23" t="s" s="2">
-        <v>78</v>
-      </c>
+      <c r="D23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -2868,21 +3039,22 @@
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
     </row>
-    <row r="24" ht="14.4" customHeight="1">
-      <c r="A24" t="s" s="5">
-        <v>79</v>
-      </c>
-      <c r="B24" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="C24" t="s" s="7">
-        <v>16</v>
-      </c>
-      <c r="D24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>81</v>
+    <row r="24" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A24" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="11" cm="1">
+        <f t="array" ref="B24">B19*SQRT(B25)</f>
+        <v>12.859821149611683</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -2897,21 +3069,21 @@
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
     </row>
-    <row r="25" ht="14.4" customHeight="1">
-      <c r="A25" t="s" s="5">
-        <v>82</v>
+    <row r="25" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A25" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="B25" s="6">
-        <v>20</v>
-      </c>
-      <c r="C25" t="s" s="7">
-        <v>83</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>78</v>
+        <v>1.5</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
@@ -2926,21 +3098,22 @@
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
     </row>
-    <row r="26" ht="14.4" customHeight="1">
-      <c r="A26" t="s" s="5">
-        <v>85</v>
-      </c>
-      <c r="B26" s="11" cm="1">
-        <f t="array" ref="B26">DEGREES(ACOS(1/B24))</f>
-        <v>48.1896851042214</v>
-      </c>
-      <c r="C26" t="s" s="7">
-        <v>86</v>
-      </c>
-      <c r="D26" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="E26" s="4"/>
+    <row r="26" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A26" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="6">
+        <v>20</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -2954,22 +3127,21 @@
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
     </row>
-    <row r="27" ht="14.4" customHeight="1">
-      <c r="A27" t="s" s="5">
-        <v>88</v>
-      </c>
-      <c r="B27" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="C27" t="s" s="7">
-        <v>16</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="E27" t="s" s="2">
-        <v>90</v>
-      </c>
+    <row r="27" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A27" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="11" cm="1">
+        <f t="array" ref="B27">DEGREES(ACOS(1/B25))</f>
+        <v>48.189685104221404</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
@@ -2983,21 +3155,21 @@
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
     </row>
-    <row r="28" ht="14.4" customHeight="1">
-      <c r="A28" t="s" s="5">
-        <v>91</v>
+    <row r="28" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A28" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B28" s="6">
         <v>0.75</v>
       </c>
-      <c r="C28" t="s" s="7">
+      <c r="C28" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D28" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="E28" t="s" s="2">
-        <v>93</v>
+      <c r="D28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -3012,20 +3184,20 @@
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
     </row>
-    <row r="29" ht="14.4" customHeight="1">
-      <c r="A29" t="s" s="5">
-        <v>94</v>
+    <row r="29" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A29" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="B29" s="6">
-        <v>0.45</v>
-      </c>
-      <c r="C29" t="s" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D29" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="E29" t="s" s="2">
+      <c r="D29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>93</v>
       </c>
       <c r="F29" s="4"/>
@@ -3041,21 +3213,21 @@
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
     </row>
-    <row r="30" ht="14.4" customHeight="1">
-      <c r="A30" t="s" s="5">
-        <v>96</v>
+    <row r="30" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A30" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B30" s="6">
-        <v>30</v>
-      </c>
-      <c r="C30" t="s" s="7">
-        <v>83</v>
-      </c>
-      <c r="D30" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="E30" t="s" s="2">
-        <v>98</v>
+        <v>0.45</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
@@ -3070,21 +3242,21 @@
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
     </row>
-    <row r="31" ht="14.4" customHeight="1">
-      <c r="A31" t="s" s="5">
-        <v>99</v>
+    <row r="31" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A31" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="B31" s="6">
-        <v>100</v>
-      </c>
-      <c r="C31" t="s" s="7">
+        <v>30</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D31" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="E31" t="s" s="2">
-        <v>101</v>
+      <c r="D31" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -3099,21 +3271,22 @@
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
     </row>
-    <row r="32" ht="14.4" customHeight="1">
-      <c r="A32" t="s" s="5">
-        <v>102</v>
-      </c>
-      <c r="B32" s="11" cm="1">
-        <f t="array" ref="B32">DEGREES(ATAN(30/100))</f>
-        <v>16.6992442339936</v>
-      </c>
-      <c r="C32" t="s" s="7">
-        <v>86</v>
-      </c>
-      <c r="D32" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="E32" s="4"/>
+    <row r="32" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A32" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="6">
+        <v>100</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>101</v>
+      </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -3127,22 +3300,21 @@
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
-    <row r="33" ht="14.4" customHeight="1">
-      <c r="A33" t="s" s="5">
-        <v>104</v>
-      </c>
-      <c r="B33" s="8">
-        <v>25</v>
-      </c>
-      <c r="C33" t="s" s="7">
-        <v>83</v>
-      </c>
-      <c r="D33" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>106</v>
-      </c>
+    <row r="33" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A33" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="11" cm="1">
+        <f t="array" ref="B33">DEGREES(ATAN(30/100))</f>
+        <v>16.699244233993621</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -3156,20 +3328,22 @@
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
     </row>
-    <row r="34" ht="14.4" customHeight="1">
-      <c r="A34" t="s" s="5">
-        <v>107</v>
-      </c>
-      <c r="B34" s="6">
-        <v>100</v>
-      </c>
-      <c r="C34" t="s" s="7">
-        <v>108</v>
-      </c>
-      <c r="D34" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="E34" s="4"/>
+    <row r="34" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A34" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="8">
+        <v>25</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -3183,18 +3357,18 @@
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
     </row>
-    <row r="35" ht="14.4" customHeight="1">
-      <c r="A35" t="s" s="5">
-        <v>110</v>
+    <row r="35" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A35" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B35" s="6">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="C35" t="s" s="7">
-        <v>111</v>
-      </c>
-      <c r="D35" t="s" s="2">
-        <v>112</v>
+        <v>100</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -3210,18 +3384,18 @@
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
     </row>
-    <row r="36" ht="14.4" customHeight="1">
-      <c r="A36" t="s" s="5">
-        <v>113</v>
-      </c>
-      <c r="B36" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="C36" t="s" s="7">
-        <v>16</v>
-      </c>
-      <c r="D36" t="s" s="2">
-        <v>114</v>
+    <row r="36" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A36" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -3237,11 +3411,19 @@
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" ht="14.4" customHeight="1">
-      <c r="A37" s="4"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
+    <row r="37" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A37" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>114</v>
+      </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
@@ -3256,12 +3438,22 @@
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
     </row>
-    <row r="38" ht="14.4" customHeight="1">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
+    <row r="38" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A38" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="16">
+        <v>4.45</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>127</v>
+      </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
@@ -3275,11 +3467,20 @@
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
     </row>
-    <row r="39" ht="14.4" customHeight="1">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
+    <row r="39" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A39" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B39" s="17">
+        <f>B4*B38</f>
+        <v>43.654500000000006</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
@@ -3294,11 +3495,20 @@
       <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" ht="14.4" customHeight="1">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
+    <row r="40" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A40" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B40" s="18">
+        <f>B39/B35</f>
+        <v>0.43654500000000007</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>126</v>
+      </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
@@ -3313,10 +3523,10 @@
       <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
     </row>
-    <row r="41" ht="14.4" customHeight="1">
-      <c r="A41" s="4"/>
+    <row r="41" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A41" s="19"/>
       <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
+      <c r="C41" s="19"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
@@ -3332,7 +3542,7 @@
       <c r="P41" s="4"/>
       <c r="Q41" s="4"/>
     </row>
-    <row r="42" ht="14.4" customHeight="1">
+    <row r="42" spans="1:17" ht="14.45" customHeight="1">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -3351,7 +3561,7 @@
       <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
     </row>
-    <row r="43" ht="14.4" customHeight="1">
+    <row r="43" spans="1:17" ht="14.45" customHeight="1">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -3370,7 +3580,7 @@
       <c r="P43" s="4"/>
       <c r="Q43" s="4"/>
     </row>
-    <row r="44" ht="14.4" customHeight="1">
+    <row r="44" spans="1:17" ht="14.45" customHeight="1">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -3389,7 +3599,7 @@
       <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
     </row>
-    <row r="45" ht="14.4" customHeight="1">
+    <row r="45" spans="1:17" ht="14.45" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -3408,7 +3618,7 @@
       <c r="P45" s="4"/>
       <c r="Q45" s="4"/>
     </row>
-    <row r="46" ht="14.4" customHeight="1">
+    <row r="46" spans="1:17" ht="14.45" customHeight="1">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -3427,7 +3637,7 @@
       <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
     </row>
-    <row r="47" ht="14.4" customHeight="1">
+    <row r="47" spans="1:17" ht="14.45" customHeight="1">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -3446,7 +3656,7 @@
       <c r="P47" s="4"/>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" ht="14.4" customHeight="1">
+    <row r="48" spans="1:17" ht="14.45" customHeight="1">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -3465,7 +3675,7 @@
       <c r="P48" s="4"/>
       <c r="Q48" s="4"/>
     </row>
-    <row r="49" ht="14.4" customHeight="1">
+    <row r="49" spans="1:17" ht="14.45" customHeight="1">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -3484,7 +3694,7 @@
       <c r="P49" s="4"/>
       <c r="Q49" s="4"/>
     </row>
-    <row r="50" ht="14.4" customHeight="1">
+    <row r="50" spans="1:17" ht="14.45" customHeight="1">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -3503,7 +3713,7 @@
       <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" ht="14.4" customHeight="1">
+    <row r="51" spans="1:17" ht="14.45" customHeight="1">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -3522,7 +3732,7 @@
       <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" ht="14.4" customHeight="1">
+    <row r="52" spans="1:17" ht="14.45" customHeight="1">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -3541,7 +3751,7 @@
       <c r="P52" s="4"/>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" ht="14.4" customHeight="1">
+    <row r="53" spans="1:17" ht="14.45" customHeight="1">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -3560,7 +3770,7 @@
       <c r="P53" s="4"/>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" ht="14.4" customHeight="1">
+    <row r="54" spans="1:17" ht="14.45" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -3579,7 +3789,7 @@
       <c r="P54" s="4"/>
       <c r="Q54" s="4"/>
     </row>
-    <row r="55" ht="14.4" customHeight="1">
+    <row r="55" spans="1:17" ht="14.45" customHeight="1">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -3598,7 +3808,7 @@
       <c r="P55" s="4"/>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" ht="14.4" customHeight="1">
+    <row r="56" spans="1:17" ht="14.45" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -3617,7 +3827,7 @@
       <c r="P56" s="4"/>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" ht="14.4" customHeight="1">
+    <row r="57" spans="1:17" ht="14.45" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3636,7 +3846,7 @@
       <c r="P57" s="4"/>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" ht="14.4" customHeight="1">
+    <row r="58" spans="1:17" ht="14.45" customHeight="1">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -3655,7 +3865,7 @@
       <c r="P58" s="4"/>
       <c r="Q58" s="4"/>
     </row>
-    <row r="59" ht="14.4" customHeight="1">
+    <row r="59" spans="1:17" ht="14.45" customHeight="1">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -3674,7 +3884,7 @@
       <c r="P59" s="4"/>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" ht="14.4" customHeight="1">
+    <row r="60" spans="1:17" ht="14.45" customHeight="1">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -3693,7 +3903,7 @@
       <c r="P60" s="4"/>
       <c r="Q60" s="4"/>
     </row>
-    <row r="61" ht="14.4" customHeight="1">
+    <row r="61" spans="1:17" ht="14.45" customHeight="1">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -3712,7 +3922,7 @@
       <c r="P61" s="4"/>
       <c r="Q61" s="4"/>
     </row>
-    <row r="62" ht="14.4" customHeight="1">
+    <row r="62" spans="1:17" ht="14.45" customHeight="1">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -3731,7 +3941,7 @@
       <c r="P62" s="4"/>
       <c r="Q62" s="4"/>
     </row>
-    <row r="63" ht="14.4" customHeight="1">
+    <row r="63" spans="1:17" ht="14.45" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -3750,7 +3960,7 @@
       <c r="P63" s="4"/>
       <c r="Q63" s="4"/>
     </row>
-    <row r="64" ht="14.4" customHeight="1">
+    <row r="64" spans="1:17" ht="14.45" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -3769,7 +3979,7 @@
       <c r="P64" s="4"/>
       <c r="Q64" s="4"/>
     </row>
-    <row r="65" ht="14.4" customHeight="1">
+    <row r="65" spans="1:17" ht="14.45" customHeight="1">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -3788,7 +3998,7 @@
       <c r="P65" s="4"/>
       <c r="Q65" s="4"/>
     </row>
-    <row r="66" ht="14.4" customHeight="1">
+    <row r="66" spans="1:17" ht="14.45" customHeight="1">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -3807,7 +4017,7 @@
       <c r="P66" s="4"/>
       <c r="Q66" s="4"/>
     </row>
-    <row r="67" ht="14.4" customHeight="1">
+    <row r="67" spans="1:17" ht="14.45" customHeight="1">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -3826,7 +4036,7 @@
       <c r="P67" s="4"/>
       <c r="Q67" s="4"/>
     </row>
-    <row r="68" ht="14.4" customHeight="1">
+    <row r="68" spans="1:17" ht="14.45" customHeight="1">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -3845,7 +4055,7 @@
       <c r="P68" s="4"/>
       <c r="Q68" s="4"/>
     </row>
-    <row r="69" ht="14.4" customHeight="1">
+    <row r="69" spans="1:17" ht="14.45" customHeight="1">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -3864,7 +4074,7 @@
       <c r="P69" s="4"/>
       <c r="Q69" s="4"/>
     </row>
-    <row r="70" ht="14.4" customHeight="1">
+    <row r="70" spans="1:17" ht="14.45" customHeight="1">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -3883,7 +4093,7 @@
       <c r="P70" s="4"/>
       <c r="Q70" s="4"/>
     </row>
-    <row r="71" ht="14.4" customHeight="1">
+    <row r="71" spans="1:17" ht="14.45" customHeight="1">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -3902,7 +4112,7 @@
       <c r="P71" s="4"/>
       <c r="Q71" s="4"/>
     </row>
-    <row r="72" ht="14.4" customHeight="1">
+    <row r="72" spans="1:17" ht="14.45" customHeight="1">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -3921,7 +4131,7 @@
       <c r="P72" s="4"/>
       <c r="Q72" s="4"/>
     </row>
-    <row r="73" ht="14.4" customHeight="1">
+    <row r="73" spans="1:17" ht="14.45" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -3940,7 +4150,7 @@
       <c r="P73" s="4"/>
       <c r="Q73" s="4"/>
     </row>
-    <row r="74" ht="14.4" customHeight="1">
+    <row r="74" spans="1:17" ht="14.45" customHeight="1">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -3959,7 +4169,7 @@
       <c r="P74" s="4"/>
       <c r="Q74" s="4"/>
     </row>
-    <row r="75" ht="14.4" customHeight="1">
+    <row r="75" spans="1:17" ht="14.45" customHeight="1">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -3978,7 +4188,7 @@
       <c r="P75" s="4"/>
       <c r="Q75" s="4"/>
     </row>
-    <row r="76" ht="14.4" customHeight="1">
+    <row r="76" spans="1:17" ht="14.45" customHeight="1">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -3997,7 +4207,7 @@
       <c r="P76" s="4"/>
       <c r="Q76" s="4"/>
     </row>
-    <row r="77" ht="14.4" customHeight="1">
+    <row r="77" spans="1:17" ht="14.45" customHeight="1">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -4016,7 +4226,7 @@
       <c r="P77" s="4"/>
       <c r="Q77" s="4"/>
     </row>
-    <row r="78" ht="14.4" customHeight="1">
+    <row r="78" spans="1:17" ht="14.45" customHeight="1">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -4035,7 +4245,7 @@
       <c r="P78" s="4"/>
       <c r="Q78" s="4"/>
     </row>
-    <row r="79" ht="14.4" customHeight="1">
+    <row r="79" spans="1:17" ht="14.45" customHeight="1">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -4054,7 +4264,7 @@
       <c r="P79" s="4"/>
       <c r="Q79" s="4"/>
     </row>
-    <row r="80" ht="14.4" customHeight="1">
+    <row r="80" spans="1:17" ht="14.45" customHeight="1">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -4073,7 +4283,7 @@
       <c r="P80" s="4"/>
       <c r="Q80" s="4"/>
     </row>
-    <row r="81" ht="14.4" customHeight="1">
+    <row r="81" spans="1:17" ht="14.45" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -4092,7 +4302,7 @@
       <c r="P81" s="4"/>
       <c r="Q81" s="4"/>
     </row>
-    <row r="82" ht="14.4" customHeight="1">
+    <row r="82" spans="1:17" ht="14.45" customHeight="1">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -4111,7 +4321,7 @@
       <c r="P82" s="4"/>
       <c r="Q82" s="4"/>
     </row>
-    <row r="83" ht="14.4" customHeight="1">
+    <row r="83" spans="1:17" ht="14.45" customHeight="1">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -4130,7 +4340,7 @@
       <c r="P83" s="4"/>
       <c r="Q83" s="4"/>
     </row>
-    <row r="84" ht="14.4" customHeight="1">
+    <row r="84" spans="1:17" ht="14.45" customHeight="1">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -4149,7 +4359,7 @@
       <c r="P84" s="4"/>
       <c r="Q84" s="4"/>
     </row>
-    <row r="85" ht="14.4" customHeight="1">
+    <row r="85" spans="1:17" ht="14.45" customHeight="1">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -4168,7 +4378,7 @@
       <c r="P85" s="4"/>
       <c r="Q85" s="4"/>
     </row>
-    <row r="86" ht="14.4" customHeight="1">
+    <row r="86" spans="1:17" ht="14.45" customHeight="1">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -4187,7 +4397,7 @@
       <c r="P86" s="4"/>
       <c r="Q86" s="4"/>
     </row>
-    <row r="87" ht="14.4" customHeight="1">
+    <row r="87" spans="1:17" ht="14.45" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -4206,7 +4416,7 @@
       <c r="P87" s="4"/>
       <c r="Q87" s="4"/>
     </row>
-    <row r="88" ht="14.4" customHeight="1">
+    <row r="88" spans="1:17" ht="14.45" customHeight="1">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -4225,7 +4435,7 @@
       <c r="P88" s="4"/>
       <c r="Q88" s="4"/>
     </row>
-    <row r="89" ht="14.4" customHeight="1">
+    <row r="89" spans="1:17" ht="14.45" customHeight="1">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -4244,7 +4454,7 @@
       <c r="P89" s="4"/>
       <c r="Q89" s="4"/>
     </row>
-    <row r="90" ht="14.4" customHeight="1">
+    <row r="90" spans="1:17" ht="14.45" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -4263,7 +4473,7 @@
       <c r="P90" s="4"/>
       <c r="Q90" s="4"/>
     </row>
-    <row r="91" ht="14.4" customHeight="1">
+    <row r="91" spans="1:17" ht="14.45" customHeight="1">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -4282,7 +4492,7 @@
       <c r="P91" s="4"/>
       <c r="Q91" s="4"/>
     </row>
-    <row r="92" ht="14.4" customHeight="1">
+    <row r="92" spans="1:17" ht="14.45" customHeight="1">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -4301,7 +4511,7 @@
       <c r="P92" s="4"/>
       <c r="Q92" s="4"/>
     </row>
-    <row r="93" ht="14.4" customHeight="1">
+    <row r="93" spans="1:17" ht="14.45" customHeight="1">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -4320,7 +4530,7 @@
       <c r="P93" s="4"/>
       <c r="Q93" s="4"/>
     </row>
-    <row r="94" ht="14.4" customHeight="1">
+    <row r="94" spans="1:17" ht="14.45" customHeight="1">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -4339,7 +4549,7 @@
       <c r="P94" s="4"/>
       <c r="Q94" s="4"/>
     </row>
-    <row r="95" ht="14.4" customHeight="1">
+    <row r="95" spans="1:17" ht="14.45" customHeight="1">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -4358,7 +4568,7 @@
       <c r="P95" s="4"/>
       <c r="Q95" s="4"/>
     </row>
-    <row r="96" ht="14.4" customHeight="1">
+    <row r="96" spans="1:17" ht="14.45" customHeight="1">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -4377,7 +4587,7 @@
       <c r="P96" s="4"/>
       <c r="Q96" s="4"/>
     </row>
-    <row r="97" ht="14.4" customHeight="1">
+    <row r="97" spans="1:17" ht="14.45" customHeight="1">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -4396,7 +4606,7 @@
       <c r="P97" s="4"/>
       <c r="Q97" s="4"/>
     </row>
-    <row r="98" ht="14.4" customHeight="1">
+    <row r="98" spans="1:17" ht="14.45" customHeight="1">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -4415,7 +4625,7 @@
       <c r="P98" s="4"/>
       <c r="Q98" s="4"/>
     </row>
-    <row r="99" ht="14.4" customHeight="1">
+    <row r="99" spans="1:17" ht="14.45" customHeight="1">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -4434,7 +4644,7 @@
       <c r="P99" s="4"/>
       <c r="Q99" s="4"/>
     </row>
-    <row r="100" ht="14.4" customHeight="1">
+    <row r="100" spans="1:17" ht="14.45" customHeight="1">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -4453,7 +4663,7 @@
       <c r="P100" s="4"/>
       <c r="Q100" s="4"/>
     </row>
-    <row r="101" ht="14.4" customHeight="1">
+    <row r="101" spans="1:17" ht="14.45" customHeight="1">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -4472,7 +4682,7 @@
       <c r="P101" s="4"/>
       <c r="Q101" s="4"/>
     </row>
-    <row r="102" ht="14.4" customHeight="1">
+    <row r="102" spans="1:17" ht="14.45" customHeight="1">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -4491,7 +4701,7 @@
       <c r="P102" s="4"/>
       <c r="Q102" s="4"/>
     </row>
-    <row r="103" ht="14.4" customHeight="1">
+    <row r="103" spans="1:17" ht="14.45" customHeight="1">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -4510,7 +4720,7 @@
       <c r="P103" s="4"/>
       <c r="Q103" s="4"/>
     </row>
-    <row r="104" ht="14.4" customHeight="1">
+    <row r="104" spans="1:17" ht="14.45" customHeight="1">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -4529,7 +4739,7 @@
       <c r="P104" s="4"/>
       <c r="Q104" s="4"/>
     </row>
-    <row r="105" ht="14.4" customHeight="1">
+    <row r="105" spans="1:17" ht="14.45" customHeight="1">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -4548,7 +4758,7 @@
       <c r="P105" s="4"/>
       <c r="Q105" s="4"/>
     </row>
-    <row r="106" ht="14.4" customHeight="1">
+    <row r="106" spans="1:17" ht="14.45" customHeight="1">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -4567,7 +4777,7 @@
       <c r="P106" s="4"/>
       <c r="Q106" s="4"/>
     </row>
-    <row r="107" ht="14.4" customHeight="1">
+    <row r="107" spans="1:17" ht="14.45" customHeight="1">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -4586,7 +4796,7 @@
       <c r="P107" s="4"/>
       <c r="Q107" s="4"/>
     </row>
-    <row r="108" ht="14.4" customHeight="1">
+    <row r="108" spans="1:17" ht="14.45" customHeight="1">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -4605,7 +4815,7 @@
       <c r="P108" s="4"/>
       <c r="Q108" s="4"/>
     </row>
-    <row r="109" ht="14.4" customHeight="1">
+    <row r="109" spans="1:17" ht="14.45" customHeight="1">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -4624,7 +4834,7 @@
       <c r="P109" s="4"/>
       <c r="Q109" s="4"/>
     </row>
-    <row r="110" ht="14.4" customHeight="1">
+    <row r="110" spans="1:17" ht="14.45" customHeight="1">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -4643,7 +4853,7 @@
       <c r="P110" s="4"/>
       <c r="Q110" s="4"/>
     </row>
-    <row r="111" ht="14.4" customHeight="1">
+    <row r="111" spans="1:17" ht="14.45" customHeight="1">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -4662,7 +4872,7 @@
       <c r="P111" s="4"/>
       <c r="Q111" s="4"/>
     </row>
-    <row r="112" ht="14.4" customHeight="1">
+    <row r="112" spans="1:17" ht="14.45" customHeight="1">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -4681,7 +4891,7 @@
       <c r="P112" s="4"/>
       <c r="Q112" s="4"/>
     </row>
-    <row r="113" ht="14.4" customHeight="1">
+    <row r="113" spans="1:17" ht="14.45" customHeight="1">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -4700,7 +4910,7 @@
       <c r="P113" s="4"/>
       <c r="Q113" s="4"/>
     </row>
-    <row r="114" ht="14.4" customHeight="1">
+    <row r="114" spans="1:17" ht="14.45" customHeight="1">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -4719,7 +4929,7 @@
       <c r="P114" s="4"/>
       <c r="Q114" s="4"/>
     </row>
-    <row r="115" ht="14.4" customHeight="1">
+    <row r="115" spans="1:17" ht="14.45" customHeight="1">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -4738,7 +4948,7 @@
       <c r="P115" s="4"/>
       <c r="Q115" s="4"/>
     </row>
-    <row r="116" ht="14.4" customHeight="1">
+    <row r="116" spans="1:17" ht="14.45" customHeight="1">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -4757,7 +4967,7 @@
       <c r="P116" s="4"/>
       <c r="Q116" s="4"/>
     </row>
-    <row r="117" ht="14.4" customHeight="1">
+    <row r="117" spans="1:17" ht="14.45" customHeight="1">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -4776,7 +4986,7 @@
       <c r="P117" s="4"/>
       <c r="Q117" s="4"/>
     </row>
-    <row r="118" ht="14.4" customHeight="1">
+    <row r="118" spans="1:17" ht="14.45" customHeight="1">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -4795,7 +5005,7 @@
       <c r="P118" s="4"/>
       <c r="Q118" s="4"/>
     </row>
-    <row r="119" ht="14.4" customHeight="1">
+    <row r="119" spans="1:17" ht="14.45" customHeight="1">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -4814,7 +5024,7 @@
       <c r="P119" s="4"/>
       <c r="Q119" s="4"/>
     </row>
-    <row r="120" ht="14.4" customHeight="1">
+    <row r="120" spans="1:17" ht="14.45" customHeight="1">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -4833,7 +5043,7 @@
       <c r="P120" s="4"/>
       <c r="Q120" s="4"/>
     </row>
-    <row r="121" ht="14.4" customHeight="1">
+    <row r="121" spans="1:17" ht="14.45" customHeight="1">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -4852,7 +5062,7 @@
       <c r="P121" s="4"/>
       <c r="Q121" s="4"/>
     </row>
-    <row r="122" ht="14.4" customHeight="1">
+    <row r="122" spans="1:17" ht="14.45" customHeight="1">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -4871,7 +5081,7 @@
       <c r="P122" s="4"/>
       <c r="Q122" s="4"/>
     </row>
-    <row r="123" ht="14.4" customHeight="1">
+    <row r="123" spans="1:17" ht="14.45" customHeight="1">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -4890,7 +5100,7 @@
       <c r="P123" s="4"/>
       <c r="Q123" s="4"/>
     </row>
-    <row r="124" ht="14.4" customHeight="1">
+    <row r="124" spans="1:17" ht="14.45" customHeight="1">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -4909,7 +5119,7 @@
       <c r="P124" s="4"/>
       <c r="Q124" s="4"/>
     </row>
-    <row r="125" ht="14.4" customHeight="1">
+    <row r="125" spans="1:17" ht="14.45" customHeight="1">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -4928,7 +5138,7 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="4"/>
     </row>
-    <row r="126" ht="14.4" customHeight="1">
+    <row r="126" spans="1:17" ht="14.45" customHeight="1">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -4947,7 +5157,7 @@
       <c r="P126" s="4"/>
       <c r="Q126" s="4"/>
     </row>
-    <row r="127" ht="14.4" customHeight="1">
+    <row r="127" spans="1:17" ht="14.45" customHeight="1">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -4966,7 +5176,7 @@
       <c r="P127" s="4"/>
       <c r="Q127" s="4"/>
     </row>
-    <row r="128" ht="14.4" customHeight="1">
+    <row r="128" spans="1:17" ht="14.45" customHeight="1">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -4985,9 +5195,28 @@
       <c r="P128" s="4"/>
       <c r="Q128" s="4"/>
     </row>
+    <row r="129" spans="1:17" ht="14.45" customHeight="1">
+      <c r="A129" s="4"/>
+      <c r="B129" s="4"/>
+      <c r="C129" s="4"/>
+      <c r="D129" s="4"/>
+      <c r="E129" s="4"/>
+      <c r="F129" s="4"/>
+      <c r="G129" s="4"/>
+      <c r="H129" s="4"/>
+      <c r="I129" s="4"/>
+      <c r="J129" s="4"/>
+      <c r="K129" s="4"/>
+      <c r="L129" s="4"/>
+      <c r="M129" s="4"/>
+      <c r="N129" s="4"/>
+      <c r="O129" s="4"/>
+      <c r="P129" s="4"/>
+      <c r="Q129" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,39 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF1B17B-09B2-4594-99A8-59303D560F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
+    <sheet name="INPUTS" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -55,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="139">
   <si>
     <t>Parameter</t>
   </si>
@@ -90,6 +68,18 @@
     <t>SL air density</t>
   </si>
   <si>
+    <t>visc</t>
+  </si>
+  <si>
+    <t>Pa-s</t>
+  </si>
+  <si>
+    <t>Air viscosity</t>
+  </si>
+  <si>
+    <t>NIST</t>
+  </si>
+  <si>
     <t>g</t>
   </si>
   <si>
@@ -99,9 +89,6 @@
     <t>Gravitational constant</t>
   </si>
   <si>
-    <t>NIST</t>
-  </si>
-  <si>
     <t>mu_TO</t>
   </si>
   <si>
@@ -402,27 +389,21 @@
     <t>Empty Weight Fraction</t>
   </si>
   <si>
-    <t>visc</t>
-  </si>
-  <si>
-    <t>Pa-s</t>
-  </si>
-  <si>
-    <t>Air viscosity</t>
+    <t>MTOM</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>Takeoff mass</t>
+  </si>
+  <si>
+    <t>From weight estimation code</t>
   </si>
   <si>
     <t>MTOW</t>
   </si>
   <si>
-    <t>MTOM</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>Takeoff mass</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
@@ -438,22 +419,63 @@
     <t>Wing area</t>
   </si>
   <si>
-    <t>From weight estimation code</t>
+    <t>CM_0</t>
+  </si>
+  <si>
+    <t>Moment Coefficient</t>
+  </si>
+  <si>
+    <t>XFLR5</t>
+  </si>
+  <si>
+    <t>c_w</t>
+  </si>
+  <si>
+    <t>Chord of wing</t>
+  </si>
+  <si>
+    <t>x_ac</t>
+  </si>
+  <si>
+    <t>Aerodynamic Center of Wing</t>
+  </si>
+  <si>
+    <t>Common Knowledge</t>
+  </si>
+  <si>
+    <t>l_t</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Wing AC to tail AC length</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000E+00"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
+    <numFmt numFmtId="0" formatCode="General"/>
+    <numFmt numFmtId="59" formatCode="0.000E+00"/>
+    <numFmt numFmtId="60" formatCode="0.000"/>
+    <numFmt numFmtId="61" formatCode="0.0"/>
+    <numFmt numFmtId="62" formatCode="0.0000"/>
   </numFmts>
   <fonts count="6">
     <font>
       <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="15"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
@@ -463,34 +485,18 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
       <sz val="11"/>
       <color indexed="14"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Courier"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -513,11 +519,6 @@
       <patternFill patternType="solid">
         <fgColor indexed="15"/>
         <bgColor auto="1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -609,179 +610,161 @@
         <color indexed="11"/>
       </left>
       <right style="thin">
-        <color indexed="11"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
         <color indexed="11"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color indexed="11"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color indexed="11"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="59" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="60" fontId="4" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="60" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="61" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="62" fontId="4" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Calculation" xfId="1" builtinId="22"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFAAAAAA"/>
-      <rgbColor rgb="FF7F7F7F"/>
-      <rgbColor rgb="FF3F3F76"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FFFA7D00"/>
-      <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ffff0000"/>
+      <rgbColor rgb="ff00ff00"/>
+      <rgbColor rgb="ff0000ff"/>
+      <rgbColor rgb="ffffff00"/>
+      <rgbColor rgb="ffff00ff"/>
+      <rgbColor rgb="ff00ffff"/>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="ff7f7f7f"/>
+      <rgbColor rgb="ff3f3f76"/>
+      <rgbColor rgb="ffffcc99"/>
+      <rgbColor rgb="fffa7d00"/>
+      <rgbColor rgb="fff2f2f2"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>28572</xdr:rowOff>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>120643</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>353433</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>91441</xdr:rowOff>
+      <xdr:colOff>429633</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture 1"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1">
+          <a:extLst/>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="542925" y="7709532"/>
-          <a:ext cx="4026909" cy="2806070"/>
+          <a:off x="619125" y="8378818"/>
+          <a:ext cx="4077709" cy="2815597"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -800,37 +783,33 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>540205</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>131984</xdr:rowOff>
+      <xdr:rowOff>131987</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>314597</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>99025</xdr:rowOff>
+      <xdr:rowOff>99030</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="Picture 2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip r:embed="rId2">
+          <a:extLst/>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7398205" y="7264304"/>
-          <a:ext cx="4486093" cy="2527362"/>
+          <a:off x="7449005" y="7472587"/>
+          <a:ext cx="4486093" cy="2536254"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -849,37 +828,33 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>619125</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>171452</xdr:rowOff>
+      <xdr:rowOff>171458</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>434552</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>133356</xdr:rowOff>
+      <xdr:rowOff>133359</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4" name="Picture 3" descr="Picture 3"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip r:embed="rId3">
+          <a:extLst/>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="619125" y="10961372"/>
-          <a:ext cx="4031828" cy="3070865"/>
+          <a:off x="619125" y="11182358"/>
+          <a:ext cx="4082628" cy="3081657"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -898,37 +873,33 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>297995</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>108861</xdr:rowOff>
+      <xdr:rowOff>108868</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>153761</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>778</xdr:rowOff>
+      <xdr:rowOff>775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="5" name="Picture 4" descr="Picture 4"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip r:embed="rId4">
+          <a:extLst/>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7155994" y="12178941"/>
-          <a:ext cx="5240568" cy="3549518"/>
+          <a:off x="7206794" y="12404373"/>
+          <a:ext cx="5240568" cy="3562208"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -947,37 +918,33 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>254451</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>81644</xdr:rowOff>
+      <xdr:rowOff>81649</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>475977</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>60004</xdr:rowOff>
+      <xdr:rowOff>60011</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="6" name="Picture 5" descr="Picture 5"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip r:embed="rId5">
+          <a:extLst/>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7112451" y="10688684"/>
-          <a:ext cx="4933227" cy="1075641"/>
+          <a:off x="7163251" y="10909034"/>
+          <a:ext cx="4933227" cy="1079453"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -996,37 +963,33 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
       <xdr:row>78</xdr:row>
-      <xdr:rowOff>182223</xdr:rowOff>
+      <xdr:rowOff>182225</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>780870</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>21047</xdr:rowOff>
+      <xdr:rowOff>21043</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="7" name="Picture 6" descr="Picture 6"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip r:embed="rId6">
+          <a:extLst/>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="381000" y="14263983"/>
-          <a:ext cx="4616271" cy="1484745"/>
+          <a:off x="381000" y="14496395"/>
+          <a:ext cx="4667071" cy="1490454"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1045,37 +1008,33 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>95262</xdr:rowOff>
+      <xdr:rowOff>95257</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1619250</xdr:colOff>
       <xdr:row>93</xdr:row>
-      <xdr:rowOff>16204</xdr:rowOff>
+      <xdr:rowOff>16197</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="Picture 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="8" name="Picture 7" descr="Picture 7"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip r:embed="rId7">
+          <a:extLst/>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="381000" y="16371582"/>
-          <a:ext cx="5454650" cy="469583"/>
+          <a:off x="381000" y="16611607"/>
+          <a:ext cx="5505450" cy="471486"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1094,37 +1053,33 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>142885</xdr:rowOff>
+      <xdr:rowOff>142880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>244370</xdr:colOff>
       <xdr:row>110</xdr:row>
-      <xdr:rowOff>53903</xdr:rowOff>
+      <xdr:rowOff>53886</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8" descr="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="9" name="Picture 8" descr="Picture 8"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip r:embed="rId8">
+          <a:extLst/>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7635875" y="16236325"/>
-          <a:ext cx="4178196" cy="3751499"/>
+          <a:off x="7686675" y="16475715"/>
+          <a:ext cx="4178196" cy="3764822"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1143,37 +1098,33 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>96</xdr:row>
-      <xdr:rowOff>13</xdr:rowOff>
+      <xdr:rowOff>4</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>57808</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>152837</xdr:rowOff>
+      <xdr:rowOff>152819</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9" descr="Picture 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="10" name="Picture 9" descr="Picture 9"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip r:embed="rId9">
+          <a:extLst/>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="901700" y="17373613"/>
-          <a:ext cx="5341009" cy="2896025"/>
+          <a:off x="901700" y="17617444"/>
+          <a:ext cx="5391809" cy="2905541"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1192,37 +1143,33 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>113</xdr:row>
-      <xdr:rowOff>161942</xdr:rowOff>
+      <xdr:rowOff>161923</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1657350</xdr:colOff>
       <xdr:row>128</xdr:row>
-      <xdr:rowOff>169725</xdr:rowOff>
+      <xdr:rowOff>169696</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10" descr="Picture 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="11" name="Picture 10" descr="Picture 10"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip r:embed="rId10">
+          <a:extLst/>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="949325" y="20644502"/>
-          <a:ext cx="4924425" cy="2750984"/>
+          <a:off x="949325" y="20899118"/>
+          <a:ext cx="4975225" cy="2760499"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1241,37 +1188,33 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
       <xdr:row>116</xdr:row>
-      <xdr:rowOff>57167</xdr:rowOff>
+      <xdr:rowOff>57146</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>15239</xdr:colOff>
       <xdr:row>122</xdr:row>
-      <xdr:rowOff>135756</xdr:rowOff>
+      <xdr:rowOff>135731</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11" descr="Picture 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="12" name="Picture 11" descr="Picture 11"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:blip r:embed="rId11">
+          <a:extLst/>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6470650" y="21088367"/>
-          <a:ext cx="7133590" cy="1175870"/>
+          <a:off x="6521450" y="21344886"/>
+          <a:ext cx="7133590" cy="1179676"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1289,7 +1232,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office Theme">
       <a:dk1>
@@ -1491,7 +1434,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1509,7 +1452,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1538,7 +1481,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1563,7 +1506,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1588,7 +1531,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1613,7 +1556,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1638,7 +1581,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1663,7 +1606,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1688,7 +1631,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1713,7 +1656,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1738,7 +1681,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1751,15 +1694,9 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -1776,7 +1713,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1794,7 +1731,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1819,7 +1756,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1844,7 +1781,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1869,7 +1806,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1894,7 +1831,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1919,7 +1856,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1944,7 +1881,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1969,7 +1906,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1994,7 +1931,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2019,7 +1956,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2032,15 +1969,9 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -2054,7 +1985,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -2072,7 +2003,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2101,7 +2032,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2126,7 +2057,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2151,7 +2082,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2176,7 +2107,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2201,7 +2132,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2226,7 +2157,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2251,7 +2182,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2276,7 +2207,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2301,7 +2232,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2314,53 +2245,46 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:Q129"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="14.45" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="25.85546875" style="1" customWidth="1"/>
-    <col min="6" max="18" width="8.85546875" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="11.8516" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85156" style="1" customWidth="1"/>
+    <col min="4" max="5" width="25.8516" style="1" customWidth="1"/>
+    <col min="6" max="17" width="8.85156" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="14.45" customHeight="1">
+      <c r="A1" t="s" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s" s="3">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s" s="2">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s" s="2">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s" s="2">
         <v>5</v>
       </c>
       <c r="G1" s="4"/>
@@ -2375,23 +2299,23 @@
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
     </row>
-    <row r="2" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A2" s="5" t="s">
+    <row r="2" ht="14.45" customHeight="1">
+      <c r="A2" t="s" s="5">
         <v>6</v>
       </c>
       <c r="B2" s="6">
-        <v>1.2250000000000001</v>
-      </c>
-      <c r="C2" s="7" t="s">
+        <v>1.225</v>
+      </c>
+      <c r="C2" t="s" s="7">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s" s="2">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s" s="2">
         <v>10</v>
       </c>
       <c r="G2" s="4"/>
@@ -2406,20 +2330,20 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
     </row>
-    <row r="3" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A3" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" s="15">
-        <v>1.7960000000000001E-5</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E3" s="2" t="s">
+    <row r="3" ht="14.45" customHeight="1">
+      <c r="A3" t="s" s="5">
+        <v>11</v>
+      </c>
+      <c r="B3" s="8">
+        <v>1.796e-05</v>
+      </c>
+      <c r="C3" t="s" s="7">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s" s="2">
         <v>14</v>
       </c>
       <c r="F3" s="2"/>
@@ -2435,20 +2359,20 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A4" s="5" t="s">
-        <v>11</v>
+    <row r="4" ht="14.45" customHeight="1">
+      <c r="A4" t="s" s="5">
+        <v>15</v>
       </c>
       <c r="B4" s="6">
         <v>9.81</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="C4" t="s" s="7">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>14</v>
       </c>
       <c r="F4" s="4"/>
@@ -2464,24 +2388,24 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A5" s="5" t="s">
-        <v>15</v>
+    <row r="5" ht="14.45" customHeight="1">
+      <c r="A5" t="s" s="5">
+        <v>18</v>
       </c>
       <c r="B5" s="6">
         <v>0.05</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="C5" t="s" s="7">
         <v>19</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>22</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -2495,24 +2419,24 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>20</v>
+    <row r="6" ht="14.45" customHeight="1">
+      <c r="A6" t="s" s="5">
+        <v>23</v>
       </c>
       <c r="B6" s="6">
         <v>0.08</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>22</v>
+      <c r="F6" t="s" s="2">
+        <v>25</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -2526,21 +2450,21 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
     </row>
-    <row r="7" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="8">
+    <row r="7" ht="14.45" customHeight="1">
+      <c r="A7" t="s" s="5">
+        <v>26</v>
+      </c>
+      <c r="B7" s="9">
         <v>0.7</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>25</v>
+      <c r="C7" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>28</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -2555,24 +2479,24 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="8">
+    <row r="8" ht="14.45" customHeight="1">
+      <c r="A8" t="s" s="5">
+        <v>29</v>
+      </c>
+      <c r="B8" s="9">
         <v>5</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>29</v>
+      <c r="C8" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>32</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -2586,22 +2510,22 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="9" cm="1">
+    <row r="9" ht="14.45" customHeight="1">
+      <c r="A9" t="s" s="5">
+        <v>33</v>
+      </c>
+      <c r="B9" s="10" cm="1">
         <f t="array" ref="B9">1/(PI()*B7*B8)</f>
-        <v>9.0945681766797334E-2</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>32</v>
+        <v>0.09094568176679731</v>
+      </c>
+      <c r="C9" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>35</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
@@ -2616,21 +2540,21 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>33</v>
+    <row r="10" ht="14.45" customHeight="1">
+      <c r="A10" t="s" s="5">
+        <v>36</v>
       </c>
       <c r="B10" s="6">
         <v>0.3</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>35</v>
+      <c r="C10" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>38</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -2645,24 +2569,24 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
     </row>
-    <row r="11" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>36</v>
+    <row r="11" ht="14.45" customHeight="1">
+      <c r="A11" t="s" s="5">
+        <v>39</v>
       </c>
       <c r="B11" s="6">
         <v>1.5</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>39</v>
+      <c r="C11" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>42</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -2676,25 +2600,25 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="10" cm="1">
+    <row r="12" ht="14.45" customHeight="1">
+      <c r="A12" t="s" s="5">
+        <v>43</v>
+      </c>
+      <c r="B12" s="11" cm="1">
         <f t="array" ref="B12">B10</f>
         <v>0.3</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>43</v>
+      <c r="C12" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>46</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -2708,25 +2632,25 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
-    <row r="13" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="11" cm="1">
+    <row r="13" ht="14.45" customHeight="1">
+      <c r="A13" t="s" s="5">
+        <v>47</v>
+      </c>
+      <c r="B13" s="12" cm="1">
         <f t="array" ref="B13">B11/B20^2</f>
-        <v>1.2396694214876032</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>47</v>
+        <v>1.2396694214876</v>
+      </c>
+      <c r="C13" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>50</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -2740,24 +2664,24 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="12">
+    <row r="14" ht="14.45" customHeight="1">
+      <c r="A14" t="s" s="5">
+        <v>51</v>
+      </c>
+      <c r="B14" s="13">
         <v>0.04</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>51</v>
+      <c r="C14" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>54</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -2771,22 +2695,22 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
     </row>
-    <row r="15" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A15" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="9" cm="1">
+    <row r="15" ht="14.45" customHeight="1">
+      <c r="A15" t="s" s="5">
+        <v>55</v>
+      </c>
+      <c r="B15" s="10" cm="1">
         <f t="array" ref="B15">B14+B9*B10^2</f>
-        <v>4.8185111359011761E-2</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>54</v>
+        <v>0.0481851113590118</v>
+      </c>
+      <c r="C15" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>57</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -2801,25 +2725,25 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
     </row>
-    <row r="16" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A16" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="9" cm="1">
+    <row r="16" ht="14.45" customHeight="1">
+      <c r="A16" t="s" s="5">
+        <v>58</v>
+      </c>
+      <c r="B16" s="10" cm="1">
         <f t="array" ref="B16">B14+B9*B12^2</f>
-        <v>4.8185111359011761E-2</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>43</v>
+        <v>0.0481851113590118</v>
+      </c>
+      <c r="C16" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>46</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -2833,22 +2757,22 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
     </row>
-    <row r="17" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="9" cm="1">
+    <row r="17" ht="14.45" customHeight="1">
+      <c r="A17" t="s" s="5">
+        <v>61</v>
+      </c>
+      <c r="B17" s="10" cm="1">
         <f t="array" ref="B17">B16-B5*B12</f>
-        <v>3.3185111359011761E-2</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>60</v>
+        <v>0.0331851113590118</v>
+      </c>
+      <c r="C17" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -2863,23 +2787,23 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
     </row>
-    <row r="18" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A18" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="11" cm="1">
+    <row r="18" ht="14.45" customHeight="1">
+      <c r="A18" t="s" s="5">
+        <v>64</v>
+      </c>
+      <c r="B18" s="12" cm="1">
         <f t="array" ref="B18">B10/B15</f>
-        <v>6.2259895544247374</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>62</v>
+        <v>6.22598955442473</v>
+      </c>
+      <c r="C18" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>65</v>
       </c>
       <c r="E18" s="4"/>
-      <c r="F18" s="2" t="s">
-        <v>63</v>
+      <c r="F18" t="s" s="2">
+        <v>66</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -2893,21 +2817,21 @@
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
     </row>
-    <row r="19" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A19" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" s="8">
+    <row r="19" ht="14.45" customHeight="1">
+      <c r="A19" t="s" s="5">
+        <v>67</v>
+      </c>
+      <c r="B19" s="9">
         <v>10.5</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>66</v>
+      <c r="C19" t="s" s="7">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>69</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -2922,21 +2846,21 @@
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
     </row>
-    <row r="20" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A20" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="13">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>35</v>
+    <row r="20" ht="14.45" customHeight="1">
+      <c r="A20" t="s" s="5">
+        <v>70</v>
+      </c>
+      <c r="B20" s="14">
+        <v>1.1</v>
+      </c>
+      <c r="C20" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>38</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
@@ -2951,22 +2875,22 @@
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
     </row>
-    <row r="21" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A21" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="11" cm="1">
+    <row r="21" ht="14.45" customHeight="1">
+      <c r="A21" t="s" s="5">
+        <v>72</v>
+      </c>
+      <c r="B21" s="12" cm="1">
         <f t="array" ref="B21">B20*B19</f>
         <v>11.55</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>35</v>
+      <c r="C21" t="s" s="7">
+        <v>16</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>38</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -2981,23 +2905,23 @@
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
     </row>
-    <row r="22" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="11" cm="1">
+    <row r="22" ht="14.45" customHeight="1">
+      <c r="A22" t="s" s="5">
+        <v>74</v>
+      </c>
+      <c r="B22" s="12" cm="1">
         <f t="array" ref="B22">SQRT(B19^2*B11/B10)</f>
-        <v>23.478713763747791</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>72</v>
+        <v>23.4787137637478</v>
+      </c>
+      <c r="C22" t="s" s="7">
+        <v>16</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>75</v>
       </c>
       <c r="E22" s="4"/>
-      <c r="F22" s="2" t="s">
-        <v>73</v>
+      <c r="F22" t="s" s="2">
+        <v>76</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -3011,19 +2935,19 @@
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
     </row>
-    <row r="23" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A23" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="11" cm="1">
+    <row r="23" ht="14.45" customHeight="1">
+      <c r="A23" t="s" s="5">
+        <v>77</v>
+      </c>
+      <c r="B23" s="12" cm="1">
         <f t="array" ref="B23">SQRT(B26*B4*SQRT(B25^2-1))</f>
-        <v>14.810748414335091</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>75</v>
+        <v>14.8107484143351</v>
+      </c>
+      <c r="C23" t="s" s="7">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>78</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
@@ -3039,22 +2963,22 @@
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
     </row>
-    <row r="24" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A24" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="11" cm="1">
+    <row r="24" ht="14.45" customHeight="1">
+      <c r="A24" t="s" s="5">
+        <v>79</v>
+      </c>
+      <c r="B24" s="12" cm="1">
         <f t="array" ref="B24">B19*SQRT(B25)</f>
-        <v>12.859821149611683</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>78</v>
+        <v>12.8598211496117</v>
+      </c>
+      <c r="C24" t="s" s="7">
+        <v>16</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>81</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -3069,21 +2993,21 @@
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
     </row>
-    <row r="25" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>79</v>
+    <row r="25" ht="14.45" customHeight="1">
+      <c r="A25" t="s" s="5">
+        <v>82</v>
       </c>
       <c r="B25" s="6">
         <v>1.5</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>81</v>
+      <c r="C25" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>84</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
@@ -3098,21 +3022,21 @@
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
     </row>
-    <row r="26" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A26" s="5" t="s">
-        <v>82</v>
+    <row r="26" ht="14.45" customHeight="1">
+      <c r="A26" t="s" s="5">
+        <v>85</v>
       </c>
       <c r="B26" s="6">
         <v>20</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>78</v>
+      <c r="C26" t="s" s="7">
+        <v>86</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>81</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -3127,19 +3051,19 @@
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
     </row>
-    <row r="27" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A27" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B27" s="11" cm="1">
+    <row r="27" ht="14.45" customHeight="1">
+      <c r="A27" t="s" s="5">
+        <v>88</v>
+      </c>
+      <c r="B27" s="12" cm="1">
         <f t="array" ref="B27">DEGREES(ACOS(1/B25))</f>
-        <v>48.189685104221404</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>87</v>
+        <v>48.1896851042214</v>
+      </c>
+      <c r="C27" t="s" s="7">
+        <v>89</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>90</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3155,21 +3079,21 @@
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
     </row>
-    <row r="28" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A28" s="5" t="s">
-        <v>88</v>
+    <row r="28" ht="14.45" customHeight="1">
+      <c r="A28" t="s" s="5">
+        <v>91</v>
       </c>
       <c r="B28" s="6">
         <v>0.75</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>90</v>
+      <c r="C28" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>93</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -3184,21 +3108,21 @@
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
     </row>
-    <row r="29" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A29" s="5" t="s">
-        <v>91</v>
+    <row r="29" ht="14.45" customHeight="1">
+      <c r="A29" t="s" s="5">
+        <v>94</v>
       </c>
       <c r="B29" s="6">
         <v>0.75</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>93</v>
+      <c r="C29" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>96</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -3213,21 +3137,21 @@
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
     </row>
-    <row r="30" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>94</v>
+    <row r="30" ht="14.45" customHeight="1">
+      <c r="A30" t="s" s="5">
+        <v>97</v>
       </c>
       <c r="B30" s="6">
         <v>0.45</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>93</v>
+      <c r="C30" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>96</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
@@ -3242,21 +3166,21 @@
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
     </row>
-    <row r="31" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A31" s="5" t="s">
-        <v>96</v>
+    <row r="31" ht="14.45" customHeight="1">
+      <c r="A31" t="s" s="5">
+        <v>99</v>
       </c>
       <c r="B31" s="6">
         <v>30</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>98</v>
+      <c r="C31" t="s" s="7">
+        <v>86</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>101</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -3271,21 +3195,21 @@
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
     </row>
-    <row r="32" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A32" s="5" t="s">
-        <v>99</v>
+    <row r="32" ht="14.45" customHeight="1">
+      <c r="A32" t="s" s="5">
+        <v>102</v>
       </c>
       <c r="B32" s="6">
         <v>100</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>101</v>
+      <c r="C32" t="s" s="7">
+        <v>86</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>104</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
@@ -3300,19 +3224,19 @@
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
-    <row r="33" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A33" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" s="11" cm="1">
+    <row r="33" ht="14.45" customHeight="1">
+      <c r="A33" t="s" s="5">
+        <v>105</v>
+      </c>
+      <c r="B33" s="12" cm="1">
         <f t="array" ref="B33">DEGREES(ATAN(30/100))</f>
-        <v>16.699244233993621</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>103</v>
+        <v>16.6992442339936</v>
+      </c>
+      <c r="C33" t="s" s="7">
+        <v>89</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>106</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -3328,21 +3252,21 @@
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
     </row>
-    <row r="34" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A34" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B34" s="8">
+    <row r="34" ht="14.45" customHeight="1">
+      <c r="A34" t="s" s="5">
+        <v>107</v>
+      </c>
+      <c r="B34" s="9">
         <v>25</v>
       </c>
-      <c r="C34" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>106</v>
+      <c r="C34" t="s" s="7">
+        <v>86</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>109</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -3357,18 +3281,18 @@
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
     </row>
-    <row r="35" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A35" s="5" t="s">
-        <v>107</v>
+    <row r="35" ht="14.45" customHeight="1">
+      <c r="A35" t="s" s="5">
+        <v>110</v>
       </c>
       <c r="B35" s="6">
         <v>100</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>109</v>
+      <c r="C35" t="s" s="7">
+        <v>111</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>112</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -3384,18 +3308,18 @@
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
     </row>
-    <row r="36" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A36" s="5" t="s">
-        <v>110</v>
+    <row r="36" ht="14.45" customHeight="1">
+      <c r="A36" t="s" s="5">
+        <v>113</v>
       </c>
       <c r="B36" s="6">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>112</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C36" t="s" s="7">
+        <v>114</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>115</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -3411,18 +3335,18 @@
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A37" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37" s="14">
+    <row r="37" ht="14.45" customHeight="1">
+      <c r="A37" t="s" s="5">
+        <v>116</v>
+      </c>
+      <c r="B37" s="6">
         <v>0.8</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>114</v>
+      <c r="C37" t="s" s="7">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>117</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -3438,21 +3362,21 @@
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
     </row>
-    <row r="38" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A38" s="4" t="s">
+    <row r="38" ht="14.45" customHeight="1">
+      <c r="A38" t="s" s="5">
+        <v>118</v>
+      </c>
+      <c r="B38" s="15">
+        <v>4.45</v>
+      </c>
+      <c r="C38" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="B38" s="16">
-        <v>4.45</v>
-      </c>
-      <c r="C38" s="4" t="s">
+      <c r="D38" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="E38" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="E38" s="19" t="s">
-        <v>127</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
@@ -3467,19 +3391,19 @@
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
     </row>
-    <row r="39" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A39" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B39" s="17">
-        <f>B4*B38</f>
-        <v>43.654500000000006</v>
-      </c>
-      <c r="C39" s="4" t="s">
+    <row r="39" ht="14.45" customHeight="1">
+      <c r="A39" t="s" s="5">
         <v>122</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="B39" s="16" cm="1">
+        <f t="array" ref="B39">B4*B38</f>
+        <v>43.6545</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>123</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>124</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -3495,19 +3419,19 @@
       <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A40" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B40" s="18">
-        <f>B39/B35</f>
-        <v>0.43654500000000007</v>
-      </c>
-      <c r="C40" s="4" t="s">
+    <row r="40" ht="14.45" customHeight="1">
+      <c r="A40" t="s" s="5">
         <v>125</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="B40" s="17" cm="1">
+        <f t="array" ref="B40">B39/B35</f>
+        <v>0.436545</v>
+      </c>
+      <c r="C40" t="s" s="2">
         <v>126</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>127</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -3523,12 +3447,22 @@
       <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
     </row>
-    <row r="41" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A41" s="19"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
+    <row r="41" ht="14.45" customHeight="1">
+      <c r="A41" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B41" s="18">
+        <v>-0.08</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
@@ -3542,11 +3476,17 @@
       <c r="P41" s="4"/>
       <c r="Q41" s="4"/>
     </row>
-    <row r="42" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
+    <row r="42" ht="14.45" customHeight="1">
+      <c r="A42" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B42" s="18">
+        <v>0.291</v>
+      </c>
       <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="D42" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -3561,12 +3501,20 @@
       <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
     </row>
-    <row r="43" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
+    <row r="43" ht="14.45" customHeight="1">
+      <c r="A43" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B43" s="18">
+        <v>0.25</v>
+      </c>
       <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
+      <c r="D43" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -3580,11 +3528,19 @@
       <c r="P43" s="4"/>
       <c r="Q43" s="4"/>
     </row>
-    <row r="44" spans="1:17" ht="14.45" customHeight="1">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
+    <row r="44" ht="14.45" customHeight="1">
+      <c r="A44" t="s" s="19">
+        <v>136</v>
+      </c>
+      <c r="B44" s="18">
+        <v>0.55</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
@@ -3599,7 +3555,7 @@
       <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
     </row>
-    <row r="45" spans="1:17" ht="14.45" customHeight="1">
+    <row r="45" ht="14.45" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -3618,7 +3574,7 @@
       <c r="P45" s="4"/>
       <c r="Q45" s="4"/>
     </row>
-    <row r="46" spans="1:17" ht="14.45" customHeight="1">
+    <row r="46" ht="14.45" customHeight="1">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -3637,7 +3593,7 @@
       <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
     </row>
-    <row r="47" spans="1:17" ht="14.45" customHeight="1">
+    <row r="47" ht="14.45" customHeight="1">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -3656,7 +3612,7 @@
       <c r="P47" s="4"/>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" spans="1:17" ht="14.45" customHeight="1">
+    <row r="48" ht="14.45" customHeight="1">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -3675,7 +3631,7 @@
       <c r="P48" s="4"/>
       <c r="Q48" s="4"/>
     </row>
-    <row r="49" spans="1:17" ht="14.45" customHeight="1">
+    <row r="49" ht="14.45" customHeight="1">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -3694,7 +3650,7 @@
       <c r="P49" s="4"/>
       <c r="Q49" s="4"/>
     </row>
-    <row r="50" spans="1:17" ht="14.45" customHeight="1">
+    <row r="50" ht="14.45" customHeight="1">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -3713,7 +3669,7 @@
       <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" spans="1:17" ht="14.45" customHeight="1">
+    <row r="51" ht="14.45" customHeight="1">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -3732,7 +3688,7 @@
       <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" spans="1:17" ht="14.45" customHeight="1">
+    <row r="52" ht="14.45" customHeight="1">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -3751,7 +3707,7 @@
       <c r="P52" s="4"/>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" spans="1:17" ht="14.45" customHeight="1">
+    <row r="53" ht="14.45" customHeight="1">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -3770,7 +3726,7 @@
       <c r="P53" s="4"/>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" spans="1:17" ht="14.45" customHeight="1">
+    <row r="54" ht="14.45" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -3789,7 +3745,7 @@
       <c r="P54" s="4"/>
       <c r="Q54" s="4"/>
     </row>
-    <row r="55" spans="1:17" ht="14.45" customHeight="1">
+    <row r="55" ht="14.45" customHeight="1">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -3808,7 +3764,7 @@
       <c r="P55" s="4"/>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" spans="1:17" ht="14.45" customHeight="1">
+    <row r="56" ht="14.45" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -3827,7 +3783,7 @@
       <c r="P56" s="4"/>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" spans="1:17" ht="14.45" customHeight="1">
+    <row r="57" ht="14.45" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3846,7 +3802,7 @@
       <c r="P57" s="4"/>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" spans="1:17" ht="14.45" customHeight="1">
+    <row r="58" ht="14.45" customHeight="1">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -3865,7 +3821,7 @@
       <c r="P58" s="4"/>
       <c r="Q58" s="4"/>
     </row>
-    <row r="59" spans="1:17" ht="14.45" customHeight="1">
+    <row r="59" ht="14.45" customHeight="1">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -3884,7 +3840,7 @@
       <c r="P59" s="4"/>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" spans="1:17" ht="14.45" customHeight="1">
+    <row r="60" ht="14.45" customHeight="1">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -3903,7 +3859,7 @@
       <c r="P60" s="4"/>
       <c r="Q60" s="4"/>
     </row>
-    <row r="61" spans="1:17" ht="14.45" customHeight="1">
+    <row r="61" ht="14.45" customHeight="1">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -3922,7 +3878,7 @@
       <c r="P61" s="4"/>
       <c r="Q61" s="4"/>
     </row>
-    <row r="62" spans="1:17" ht="14.45" customHeight="1">
+    <row r="62" ht="14.45" customHeight="1">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -3941,7 +3897,7 @@
       <c r="P62" s="4"/>
       <c r="Q62" s="4"/>
     </row>
-    <row r="63" spans="1:17" ht="14.45" customHeight="1">
+    <row r="63" ht="14.45" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -3960,7 +3916,7 @@
       <c r="P63" s="4"/>
       <c r="Q63" s="4"/>
     </row>
-    <row r="64" spans="1:17" ht="14.45" customHeight="1">
+    <row r="64" ht="14.45" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -3979,7 +3935,7 @@
       <c r="P64" s="4"/>
       <c r="Q64" s="4"/>
     </row>
-    <row r="65" spans="1:17" ht="14.45" customHeight="1">
+    <row r="65" ht="14.45" customHeight="1">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -3998,7 +3954,7 @@
       <c r="P65" s="4"/>
       <c r="Q65" s="4"/>
     </row>
-    <row r="66" spans="1:17" ht="14.45" customHeight="1">
+    <row r="66" ht="14.45" customHeight="1">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -4017,7 +3973,7 @@
       <c r="P66" s="4"/>
       <c r="Q66" s="4"/>
     </row>
-    <row r="67" spans="1:17" ht="14.45" customHeight="1">
+    <row r="67" ht="14.45" customHeight="1">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -4036,7 +3992,7 @@
       <c r="P67" s="4"/>
       <c r="Q67" s="4"/>
     </row>
-    <row r="68" spans="1:17" ht="14.45" customHeight="1">
+    <row r="68" ht="14.45" customHeight="1">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -4055,7 +4011,7 @@
       <c r="P68" s="4"/>
       <c r="Q68" s="4"/>
     </row>
-    <row r="69" spans="1:17" ht="14.45" customHeight="1">
+    <row r="69" ht="14.45" customHeight="1">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -4074,7 +4030,7 @@
       <c r="P69" s="4"/>
       <c r="Q69" s="4"/>
     </row>
-    <row r="70" spans="1:17" ht="14.45" customHeight="1">
+    <row r="70" ht="14.45" customHeight="1">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -4093,7 +4049,7 @@
       <c r="P70" s="4"/>
       <c r="Q70" s="4"/>
     </row>
-    <row r="71" spans="1:17" ht="14.45" customHeight="1">
+    <row r="71" ht="14.45" customHeight="1">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -4112,7 +4068,7 @@
       <c r="P71" s="4"/>
       <c r="Q71" s="4"/>
     </row>
-    <row r="72" spans="1:17" ht="14.45" customHeight="1">
+    <row r="72" ht="14.45" customHeight="1">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -4131,7 +4087,7 @@
       <c r="P72" s="4"/>
       <c r="Q72" s="4"/>
     </row>
-    <row r="73" spans="1:17" ht="14.45" customHeight="1">
+    <row r="73" ht="14.45" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -4150,7 +4106,7 @@
       <c r="P73" s="4"/>
       <c r="Q73" s="4"/>
     </row>
-    <row r="74" spans="1:17" ht="14.45" customHeight="1">
+    <row r="74" ht="14.45" customHeight="1">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -4169,7 +4125,7 @@
       <c r="P74" s="4"/>
       <c r="Q74" s="4"/>
     </row>
-    <row r="75" spans="1:17" ht="14.45" customHeight="1">
+    <row r="75" ht="14.45" customHeight="1">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -4188,7 +4144,7 @@
       <c r="P75" s="4"/>
       <c r="Q75" s="4"/>
     </row>
-    <row r="76" spans="1:17" ht="14.45" customHeight="1">
+    <row r="76" ht="14.45" customHeight="1">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -4207,7 +4163,7 @@
       <c r="P76" s="4"/>
       <c r="Q76" s="4"/>
     </row>
-    <row r="77" spans="1:17" ht="14.45" customHeight="1">
+    <row r="77" ht="14.45" customHeight="1">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -4226,7 +4182,7 @@
       <c r="P77" s="4"/>
       <c r="Q77" s="4"/>
     </row>
-    <row r="78" spans="1:17" ht="14.45" customHeight="1">
+    <row r="78" ht="14.45" customHeight="1">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -4245,7 +4201,7 @@
       <c r="P78" s="4"/>
       <c r="Q78" s="4"/>
     </row>
-    <row r="79" spans="1:17" ht="14.45" customHeight="1">
+    <row r="79" ht="14.45" customHeight="1">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -4264,7 +4220,7 @@
       <c r="P79" s="4"/>
       <c r="Q79" s="4"/>
     </row>
-    <row r="80" spans="1:17" ht="14.45" customHeight="1">
+    <row r="80" ht="14.45" customHeight="1">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -4283,7 +4239,7 @@
       <c r="P80" s="4"/>
       <c r="Q80" s="4"/>
     </row>
-    <row r="81" spans="1:17" ht="14.45" customHeight="1">
+    <row r="81" ht="14.45" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -4302,7 +4258,7 @@
       <c r="P81" s="4"/>
       <c r="Q81" s="4"/>
     </row>
-    <row r="82" spans="1:17" ht="14.45" customHeight="1">
+    <row r="82" ht="14.45" customHeight="1">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -4321,7 +4277,7 @@
       <c r="P82" s="4"/>
       <c r="Q82" s="4"/>
     </row>
-    <row r="83" spans="1:17" ht="14.45" customHeight="1">
+    <row r="83" ht="14.45" customHeight="1">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -4340,7 +4296,7 @@
       <c r="P83" s="4"/>
       <c r="Q83" s="4"/>
     </row>
-    <row r="84" spans="1:17" ht="14.45" customHeight="1">
+    <row r="84" ht="14.45" customHeight="1">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -4359,7 +4315,7 @@
       <c r="P84" s="4"/>
       <c r="Q84" s="4"/>
     </row>
-    <row r="85" spans="1:17" ht="14.45" customHeight="1">
+    <row r="85" ht="14.45" customHeight="1">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -4378,7 +4334,7 @@
       <c r="P85" s="4"/>
       <c r="Q85" s="4"/>
     </row>
-    <row r="86" spans="1:17" ht="14.45" customHeight="1">
+    <row r="86" ht="14.45" customHeight="1">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -4397,7 +4353,7 @@
       <c r="P86" s="4"/>
       <c r="Q86" s="4"/>
     </row>
-    <row r="87" spans="1:17" ht="14.45" customHeight="1">
+    <row r="87" ht="14.45" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -4416,7 +4372,7 @@
       <c r="P87" s="4"/>
       <c r="Q87" s="4"/>
     </row>
-    <row r="88" spans="1:17" ht="14.45" customHeight="1">
+    <row r="88" ht="14.45" customHeight="1">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -4435,7 +4391,7 @@
       <c r="P88" s="4"/>
       <c r="Q88" s="4"/>
     </row>
-    <row r="89" spans="1:17" ht="14.45" customHeight="1">
+    <row r="89" ht="14.45" customHeight="1">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -4454,7 +4410,7 @@
       <c r="P89" s="4"/>
       <c r="Q89" s="4"/>
     </row>
-    <row r="90" spans="1:17" ht="14.45" customHeight="1">
+    <row r="90" ht="14.45" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -4473,7 +4429,7 @@
       <c r="P90" s="4"/>
       <c r="Q90" s="4"/>
     </row>
-    <row r="91" spans="1:17" ht="14.45" customHeight="1">
+    <row r="91" ht="14.45" customHeight="1">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -4492,7 +4448,7 @@
       <c r="P91" s="4"/>
       <c r="Q91" s="4"/>
     </row>
-    <row r="92" spans="1:17" ht="14.45" customHeight="1">
+    <row r="92" ht="14.45" customHeight="1">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -4511,7 +4467,7 @@
       <c r="P92" s="4"/>
       <c r="Q92" s="4"/>
     </row>
-    <row r="93" spans="1:17" ht="14.45" customHeight="1">
+    <row r="93" ht="14.45" customHeight="1">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -4530,7 +4486,7 @@
       <c r="P93" s="4"/>
       <c r="Q93" s="4"/>
     </row>
-    <row r="94" spans="1:17" ht="14.45" customHeight="1">
+    <row r="94" ht="14.45" customHeight="1">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -4549,7 +4505,7 @@
       <c r="P94" s="4"/>
       <c r="Q94" s="4"/>
     </row>
-    <row r="95" spans="1:17" ht="14.45" customHeight="1">
+    <row r="95" ht="14.45" customHeight="1">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -4568,7 +4524,7 @@
       <c r="P95" s="4"/>
       <c r="Q95" s="4"/>
     </row>
-    <row r="96" spans="1:17" ht="14.45" customHeight="1">
+    <row r="96" ht="14.45" customHeight="1">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -4587,7 +4543,7 @@
       <c r="P96" s="4"/>
       <c r="Q96" s="4"/>
     </row>
-    <row r="97" spans="1:17" ht="14.45" customHeight="1">
+    <row r="97" ht="14.45" customHeight="1">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -4606,7 +4562,7 @@
       <c r="P97" s="4"/>
       <c r="Q97" s="4"/>
     </row>
-    <row r="98" spans="1:17" ht="14.45" customHeight="1">
+    <row r="98" ht="14.45" customHeight="1">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -4625,7 +4581,7 @@
       <c r="P98" s="4"/>
       <c r="Q98" s="4"/>
     </row>
-    <row r="99" spans="1:17" ht="14.45" customHeight="1">
+    <row r="99" ht="14.45" customHeight="1">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -4644,7 +4600,7 @@
       <c r="P99" s="4"/>
       <c r="Q99" s="4"/>
     </row>
-    <row r="100" spans="1:17" ht="14.45" customHeight="1">
+    <row r="100" ht="14.45" customHeight="1">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -4663,7 +4619,7 @@
       <c r="P100" s="4"/>
       <c r="Q100" s="4"/>
     </row>
-    <row r="101" spans="1:17" ht="14.45" customHeight="1">
+    <row r="101" ht="14.45" customHeight="1">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -4682,7 +4638,7 @@
       <c r="P101" s="4"/>
       <c r="Q101" s="4"/>
     </row>
-    <row r="102" spans="1:17" ht="14.45" customHeight="1">
+    <row r="102" ht="14.45" customHeight="1">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -4701,7 +4657,7 @@
       <c r="P102" s="4"/>
       <c r="Q102" s="4"/>
     </row>
-    <row r="103" spans="1:17" ht="14.45" customHeight="1">
+    <row r="103" ht="14.45" customHeight="1">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -4720,7 +4676,7 @@
       <c r="P103" s="4"/>
       <c r="Q103" s="4"/>
     </row>
-    <row r="104" spans="1:17" ht="14.45" customHeight="1">
+    <row r="104" ht="14.45" customHeight="1">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -4739,7 +4695,7 @@
       <c r="P104" s="4"/>
       <c r="Q104" s="4"/>
     </row>
-    <row r="105" spans="1:17" ht="14.45" customHeight="1">
+    <row r="105" ht="14.45" customHeight="1">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -4758,7 +4714,7 @@
       <c r="P105" s="4"/>
       <c r="Q105" s="4"/>
     </row>
-    <row r="106" spans="1:17" ht="14.45" customHeight="1">
+    <row r="106" ht="14.45" customHeight="1">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -4777,7 +4733,7 @@
       <c r="P106" s="4"/>
       <c r="Q106" s="4"/>
     </row>
-    <row r="107" spans="1:17" ht="14.45" customHeight="1">
+    <row r="107" ht="14.45" customHeight="1">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -4796,7 +4752,7 @@
       <c r="P107" s="4"/>
       <c r="Q107" s="4"/>
     </row>
-    <row r="108" spans="1:17" ht="14.45" customHeight="1">
+    <row r="108" ht="14.45" customHeight="1">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -4815,7 +4771,7 @@
       <c r="P108" s="4"/>
       <c r="Q108" s="4"/>
     </row>
-    <row r="109" spans="1:17" ht="14.45" customHeight="1">
+    <row r="109" ht="14.45" customHeight="1">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -4834,7 +4790,7 @@
       <c r="P109" s="4"/>
       <c r="Q109" s="4"/>
     </row>
-    <row r="110" spans="1:17" ht="14.45" customHeight="1">
+    <row r="110" ht="14.45" customHeight="1">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -4853,7 +4809,7 @@
       <c r="P110" s="4"/>
       <c r="Q110" s="4"/>
     </row>
-    <row r="111" spans="1:17" ht="14.45" customHeight="1">
+    <row r="111" ht="14.45" customHeight="1">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -4872,7 +4828,7 @@
       <c r="P111" s="4"/>
       <c r="Q111" s="4"/>
     </row>
-    <row r="112" spans="1:17" ht="14.45" customHeight="1">
+    <row r="112" ht="14.45" customHeight="1">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -4891,7 +4847,7 @@
       <c r="P112" s="4"/>
       <c r="Q112" s="4"/>
     </row>
-    <row r="113" spans="1:17" ht="14.45" customHeight="1">
+    <row r="113" ht="14.45" customHeight="1">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -4910,7 +4866,7 @@
       <c r="P113" s="4"/>
       <c r="Q113" s="4"/>
     </row>
-    <row r="114" spans="1:17" ht="14.45" customHeight="1">
+    <row r="114" ht="14.45" customHeight="1">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -4929,7 +4885,7 @@
       <c r="P114" s="4"/>
       <c r="Q114" s="4"/>
     </row>
-    <row r="115" spans="1:17" ht="14.45" customHeight="1">
+    <row r="115" ht="14.45" customHeight="1">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -4948,7 +4904,7 @@
       <c r="P115" s="4"/>
       <c r="Q115" s="4"/>
     </row>
-    <row r="116" spans="1:17" ht="14.45" customHeight="1">
+    <row r="116" ht="14.45" customHeight="1">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -4967,7 +4923,7 @@
       <c r="P116" s="4"/>
       <c r="Q116" s="4"/>
     </row>
-    <row r="117" spans="1:17" ht="14.45" customHeight="1">
+    <row r="117" ht="14.45" customHeight="1">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -4986,7 +4942,7 @@
       <c r="P117" s="4"/>
       <c r="Q117" s="4"/>
     </row>
-    <row r="118" spans="1:17" ht="14.45" customHeight="1">
+    <row r="118" ht="14.45" customHeight="1">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -5005,7 +4961,7 @@
       <c r="P118" s="4"/>
       <c r="Q118" s="4"/>
     </row>
-    <row r="119" spans="1:17" ht="14.45" customHeight="1">
+    <row r="119" ht="14.45" customHeight="1">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -5024,7 +4980,7 @@
       <c r="P119" s="4"/>
       <c r="Q119" s="4"/>
     </row>
-    <row r="120" spans="1:17" ht="14.45" customHeight="1">
+    <row r="120" ht="14.45" customHeight="1">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -5043,7 +4999,7 @@
       <c r="P120" s="4"/>
       <c r="Q120" s="4"/>
     </row>
-    <row r="121" spans="1:17" ht="14.45" customHeight="1">
+    <row r="121" ht="14.45" customHeight="1">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -5062,7 +5018,7 @@
       <c r="P121" s="4"/>
       <c r="Q121" s="4"/>
     </row>
-    <row r="122" spans="1:17" ht="14.45" customHeight="1">
+    <row r="122" ht="14.45" customHeight="1">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -5081,7 +5037,7 @@
       <c r="P122" s="4"/>
       <c r="Q122" s="4"/>
     </row>
-    <row r="123" spans="1:17" ht="14.45" customHeight="1">
+    <row r="123" ht="14.45" customHeight="1">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -5100,7 +5056,7 @@
       <c r="P123" s="4"/>
       <c r="Q123" s="4"/>
     </row>
-    <row r="124" spans="1:17" ht="14.45" customHeight="1">
+    <row r="124" ht="14.45" customHeight="1">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -5119,7 +5075,7 @@
       <c r="P124" s="4"/>
       <c r="Q124" s="4"/>
     </row>
-    <row r="125" spans="1:17" ht="14.45" customHeight="1">
+    <row r="125" ht="14.45" customHeight="1">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -5138,7 +5094,7 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="4"/>
     </row>
-    <row r="126" spans="1:17" ht="14.45" customHeight="1">
+    <row r="126" ht="14.45" customHeight="1">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -5157,7 +5113,7 @@
       <c r="P126" s="4"/>
       <c r="Q126" s="4"/>
     </row>
-    <row r="127" spans="1:17" ht="14.45" customHeight="1">
+    <row r="127" ht="14.45" customHeight="1">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -5176,7 +5132,7 @@
       <c r="P127" s="4"/>
       <c r="Q127" s="4"/>
     </row>
-    <row r="128" spans="1:17" ht="14.45" customHeight="1">
+    <row r="128" ht="14.45" customHeight="1">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -5195,7 +5151,7 @@
       <c r="P128" s="4"/>
       <c r="Q128" s="4"/>
     </row>
-    <row r="129" spans="1:17" ht="14.45" customHeight="1">
+    <row r="129" ht="14.45" customHeight="1">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -5216,7 +5172,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="144">
   <si>
     <t>Parameter</t>
   </si>
@@ -450,6 +450,21 @@
   </si>
   <si>
     <t>Wing AC to tail AC length</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Elevator Chord Fraction</t>
+  </si>
+  <si>
+    <t>Standard Value</t>
+  </si>
+  <si>
+    <t>CL_0</t>
+  </si>
+  <si>
+    <t>Lift at zero AoA</t>
   </si>
 </sst>
 </file>
@@ -735,16 +750,16 @@
 <xdr:wsDr xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>120643</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>429633</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>39108</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>62871</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -763,8 +778,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="619125" y="8378818"/>
-          <a:ext cx="4077709" cy="2815597"/>
+          <a:off x="8928100" y="4037329"/>
+          <a:ext cx="4077709" cy="2815598"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2574,7 +2589,7 @@
         <v>39</v>
       </c>
       <c r="B11" s="6">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="C11" t="s" s="7">
         <v>19</v>
@@ -2638,7 +2653,7 @@
       </c>
       <c r="B13" s="12" cm="1">
         <f t="array" ref="B13">B11/B20^2</f>
-        <v>1.2396694214876</v>
+        <v>1.18181818181818</v>
       </c>
       <c r="C13" t="s" s="7">
         <v>19</v>
@@ -2911,7 +2926,7 @@
       </c>
       <c r="B22" s="12" cm="1">
         <f t="array" ref="B22">SQRT(B19^2*B11/B10)</f>
-        <v>23.4787137637478</v>
+        <v>22.9243320513379</v>
       </c>
       <c r="C22" t="s" s="7">
         <v>16</v>
@@ -3556,11 +3571,21 @@
       <c r="Q44" s="4"/>
     </row>
     <row r="45" ht="14.45" customHeight="1">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
+      <c r="A45" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B45" s="18">
+        <v>0.3</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
@@ -3575,11 +3600,21 @@
       <c r="Q45" s="4"/>
     </row>
     <row r="46" ht="14.45" customHeight="1">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
+      <c r="A46" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B46" s="18">
+        <v>0.43</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="147">
   <si>
     <t>Parameter</t>
   </si>
@@ -465,6 +465,15 @@
   </si>
   <si>
     <t>Lift at zero AoA</t>
+  </si>
+  <si>
+    <t>c_t</t>
+  </si>
+  <si>
+    <t>Chord of the tail</t>
+  </si>
+  <si>
+    <t>Made up, need real val</t>
   </si>
 </sst>
 </file>
@@ -3629,11 +3638,21 @@
       <c r="Q46" s="4"/>
     </row>
     <row r="47" ht="14.45" customHeight="1">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
+      <c r="A47" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B47" s="18">
+        <v>0.12</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="150">
   <si>
     <t>Parameter</t>
   </si>
@@ -474,6 +474,15 @@
   </si>
   <si>
     <t>Made up, need real val</t>
+  </si>
+  <si>
+    <t>AR_tail</t>
+  </si>
+  <si>
+    <t>Aspect Ratio of the tail</t>
+  </si>
+  <si>
+    <t>Smaller than wing to delay stall</t>
   </si>
 </sst>
 </file>
@@ -3584,7 +3593,7 @@
         <v>139</v>
       </c>
       <c r="B45" s="18">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>19</v>
@@ -3667,11 +3676,21 @@
       <c r="Q47" s="4"/>
     </row>
     <row r="48" ht="14.45" customHeight="1">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
+      <c r="A48" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B48" s="18">
+        <v>2.75</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -770,14 +770,14 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>183515</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>39108</xdr:colOff>
+      <xdr:colOff>39107</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>62871</xdr:rowOff>
+      <xdr:rowOff>62873</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -796,8 +796,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8928100" y="4037329"/>
-          <a:ext cx="4077709" cy="2815598"/>
+          <a:off x="8928100" y="4037330"/>
+          <a:ext cx="4077708" cy="2815599"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -816,13 +816,13 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>540205</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>131987</xdr:rowOff>
+      <xdr:rowOff>131990</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>314597</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>99030</xdr:rowOff>
+      <xdr:rowOff>99034</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -841,8 +841,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7449005" y="7472587"/>
-          <a:ext cx="4486093" cy="2536254"/>
+          <a:off x="7449005" y="7472590"/>
+          <a:ext cx="4486093" cy="2536255"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -861,13 +861,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>619125</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>171458</xdr:rowOff>
+      <xdr:rowOff>171463</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>434552</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>133359</xdr:rowOff>
+      <xdr:rowOff>133362</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -886,8 +886,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="619125" y="11182358"/>
-          <a:ext cx="4082628" cy="3081657"/>
+          <a:off x="619125" y="11182363"/>
+          <a:ext cx="4082628" cy="3081655"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -906,13 +906,13 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>297995</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>108868</xdr:rowOff>
+      <xdr:rowOff>108875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>153761</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>775</xdr:rowOff>
+      <xdr:rowOff>772</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -931,8 +931,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7206794" y="12404373"/>
-          <a:ext cx="5240568" cy="3562208"/>
+          <a:off x="7206794" y="12404380"/>
+          <a:ext cx="5240568" cy="3562198"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -951,13 +951,13 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>254451</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>81649</xdr:rowOff>
+      <xdr:rowOff>81655</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>475977</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>60011</xdr:rowOff>
+      <xdr:rowOff>60018</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -976,8 +976,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7163251" y="10909034"/>
-          <a:ext cx="4933227" cy="1079453"/>
+          <a:off x="7163251" y="10909040"/>
+          <a:ext cx="4933227" cy="1079454"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -996,13 +996,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
       <xdr:row>78</xdr:row>
-      <xdr:rowOff>182225</xdr:rowOff>
+      <xdr:rowOff>182227</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>780870</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>21043</xdr:rowOff>
+      <xdr:rowOff>21040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1021,8 +1021,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="381000" y="14496395"/>
-          <a:ext cx="4667071" cy="1490454"/>
+          <a:off x="381000" y="14496397"/>
+          <a:ext cx="4667071" cy="1490449"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1041,13 +1041,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>95257</xdr:rowOff>
+      <xdr:rowOff>95253</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1619250</xdr:colOff>
       <xdr:row>93</xdr:row>
-      <xdr:rowOff>16197</xdr:rowOff>
+      <xdr:rowOff>16190</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1066,8 +1066,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="381000" y="16611607"/>
-          <a:ext cx="5505450" cy="471486"/>
+          <a:off x="381000" y="16611603"/>
+          <a:ext cx="5505450" cy="471483"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1086,13 +1086,13 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>142880</xdr:rowOff>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>244370</xdr:colOff>
       <xdr:row>110</xdr:row>
-      <xdr:rowOff>53886</xdr:rowOff>
+      <xdr:rowOff>53869</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1111,8 +1111,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7686675" y="16475715"/>
-          <a:ext cx="4178196" cy="3764822"/>
+          <a:off x="7686675" y="16475710"/>
+          <a:ext cx="4178196" cy="3764810"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1130,14 +1130,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>4</xdr:rowOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>183511</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>57808</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>152819</xdr:rowOff>
+      <xdr:rowOff>152800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1156,8 +1156,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="901700" y="17617444"/>
-          <a:ext cx="5391809" cy="2905541"/>
+          <a:off x="901700" y="17617436"/>
+          <a:ext cx="5391809" cy="2905530"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1176,13 +1176,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>113</xdr:row>
-      <xdr:rowOff>161923</xdr:rowOff>
+      <xdr:rowOff>161904</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1657350</xdr:colOff>
       <xdr:row>128</xdr:row>
-      <xdr:rowOff>169696</xdr:rowOff>
+      <xdr:rowOff>169668</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1201,8 +1201,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="949325" y="20899118"/>
-          <a:ext cx="4975225" cy="2760499"/>
+          <a:off x="949325" y="20899099"/>
+          <a:ext cx="4975225" cy="2760490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1221,13 +1221,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
       <xdr:row>116</xdr:row>
-      <xdr:rowOff>57146</xdr:rowOff>
+      <xdr:rowOff>57124</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>15239</xdr:colOff>
       <xdr:row>122</xdr:row>
-      <xdr:rowOff>135731</xdr:rowOff>
+      <xdr:rowOff>135706</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1246,8 +1246,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6521450" y="21344886"/>
-          <a:ext cx="7133590" cy="1179676"/>
+          <a:off x="6521450" y="21344864"/>
+          <a:ext cx="7133590" cy="1179673"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3566,7 +3566,7 @@
         <v>136</v>
       </c>
       <c r="B44" s="18">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>137</v>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -419,10 +419,10 @@
     <t>Wing area</t>
   </si>
   <si>
-    <t>CM_0</t>
-  </si>
-  <si>
-    <t>Moment Coefficient</t>
+    <t>CM_ac_w</t>
+  </si>
+  <si>
+    <t>Moment Coefficient at AC, wing</t>
   </si>
   <si>
     <t>XFLR5</t>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,17 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hudson/Documents/GitHub/451-DBF-Team01/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB30DBF-D90C-D04A-9CE1-D2D257DE167B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="INPUTS" sheetId="1" r:id="rId5"/>
+    <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -33,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="153">
   <si>
     <t>Parameter</t>
   </si>
@@ -200,9 +222,6 @@
     <t>Home-built/GA, fixed gear, same for TO (no flaps)</t>
   </si>
   <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>CD at cruise</t>
   </si>
   <si>
@@ -419,96 +438,97 @@
     <t>Wing area</t>
   </si>
   <si>
+    <t>Moment Coefficient</t>
+  </si>
+  <si>
+    <t>XFLR5</t>
+  </si>
+  <si>
+    <t>c_w</t>
+  </si>
+  <si>
+    <t>Chord of wing</t>
+  </si>
+  <si>
+    <t>x_ac</t>
+  </si>
+  <si>
+    <t>Aerodynamic Center of Wing</t>
+  </si>
+  <si>
+    <t>Common Knowledge</t>
+  </si>
+  <si>
+    <t>l_t</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Wing AC to tail AC length</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Elevator Chord Fraction</t>
+  </si>
+  <si>
+    <t>Standard Value</t>
+  </si>
+  <si>
+    <t>CL_0</t>
+  </si>
+  <si>
+    <t>Lift at zero AoA</t>
+  </si>
+  <si>
+    <t>c_t</t>
+  </si>
+  <si>
+    <t>Chord of the tail</t>
+  </si>
+  <si>
+    <t>Made up, need real val</t>
+  </si>
+  <si>
+    <t>AR_tail</t>
+  </si>
+  <si>
+    <t>Aspect Ratio of the tail</t>
+  </si>
+  <si>
+    <t>Smaller than wing to delay stall</t>
+  </si>
+  <si>
+    <t>e_t</t>
+  </si>
+  <si>
+    <t>Oswald span efficiency, tail</t>
+  </si>
+  <si>
+    <t>Need to Justify</t>
+  </si>
+  <si>
+    <t>CD_cruise</t>
+  </si>
+  <si>
     <t>CM_ac_w</t>
-  </si>
-  <si>
-    <t>Moment Coefficient at AC, wing</t>
-  </si>
-  <si>
-    <t>XFLR5</t>
-  </si>
-  <si>
-    <t>c_w</t>
-  </si>
-  <si>
-    <t>Chord of wing</t>
-  </si>
-  <si>
-    <t>x_ac</t>
-  </si>
-  <si>
-    <t>Aerodynamic Center of Wing</t>
-  </si>
-  <si>
-    <t>Common Knowledge</t>
-  </si>
-  <si>
-    <t>l_t</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>Wing AC to tail AC length</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>Elevator Chord Fraction</t>
-  </si>
-  <si>
-    <t>Standard Value</t>
-  </si>
-  <si>
-    <t>CL_0</t>
-  </si>
-  <si>
-    <t>Lift at zero AoA</t>
-  </si>
-  <si>
-    <t>c_t</t>
-  </si>
-  <si>
-    <t>Chord of the tail</t>
-  </si>
-  <si>
-    <t>Made up, need real val</t>
-  </si>
-  <si>
-    <t>AR_tail</t>
-  </si>
-  <si>
-    <t>Aspect Ratio of the tail</t>
-  </si>
-  <si>
-    <t>Smaller than wing to delay stall</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="59" formatCode="0.000E+00"/>
-    <numFmt numFmtId="60" formatCode="0.000"/>
-    <numFmt numFmtId="61" formatCode="0.0"/>
-    <numFmt numFmtId="62" formatCode="0.0000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.000E+00"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
@@ -516,17 +536,20 @@
       <sz val="11"/>
       <color indexed="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="11"/>
       <color indexed="14"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color indexed="8"/>
-      <name val="Courier"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -670,71 +693,31 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="59" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="60" fontId="4" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="60" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="61" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="62" fontId="4" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -743,61 +726,121 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ff7f7f7f"/>
-      <rgbColor rgb="ff3f3f76"/>
-      <rgbColor rgb="ffffcc99"/>
-      <rgbColor rgb="fffa7d00"/>
-      <rgbColor rgb="fff2f2f2"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="FF7F7F7F"/>
+      <rgbColor rgb="FF3F3F76"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFA7D00"/>
+      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>183515</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>39107</xdr:colOff>
+      <xdr:colOff>39108</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>62873</xdr:rowOff>
+      <xdr:rowOff>62871</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8928100" y="4037330"/>
-          <a:ext cx="4077708" cy="2815599"/>
+          <a:off x="8928100" y="4037329"/>
+          <a:ext cx="4077709" cy="2815598"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -816,33 +859,37 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>540205</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>131990</xdr:rowOff>
+      <xdr:rowOff>131987</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>314597</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>99034</xdr:rowOff>
+      <xdr:rowOff>99030</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="Picture 2"/>
+        <xdr:cNvPr id="3" name="Picture 2" descr="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7449005" y="7472590"/>
-          <a:ext cx="4486093" cy="2536255"/>
+          <a:off x="7449005" y="7472587"/>
+          <a:ext cx="4486093" cy="2536254"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -861,33 +908,37 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>619125</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>171463</xdr:rowOff>
+      <xdr:rowOff>171458</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>434552</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>133362</xdr:rowOff>
+      <xdr:rowOff>133359</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3" descr="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="619125" y="11182363"/>
-          <a:ext cx="4082628" cy="3081655"/>
+          <a:off x="619125" y="11182358"/>
+          <a:ext cx="4082628" cy="3081657"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -906,33 +957,37 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>297995</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>108875</xdr:rowOff>
+      <xdr:rowOff>108868</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>153761</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>772</xdr:rowOff>
+      <xdr:rowOff>775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4" descr="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7206794" y="12404380"/>
-          <a:ext cx="5240568" cy="3562198"/>
+          <a:off x="7206794" y="12404373"/>
+          <a:ext cx="5240568" cy="3562208"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -951,33 +1006,37 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>254451</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>81655</xdr:rowOff>
+      <xdr:rowOff>81649</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>475977</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>60018</xdr:rowOff>
+      <xdr:rowOff>60011</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5" descr="Picture 5"/>
+        <xdr:cNvPr id="6" name="Picture 5" descr="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId5">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7163251" y="10909040"/>
-          <a:ext cx="4933227" cy="1079454"/>
+          <a:off x="7163251" y="10909034"/>
+          <a:ext cx="4933227" cy="1079453"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -996,33 +1055,37 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
       <xdr:row>78</xdr:row>
-      <xdr:rowOff>182227</xdr:rowOff>
+      <xdr:rowOff>182225</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>780870</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>21040</xdr:rowOff>
+      <xdr:rowOff>21043</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6" descr="Picture 6"/>
+        <xdr:cNvPr id="7" name="Picture 6" descr="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId6">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="381000" y="14496397"/>
-          <a:ext cx="4667071" cy="1490449"/>
+          <a:off x="381000" y="14496395"/>
+          <a:ext cx="4667071" cy="1490454"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1041,33 +1104,37 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>95253</xdr:rowOff>
+      <xdr:rowOff>95257</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1619250</xdr:colOff>
       <xdr:row>93</xdr:row>
-      <xdr:rowOff>16190</xdr:rowOff>
+      <xdr:rowOff>16197</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="Picture 7"/>
+        <xdr:cNvPr id="8" name="Picture 7" descr="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId7">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="381000" y="16611603"/>
-          <a:ext cx="5505450" cy="471483"/>
+          <a:off x="381000" y="16611607"/>
+          <a:ext cx="5505450" cy="471486"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1086,33 +1153,37 @@
       <xdr:col>7</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>142880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>244370</xdr:colOff>
       <xdr:row>110</xdr:row>
-      <xdr:rowOff>53869</xdr:rowOff>
+      <xdr:rowOff>53886</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8" descr="Picture 8"/>
+        <xdr:cNvPr id="9" name="Picture 8" descr="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId8">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7686675" y="16475710"/>
-          <a:ext cx="4178196" cy="3764810"/>
+          <a:off x="7686675" y="16475715"/>
+          <a:ext cx="4178196" cy="3764822"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1130,34 +1201,38 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>183511</xdr:rowOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>4</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>57808</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>152800</xdr:rowOff>
+      <xdr:rowOff>152819</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9" descr="Picture 9"/>
+        <xdr:cNvPr id="10" name="Picture 9" descr="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId9">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="901700" y="17617436"/>
-          <a:ext cx="5391809" cy="2905530"/>
+          <a:off x="901700" y="17617444"/>
+          <a:ext cx="5391809" cy="2905541"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1176,33 +1251,37 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>113</xdr:row>
-      <xdr:rowOff>161904</xdr:rowOff>
+      <xdr:rowOff>161923</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1657350</xdr:colOff>
       <xdr:row>128</xdr:row>
-      <xdr:rowOff>169668</xdr:rowOff>
+      <xdr:rowOff>169696</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10" descr="Picture 10"/>
+        <xdr:cNvPr id="11" name="Picture 10" descr="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId10">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="949325" y="20899099"/>
-          <a:ext cx="4975225" cy="2760490"/>
+          <a:off x="949325" y="20899118"/>
+          <a:ext cx="4975225" cy="2760499"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1221,33 +1300,37 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
       <xdr:row>116</xdr:row>
-      <xdr:rowOff>57124</xdr:rowOff>
+      <xdr:rowOff>57146</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>15239</xdr:colOff>
       <xdr:row>122</xdr:row>
-      <xdr:rowOff>135706</xdr:rowOff>
+      <xdr:rowOff>135731</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11" descr="Picture 11"/>
+        <xdr:cNvPr id="12" name="Picture 11" descr="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId11">
-          <a:extLst/>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6521450" y="21344864"/>
-          <a:ext cx="7133590" cy="1179673"/>
+          <a:off x="6521450" y="21344886"/>
+          <a:ext cx="7133590" cy="1179676"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1265,7 +1348,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office Theme">
       <a:dk1>
@@ -1467,7 +1550,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1485,7 +1568,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1514,7 +1597,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1539,7 +1622,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1564,7 +1647,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1589,7 +1672,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1614,7 +1697,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1639,7 +1722,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1664,7 +1747,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1689,7 +1772,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1714,7 +1797,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1727,9 +1810,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -1746,7 +1835,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1764,7 +1853,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1789,7 +1878,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1814,7 +1903,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1839,7 +1928,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1864,7 +1953,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1889,7 +1978,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1914,7 +2003,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1939,7 +2028,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1964,7 +2053,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1989,7 +2078,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2002,9 +2091,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -2018,7 +2113,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -2036,7 +2131,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2065,7 +2160,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2090,7 +2185,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2115,7 +2210,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2140,7 +2235,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2165,7 +2260,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2190,7 +2285,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2215,7 +2310,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2240,7 +2335,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2265,7 +2360,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -2278,46 +2373,53 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q129"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="14.45" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.8516" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85156" style="1" customWidth="1"/>
-    <col min="4" max="5" width="25.8516" style="1" customWidth="1"/>
-    <col min="6" max="17" width="8.85156" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.85156" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="25.83203125" style="1" customWidth="1"/>
+    <col min="6" max="18" width="8.83203125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.45" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="3">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="2">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="2">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="2">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="2">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4"/>
@@ -2332,23 +2434,23 @@
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
     </row>
-    <row r="2" ht="14.45" customHeight="1">
-      <c r="A2" t="s" s="5">
+    <row r="2" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="6">
-        <v>1.225</v>
-      </c>
-      <c r="C2" t="s" s="7">
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="2">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s" s="2">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s" s="2">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="4"/>
@@ -2363,20 +2465,20 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
     </row>
-    <row r="3" ht="14.45" customHeight="1">
-      <c r="A3" t="s" s="5">
+    <row r="3" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="8">
-        <v>1.796e-05</v>
-      </c>
-      <c r="C3" t="s" s="7">
+        <v>1.7960000000000001E-5</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s" s="2">
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s" s="2">
+      <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="2"/>
@@ -2392,20 +2494,20 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" ht="14.45" customHeight="1">
-      <c r="A4" t="s" s="5">
+    <row r="4" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="6">
         <v>9.81</v>
       </c>
-      <c r="C4" t="s" s="7">
+      <c r="C4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s" s="2">
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s" s="2">
+      <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="4"/>
@@ -2421,23 +2523,23 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
     </row>
-    <row r="5" ht="14.45" customHeight="1">
-      <c r="A5" t="s" s="5">
+    <row r="5" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="6">
         <v>0.05</v>
       </c>
-      <c r="C5" t="s" s="7">
+      <c r="C5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s" s="2">
+      <c r="D5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E5" t="s" s="2">
+      <c r="E5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F5" t="s" s="2">
+      <c r="F5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="4"/>
@@ -2452,23 +2554,23 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" ht="14.45" customHeight="1">
-      <c r="A6" t="s" s="5">
+    <row r="6" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="6">
         <v>0.08</v>
       </c>
-      <c r="C6" t="s" s="7">
+      <c r="C6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D6" t="s" s="2">
+      <c r="D6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E6" t="s" s="2">
+      <c r="E6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F6" t="s" s="2">
+      <c r="F6" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G6" s="4"/>
@@ -2483,20 +2585,20 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
     </row>
-    <row r="7" ht="14.45" customHeight="1">
-      <c r="A7" t="s" s="5">
+    <row r="7" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="9">
         <v>0.7</v>
       </c>
-      <c r="C7" t="s" s="7">
+      <c r="C7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s" s="2">
+      <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E7" t="s" s="2">
+      <c r="E7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="F7" s="4"/>
@@ -2512,23 +2614,23 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" ht="14.45" customHeight="1">
-      <c r="A8" t="s" s="5">
+    <row r="8" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B8" s="9">
         <v>5</v>
       </c>
-      <c r="C8" t="s" s="7">
+      <c r="C8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s" s="2">
+      <c r="D8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E8" t="s" s="2">
+      <c r="E8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F8" t="s" s="2">
+      <c r="F8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G8" s="4"/>
@@ -2543,21 +2645,21 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" ht="14.45" customHeight="1">
-      <c r="A9" t="s" s="5">
+    <row r="9" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="10" cm="1">
         <f t="array" ref="B9">1/(PI()*B7*B8)</f>
-        <v>0.09094568176679731</v>
-      </c>
-      <c r="C9" t="s" s="7">
+        <v>9.0945681766797334E-2</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D9" t="s" s="2">
+      <c r="D9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E9" t="s" s="2">
+      <c r="E9" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F9" s="4"/>
@@ -2573,20 +2675,20 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" ht="14.45" customHeight="1">
-      <c r="A10" t="s" s="5">
+    <row r="10" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B10" s="6">
         <v>0.3</v>
       </c>
-      <c r="C10" t="s" s="7">
+      <c r="C10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D10" t="s" s="2">
+      <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E10" t="s" s="2">
+      <c r="E10" s="2" t="s">
         <v>38</v>
       </c>
       <c r="F10" s="4"/>
@@ -2602,23 +2704,23 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
     </row>
-    <row r="11" ht="14.45" customHeight="1">
-      <c r="A11" t="s" s="5">
+    <row r="11" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B11" s="6">
         <v>1.43</v>
       </c>
-      <c r="C11" t="s" s="7">
+      <c r="C11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D11" t="s" s="2">
+      <c r="D11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E11" t="s" s="2">
+      <c r="E11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F11" t="s" s="2">
+      <c r="F11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="G11" s="4"/>
@@ -2633,24 +2735,24 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" ht="14.45" customHeight="1">
-      <c r="A12" t="s" s="5">
+    <row r="12" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B12" s="11" cm="1">
         <f t="array" ref="B12">B10</f>
         <v>0.3</v>
       </c>
-      <c r="C12" t="s" s="7">
+      <c r="C12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D12" t="s" s="2">
+      <c r="D12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E12" t="s" s="2">
+      <c r="E12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F12" t="s" s="2">
+      <c r="F12" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G12" s="4"/>
@@ -2665,24 +2767,24 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
-    <row r="13" ht="14.45" customHeight="1">
-      <c r="A13" t="s" s="5">
+    <row r="13" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B13" s="12" cm="1">
         <f t="array" ref="B13">B11/B20^2</f>
-        <v>1.18181818181818</v>
-      </c>
-      <c r="C13" t="s" s="7">
+        <v>1.1818181818181817</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D13" t="s" s="2">
+      <c r="D13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E13" t="s" s="2">
+      <c r="E13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F13" t="s" s="2">
+      <c r="F13" s="2" t="s">
         <v>50</v>
       </c>
       <c r="G13" s="4"/>
@@ -2697,23 +2799,23 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" ht="14.45" customHeight="1">
-      <c r="A14" t="s" s="5">
+    <row r="14" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B14" s="13">
         <v>0.04</v>
       </c>
-      <c r="C14" t="s" s="7">
+      <c r="C14" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D14" t="s" s="2">
+      <c r="D14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E14" t="s" s="2">
+      <c r="E14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F14" t="s" s="2">
+      <c r="F14" s="2" t="s">
         <v>54</v>
       </c>
       <c r="G14" s="4"/>
@@ -2728,22 +2830,22 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
     </row>
-    <row r="15" ht="14.45" customHeight="1">
-      <c r="A15" t="s" s="5">
-        <v>55</v>
+    <row r="15" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="21" t="s">
+        <v>151</v>
       </c>
       <c r="B15" s="10" cm="1">
         <f t="array" ref="B15">B14+B9*B10^2</f>
-        <v>0.0481851113590118</v>
-      </c>
-      <c r="C15" t="s" s="7">
+        <v>4.8185111359011761E-2</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D15" t="s" s="2">
+      <c r="D15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>57</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -2758,24 +2860,24 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
     </row>
-    <row r="16" ht="14.45" customHeight="1">
-      <c r="A16" t="s" s="5">
-        <v>58</v>
+    <row r="16" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="B16" s="10" cm="1">
         <f t="array" ref="B16">B14+B9*B12^2</f>
-        <v>0.0481851113590118</v>
-      </c>
-      <c r="C16" t="s" s="7">
+        <v>4.8185111359011761E-2</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D16" t="s" s="2">
+      <c r="D16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E16" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="F16" t="s" s="2">
+      <c r="F16" s="2" t="s">
         <v>46</v>
       </c>
       <c r="G16" s="4"/>
@@ -2790,22 +2892,22 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
     </row>
-    <row r="17" ht="14.45" customHeight="1">
-      <c r="A17" t="s" s="5">
-        <v>61</v>
+    <row r="17" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="B17" s="10" cm="1">
         <f t="array" ref="B17">B16-B5*B12</f>
-        <v>0.0331851113590118</v>
-      </c>
-      <c r="C17" t="s" s="7">
+        <v>3.3185111359011761E-2</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D17" t="s" s="2">
+      <c r="D17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>63</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -2820,23 +2922,23 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
     </row>
-    <row r="18" ht="14.45" customHeight="1">
-      <c r="A18" t="s" s="5">
-        <v>64</v>
+    <row r="18" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="B18" s="12" cm="1">
         <f t="array" ref="B18">B10/B15</f>
-        <v>6.22598955442473</v>
-      </c>
-      <c r="C18" t="s" s="7">
+        <v>6.2259895544247374</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D18" t="s" s="2">
+      <c r="D18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="E18" s="4"/>
-      <c r="F18" t="s" s="2">
-        <v>66</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -2850,21 +2952,21 @@
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
     </row>
-    <row r="19" ht="14.45" customHeight="1">
-      <c r="A19" t="s" s="5">
-        <v>67</v>
+    <row r="19" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="B19" s="9">
         <v>10.5</v>
       </c>
-      <c r="C19" t="s" s="7">
+      <c r="C19" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D19" t="s" s="2">
+      <c r="D19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="E19" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -2879,20 +2981,20 @@
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
     </row>
-    <row r="20" ht="14.45" customHeight="1">
-      <c r="A20" t="s" s="5">
+    <row r="20" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="14">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="14">
-        <v>1.1</v>
-      </c>
-      <c r="C20" t="s" s="7">
-        <v>19</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E20" t="s" s="2">
+      <c r="E20" s="2" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="4"/>
@@ -2908,21 +3010,21 @@
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
     </row>
-    <row r="21" ht="14.45" customHeight="1">
-      <c r="A21" t="s" s="5">
-        <v>72</v>
+    <row r="21" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="B21" s="12" cm="1">
         <f t="array" ref="B21">B20*B19</f>
         <v>11.55</v>
       </c>
-      <c r="C21" t="s" s="7">
+      <c r="C21" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E21" t="s" s="2">
+      <c r="D21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>38</v>
       </c>
       <c r="F21" s="4"/>
@@ -2938,23 +3040,23 @@
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
     </row>
-    <row r="22" ht="14.45" customHeight="1">
-      <c r="A22" t="s" s="5">
-        <v>74</v>
+    <row r="22" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="B22" s="12" cm="1">
         <f t="array" ref="B22">SQRT(B19^2*B11/B10)</f>
-        <v>22.9243320513379</v>
-      </c>
-      <c r="C22" t="s" s="7">
+        <v>22.924332051337942</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D22" t="s" s="2">
+      <c r="D22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="E22" s="4"/>
-      <c r="F22" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -2968,19 +3070,19 @@
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
     </row>
-    <row r="23" ht="14.45" customHeight="1">
-      <c r="A23" t="s" s="5">
-        <v>77</v>
+    <row r="23" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="B23" s="12" cm="1">
         <f t="array" ref="B23">SQRT(B26*B4*SQRT(B25^2-1))</f>
-        <v>14.8107484143351</v>
-      </c>
-      <c r="C23" t="s" s="7">
+        <v>14.810748414335091</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D23" t="s" s="2">
-        <v>78</v>
+      <c r="D23" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
@@ -2996,22 +3098,22 @@
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
     </row>
-    <row r="24" ht="14.45" customHeight="1">
-      <c r="A24" t="s" s="5">
-        <v>79</v>
+    <row r="24" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="B24" s="12" cm="1">
         <f t="array" ref="B24">B19*SQRT(B25)</f>
-        <v>12.8598211496117</v>
-      </c>
-      <c r="C24" t="s" s="7">
+        <v>12.859821149611683</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D24" t="s" s="2">
+      <c r="D24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -3026,21 +3128,21 @@
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
     </row>
-    <row r="25" ht="14.45" customHeight="1">
-      <c r="A25" t="s" s="5">
-        <v>82</v>
+    <row r="25" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="B25" s="6">
         <v>1.5</v>
       </c>
-      <c r="C25" t="s" s="7">
+      <c r="C25" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D25" t="s" s="2">
+      <c r="D25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
@@ -3055,21 +3157,21 @@
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
     </row>
-    <row r="26" ht="14.45" customHeight="1">
-      <c r="A26" t="s" s="5">
-        <v>85</v>
+    <row r="26" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="B26" s="6">
         <v>20</v>
       </c>
-      <c r="C26" t="s" s="7">
+      <c r="C26" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D26" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="E26" t="s" s="2">
-        <v>81</v>
+      <c r="E26" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -3084,19 +3186,19 @@
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
     </row>
-    <row r="27" ht="14.45" customHeight="1">
-      <c r="A27" t="s" s="5">
-        <v>88</v>
+    <row r="27" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="B27" s="12" cm="1">
         <f t="array" ref="B27">DEGREES(ACOS(1/B25))</f>
-        <v>48.1896851042214</v>
-      </c>
-      <c r="C27" t="s" s="7">
+        <v>48.189685104221404</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="D27" t="s" s="2">
-        <v>90</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3112,21 +3214,21 @@
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
     </row>
-    <row r="28" ht="14.45" customHeight="1">
-      <c r="A28" t="s" s="5">
-        <v>91</v>
+    <row r="28" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>90</v>
       </c>
       <c r="B28" s="6">
         <v>0.75</v>
       </c>
-      <c r="C28" t="s" s="7">
+      <c r="C28" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D28" t="s" s="2">
+      <c r="D28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="E28" t="s" s="2">
-        <v>93</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -3141,21 +3243,21 @@
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
     </row>
-    <row r="29" ht="14.45" customHeight="1">
-      <c r="A29" t="s" s="5">
-        <v>94</v>
+    <row r="29" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="B29" s="6">
         <v>0.75</v>
       </c>
-      <c r="C29" t="s" s="7">
+      <c r="C29" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D29" t="s" s="2">
+      <c r="D29" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="E29" t="s" s="2">
-        <v>96</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -3170,21 +3272,21 @@
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
     </row>
-    <row r="30" ht="14.45" customHeight="1">
-      <c r="A30" t="s" s="5">
-        <v>97</v>
+    <row r="30" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="B30" s="6">
         <v>0.45</v>
       </c>
-      <c r="C30" t="s" s="7">
+      <c r="C30" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D30" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="E30" t="s" s="2">
-        <v>96</v>
+      <c r="D30" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
@@ -3199,21 +3301,21 @@
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
     </row>
-    <row r="31" ht="14.45" customHeight="1">
-      <c r="A31" t="s" s="5">
-        <v>99</v>
+    <row r="31" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="B31" s="6">
         <v>30</v>
       </c>
-      <c r="C31" t="s" s="7">
-        <v>86</v>
-      </c>
-      <c r="D31" t="s" s="2">
+      <c r="C31" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="E31" t="s" s="2">
-        <v>101</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -3228,21 +3330,21 @@
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
     </row>
-    <row r="32" ht="14.45" customHeight="1">
-      <c r="A32" t="s" s="5">
-        <v>102</v>
+    <row r="32" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="B32" s="6">
         <v>100</v>
       </c>
-      <c r="C32" t="s" s="7">
-        <v>86</v>
-      </c>
-      <c r="D32" t="s" s="2">
+      <c r="C32" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="E32" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
@@ -3257,19 +3359,19 @@
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
-    <row r="33" ht="14.45" customHeight="1">
-      <c r="A33" t="s" s="5">
-        <v>105</v>
+    <row r="33" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B33" s="12" cm="1">
         <f t="array" ref="B33">DEGREES(ATAN(30/100))</f>
-        <v>16.6992442339936</v>
-      </c>
-      <c r="C33" t="s" s="7">
-        <v>89</v>
-      </c>
-      <c r="D33" t="s" s="2">
-        <v>106</v>
+        <v>16.699244233993621</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -3285,21 +3387,21 @@
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
     </row>
-    <row r="34" ht="14.45" customHeight="1">
-      <c r="A34" t="s" s="5">
-        <v>107</v>
+    <row r="34" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B34" s="9">
         <v>25</v>
       </c>
-      <c r="C34" t="s" s="7">
-        <v>86</v>
-      </c>
-      <c r="D34" t="s" s="2">
+      <c r="C34" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="E34" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -3314,18 +3416,18 @@
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
     </row>
-    <row r="35" ht="14.45" customHeight="1">
-      <c r="A35" t="s" s="5">
-        <v>110</v>
+    <row r="35" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="B35" s="6">
         <v>100</v>
       </c>
-      <c r="C35" t="s" s="7">
+      <c r="C35" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="D35" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -3341,18 +3443,18 @@
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
     </row>
-    <row r="36" ht="14.45" customHeight="1">
-      <c r="A36" t="s" s="5">
+    <row r="36" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" s="6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B36" s="6">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="C36" t="s" s="7">
+      <c r="D36" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="D36" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -3368,18 +3470,18 @@
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" ht="14.45" customHeight="1">
-      <c r="A37" t="s" s="5">
-        <v>116</v>
+    <row r="37" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B37" s="6">
         <v>0.8</v>
       </c>
-      <c r="C37" t="s" s="7">
+      <c r="C37" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D37" t="s" s="2">
-        <v>117</v>
+      <c r="D37" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -3395,21 +3497,21 @@
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
     </row>
-    <row r="38" ht="14.45" customHeight="1">
-      <c r="A38" t="s" s="5">
-        <v>118</v>
+    <row r="38" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="B38" s="15">
         <v>4.45</v>
       </c>
-      <c r="C38" t="s" s="2">
+      <c r="C38" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D38" t="s" s="2">
+      <c r="E38" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="E38" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
@@ -3424,19 +3526,19 @@
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
     </row>
-    <row r="39" ht="14.45" customHeight="1">
-      <c r="A39" t="s" s="5">
-        <v>122</v>
+    <row r="39" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="B39" s="16" cm="1">
         <f t="array" ref="B39">B4*B38</f>
-        <v>43.6545</v>
-      </c>
-      <c r="C39" t="s" s="2">
+        <v>43.654500000000006</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="D39" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -3452,19 +3554,19 @@
       <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" ht="14.45" customHeight="1">
-      <c r="A40" t="s" s="5">
-        <v>125</v>
+    <row r="40" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="B40" s="17" cm="1">
         <f t="array" ref="B40">B39/B35</f>
-        <v>0.436545</v>
-      </c>
-      <c r="C40" t="s" s="2">
+        <v>0.43654500000000007</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="D40" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -3480,21 +3582,21 @@
       <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
     </row>
-    <row r="41" ht="14.45" customHeight="1">
-      <c r="A41" t="s" s="2">
-        <v>128</v>
+    <row r="41" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="19" t="s">
+        <v>152</v>
       </c>
       <c r="B41" s="18">
         <v>-0.08</v>
       </c>
-      <c r="C41" t="s" s="2">
+      <c r="C41" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D41" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="E41" t="s" s="2">
-        <v>130</v>
+      <c r="D41" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
@@ -3509,16 +3611,16 @@
       <c r="P41" s="4"/>
       <c r="Q41" s="4"/>
     </row>
-    <row r="42" ht="14.45" customHeight="1">
-      <c r="A42" t="s" s="2">
-        <v>131</v>
+    <row r="42" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="B42" s="18">
-        <v>0.291</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="C42" s="4"/>
-      <c r="D42" t="s" s="2">
-        <v>132</v>
+      <c r="D42" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -3534,19 +3636,19 @@
       <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
     </row>
-    <row r="43" ht="14.45" customHeight="1">
-      <c r="A43" t="s" s="2">
-        <v>133</v>
+    <row r="43" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="B43" s="18">
         <v>0.25</v>
       </c>
       <c r="C43" s="4"/>
-      <c r="D43" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="E43" t="s" s="2">
-        <v>135</v>
+      <c r="D43" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
@@ -3561,18 +3663,18 @@
       <c r="P43" s="4"/>
       <c r="Q43" s="4"/>
     </row>
-    <row r="44" ht="14.45" customHeight="1">
-      <c r="A44" t="s" s="19">
-        <v>136</v>
+    <row r="44" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="19" t="s">
+        <v>134</v>
       </c>
       <c r="B44" s="18">
         <v>0.65</v>
       </c>
-      <c r="C44" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="D44" t="s" s="2">
-        <v>138</v>
+      <c r="C44" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
@@ -3588,21 +3690,21 @@
       <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
     </row>
-    <row r="45" ht="14.45" customHeight="1">
-      <c r="A45" t="s" s="2">
-        <v>139</v>
+    <row r="45" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="B45" s="18">
         <v>0.2</v>
       </c>
-      <c r="C45" t="s" s="2">
+      <c r="C45" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D45" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="E45" t="s" s="2">
-        <v>141</v>
+      <c r="D45" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
@@ -3617,21 +3719,21 @@
       <c r="P45" s="4"/>
       <c r="Q45" s="4"/>
     </row>
-    <row r="46" ht="14.45" customHeight="1">
-      <c r="A46" t="s" s="2">
-        <v>142</v>
+    <row r="46" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="B46" s="18">
         <v>0.43</v>
       </c>
-      <c r="C46" t="s" s="2">
+      <c r="C46" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D46" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="E46" t="s" s="2">
-        <v>130</v>
+      <c r="D46" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
@@ -3646,21 +3748,21 @@
       <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
     </row>
-    <row r="47" ht="14.45" customHeight="1">
-      <c r="A47" t="s" s="2">
-        <v>144</v>
+    <row r="47" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="B47" s="18">
         <v>0.12</v>
       </c>
-      <c r="C47" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="D47" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="E47" t="s" s="2">
-        <v>146</v>
+      <c r="C47" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
@@ -3675,21 +3777,21 @@
       <c r="P47" s="4"/>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" ht="14.45" customHeight="1">
-      <c r="A48" t="s" s="2">
-        <v>147</v>
+    <row r="48" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="B48" s="18">
         <v>2.75</v>
       </c>
-      <c r="C48" t="s" s="2">
+      <c r="C48" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D48" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="E48" t="s" s="2">
-        <v>149</v>
+      <c r="D48" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -3704,12 +3806,22 @@
       <c r="P48" s="4"/>
       <c r="Q48" s="4"/>
     </row>
-    <row r="49" ht="14.45" customHeight="1">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
+    <row r="49" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="B49" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>150</v>
+      </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -3723,7 +3835,7 @@
       <c r="P49" s="4"/>
       <c r="Q49" s="4"/>
     </row>
-    <row r="50" ht="14.45" customHeight="1">
+    <row r="50" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -3742,7 +3854,7 @@
       <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" ht="14.45" customHeight="1">
+    <row r="51" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -3761,7 +3873,7 @@
       <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" ht="14.45" customHeight="1">
+    <row r="52" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -3780,7 +3892,7 @@
       <c r="P52" s="4"/>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" ht="14.45" customHeight="1">
+    <row r="53" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -3799,7 +3911,7 @@
       <c r="P53" s="4"/>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" ht="14.45" customHeight="1">
+    <row r="54" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -3818,7 +3930,7 @@
       <c r="P54" s="4"/>
       <c r="Q54" s="4"/>
     </row>
-    <row r="55" ht="14.45" customHeight="1">
+    <row r="55" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -3837,7 +3949,7 @@
       <c r="P55" s="4"/>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" ht="14.45" customHeight="1">
+    <row r="56" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -3856,7 +3968,7 @@
       <c r="P56" s="4"/>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" ht="14.45" customHeight="1">
+    <row r="57" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3875,7 +3987,7 @@
       <c r="P57" s="4"/>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" ht="14.45" customHeight="1">
+    <row r="58" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -3894,7 +4006,7 @@
       <c r="P58" s="4"/>
       <c r="Q58" s="4"/>
     </row>
-    <row r="59" ht="14.45" customHeight="1">
+    <row r="59" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -3913,7 +4025,7 @@
       <c r="P59" s="4"/>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" ht="14.45" customHeight="1">
+    <row r="60" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -3932,7 +4044,7 @@
       <c r="P60" s="4"/>
       <c r="Q60" s="4"/>
     </row>
-    <row r="61" ht="14.45" customHeight="1">
+    <row r="61" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -3951,7 +4063,7 @@
       <c r="P61" s="4"/>
       <c r="Q61" s="4"/>
     </row>
-    <row r="62" ht="14.45" customHeight="1">
+    <row r="62" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -3970,7 +4082,7 @@
       <c r="P62" s="4"/>
       <c r="Q62" s="4"/>
     </row>
-    <row r="63" ht="14.45" customHeight="1">
+    <row r="63" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -3989,7 +4101,7 @@
       <c r="P63" s="4"/>
       <c r="Q63" s="4"/>
     </row>
-    <row r="64" ht="14.45" customHeight="1">
+    <row r="64" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -4008,7 +4120,7 @@
       <c r="P64" s="4"/>
       <c r="Q64" s="4"/>
     </row>
-    <row r="65" ht="14.45" customHeight="1">
+    <row r="65" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -4027,7 +4139,7 @@
       <c r="P65" s="4"/>
       <c r="Q65" s="4"/>
     </row>
-    <row r="66" ht="14.45" customHeight="1">
+    <row r="66" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -4046,7 +4158,7 @@
       <c r="P66" s="4"/>
       <c r="Q66" s="4"/>
     </row>
-    <row r="67" ht="14.45" customHeight="1">
+    <row r="67" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -4065,7 +4177,7 @@
       <c r="P67" s="4"/>
       <c r="Q67" s="4"/>
     </row>
-    <row r="68" ht="14.45" customHeight="1">
+    <row r="68" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -4084,7 +4196,7 @@
       <c r="P68" s="4"/>
       <c r="Q68" s="4"/>
     </row>
-    <row r="69" ht="14.45" customHeight="1">
+    <row r="69" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -4103,7 +4215,7 @@
       <c r="P69" s="4"/>
       <c r="Q69" s="4"/>
     </row>
-    <row r="70" ht="14.45" customHeight="1">
+    <row r="70" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -4122,7 +4234,7 @@
       <c r="P70" s="4"/>
       <c r="Q70" s="4"/>
     </row>
-    <row r="71" ht="14.45" customHeight="1">
+    <row r="71" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -4141,7 +4253,7 @@
       <c r="P71" s="4"/>
       <c r="Q71" s="4"/>
     </row>
-    <row r="72" ht="14.45" customHeight="1">
+    <row r="72" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -4160,7 +4272,7 @@
       <c r="P72" s="4"/>
       <c r="Q72" s="4"/>
     </row>
-    <row r="73" ht="14.45" customHeight="1">
+    <row r="73" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -4179,7 +4291,7 @@
       <c r="P73" s="4"/>
       <c r="Q73" s="4"/>
     </row>
-    <row r="74" ht="14.45" customHeight="1">
+    <row r="74" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -4198,7 +4310,7 @@
       <c r="P74" s="4"/>
       <c r="Q74" s="4"/>
     </row>
-    <row r="75" ht="14.45" customHeight="1">
+    <row r="75" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -4217,7 +4329,7 @@
       <c r="P75" s="4"/>
       <c r="Q75" s="4"/>
     </row>
-    <row r="76" ht="14.45" customHeight="1">
+    <row r="76" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -4236,7 +4348,7 @@
       <c r="P76" s="4"/>
       <c r="Q76" s="4"/>
     </row>
-    <row r="77" ht="14.45" customHeight="1">
+    <row r="77" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -4255,7 +4367,7 @@
       <c r="P77" s="4"/>
       <c r="Q77" s="4"/>
     </row>
-    <row r="78" ht="14.45" customHeight="1">
+    <row r="78" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -4274,7 +4386,7 @@
       <c r="P78" s="4"/>
       <c r="Q78" s="4"/>
     </row>
-    <row r="79" ht="14.45" customHeight="1">
+    <row r="79" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -4293,7 +4405,7 @@
       <c r="P79" s="4"/>
       <c r="Q79" s="4"/>
     </row>
-    <row r="80" ht="14.45" customHeight="1">
+    <row r="80" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -4312,7 +4424,7 @@
       <c r="P80" s="4"/>
       <c r="Q80" s="4"/>
     </row>
-    <row r="81" ht="14.45" customHeight="1">
+    <row r="81" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -4331,7 +4443,7 @@
       <c r="P81" s="4"/>
       <c r="Q81" s="4"/>
     </row>
-    <row r="82" ht="14.45" customHeight="1">
+    <row r="82" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -4350,7 +4462,7 @@
       <c r="P82" s="4"/>
       <c r="Q82" s="4"/>
     </row>
-    <row r="83" ht="14.45" customHeight="1">
+    <row r="83" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -4369,7 +4481,7 @@
       <c r="P83" s="4"/>
       <c r="Q83" s="4"/>
     </row>
-    <row r="84" ht="14.45" customHeight="1">
+    <row r="84" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -4388,7 +4500,7 @@
       <c r="P84" s="4"/>
       <c r="Q84" s="4"/>
     </row>
-    <row r="85" ht="14.45" customHeight="1">
+    <row r="85" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -4407,7 +4519,7 @@
       <c r="P85" s="4"/>
       <c r="Q85" s="4"/>
     </row>
-    <row r="86" ht="14.45" customHeight="1">
+    <row r="86" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -4426,7 +4538,7 @@
       <c r="P86" s="4"/>
       <c r="Q86" s="4"/>
     </row>
-    <row r="87" ht="14.45" customHeight="1">
+    <row r="87" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -4445,7 +4557,7 @@
       <c r="P87" s="4"/>
       <c r="Q87" s="4"/>
     </row>
-    <row r="88" ht="14.45" customHeight="1">
+    <row r="88" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -4464,7 +4576,7 @@
       <c r="P88" s="4"/>
       <c r="Q88" s="4"/>
     </row>
-    <row r="89" ht="14.45" customHeight="1">
+    <row r="89" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -4483,7 +4595,7 @@
       <c r="P89" s="4"/>
       <c r="Q89" s="4"/>
     </row>
-    <row r="90" ht="14.45" customHeight="1">
+    <row r="90" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -4502,7 +4614,7 @@
       <c r="P90" s="4"/>
       <c r="Q90" s="4"/>
     </row>
-    <row r="91" ht="14.45" customHeight="1">
+    <row r="91" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -4521,7 +4633,7 @@
       <c r="P91" s="4"/>
       <c r="Q91" s="4"/>
     </row>
-    <row r="92" ht="14.45" customHeight="1">
+    <row r="92" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -4540,7 +4652,7 @@
       <c r="P92" s="4"/>
       <c r="Q92" s="4"/>
     </row>
-    <row r="93" ht="14.45" customHeight="1">
+    <row r="93" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -4559,7 +4671,7 @@
       <c r="P93" s="4"/>
       <c r="Q93" s="4"/>
     </row>
-    <row r="94" ht="14.45" customHeight="1">
+    <row r="94" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -4578,7 +4690,7 @@
       <c r="P94" s="4"/>
       <c r="Q94" s="4"/>
     </row>
-    <row r="95" ht="14.45" customHeight="1">
+    <row r="95" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -4597,7 +4709,7 @@
       <c r="P95" s="4"/>
       <c r="Q95" s="4"/>
     </row>
-    <row r="96" ht="14.45" customHeight="1">
+    <row r="96" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -4616,7 +4728,7 @@
       <c r="P96" s="4"/>
       <c r="Q96" s="4"/>
     </row>
-    <row r="97" ht="14.45" customHeight="1">
+    <row r="97" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -4635,7 +4747,7 @@
       <c r="P97" s="4"/>
       <c r="Q97" s="4"/>
     </row>
-    <row r="98" ht="14.45" customHeight="1">
+    <row r="98" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -4654,7 +4766,7 @@
       <c r="P98" s="4"/>
       <c r="Q98" s="4"/>
     </row>
-    <row r="99" ht="14.45" customHeight="1">
+    <row r="99" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -4673,7 +4785,7 @@
       <c r="P99" s="4"/>
       <c r="Q99" s="4"/>
     </row>
-    <row r="100" ht="14.45" customHeight="1">
+    <row r="100" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -4692,7 +4804,7 @@
       <c r="P100" s="4"/>
       <c r="Q100" s="4"/>
     </row>
-    <row r="101" ht="14.45" customHeight="1">
+    <row r="101" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -4711,7 +4823,7 @@
       <c r="P101" s="4"/>
       <c r="Q101" s="4"/>
     </row>
-    <row r="102" ht="14.45" customHeight="1">
+    <row r="102" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -4730,7 +4842,7 @@
       <c r="P102" s="4"/>
       <c r="Q102" s="4"/>
     </row>
-    <row r="103" ht="14.45" customHeight="1">
+    <row r="103" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -4749,7 +4861,7 @@
       <c r="P103" s="4"/>
       <c r="Q103" s="4"/>
     </row>
-    <row r="104" ht="14.45" customHeight="1">
+    <row r="104" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -4768,7 +4880,7 @@
       <c r="P104" s="4"/>
       <c r="Q104" s="4"/>
     </row>
-    <row r="105" ht="14.45" customHeight="1">
+    <row r="105" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -4787,7 +4899,7 @@
       <c r="P105" s="4"/>
       <c r="Q105" s="4"/>
     </row>
-    <row r="106" ht="14.45" customHeight="1">
+    <row r="106" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -4806,7 +4918,7 @@
       <c r="P106" s="4"/>
       <c r="Q106" s="4"/>
     </row>
-    <row r="107" ht="14.45" customHeight="1">
+    <row r="107" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -4825,7 +4937,7 @@
       <c r="P107" s="4"/>
       <c r="Q107" s="4"/>
     </row>
-    <row r="108" ht="14.45" customHeight="1">
+    <row r="108" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -4844,7 +4956,7 @@
       <c r="P108" s="4"/>
       <c r="Q108" s="4"/>
     </row>
-    <row r="109" ht="14.45" customHeight="1">
+    <row r="109" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -4863,7 +4975,7 @@
       <c r="P109" s="4"/>
       <c r="Q109" s="4"/>
     </row>
-    <row r="110" ht="14.45" customHeight="1">
+    <row r="110" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -4882,7 +4994,7 @@
       <c r="P110" s="4"/>
       <c r="Q110" s="4"/>
     </row>
-    <row r="111" ht="14.45" customHeight="1">
+    <row r="111" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -4901,7 +5013,7 @@
       <c r="P111" s="4"/>
       <c r="Q111" s="4"/>
     </row>
-    <row r="112" ht="14.45" customHeight="1">
+    <row r="112" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -4920,7 +5032,7 @@
       <c r="P112" s="4"/>
       <c r="Q112" s="4"/>
     </row>
-    <row r="113" ht="14.45" customHeight="1">
+    <row r="113" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -4939,7 +5051,7 @@
       <c r="P113" s="4"/>
       <c r="Q113" s="4"/>
     </row>
-    <row r="114" ht="14.45" customHeight="1">
+    <row r="114" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -4958,7 +5070,7 @@
       <c r="P114" s="4"/>
       <c r="Q114" s="4"/>
     </row>
-    <row r="115" ht="14.45" customHeight="1">
+    <row r="115" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -4977,7 +5089,7 @@
       <c r="P115" s="4"/>
       <c r="Q115" s="4"/>
     </row>
-    <row r="116" ht="14.45" customHeight="1">
+    <row r="116" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -4996,7 +5108,7 @@
       <c r="P116" s="4"/>
       <c r="Q116" s="4"/>
     </row>
-    <row r="117" ht="14.45" customHeight="1">
+    <row r="117" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -5015,7 +5127,7 @@
       <c r="P117" s="4"/>
       <c r="Q117" s="4"/>
     </row>
-    <row r="118" ht="14.45" customHeight="1">
+    <row r="118" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -5034,7 +5146,7 @@
       <c r="P118" s="4"/>
       <c r="Q118" s="4"/>
     </row>
-    <row r="119" ht="14.45" customHeight="1">
+    <row r="119" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -5053,7 +5165,7 @@
       <c r="P119" s="4"/>
       <c r="Q119" s="4"/>
     </row>
-    <row r="120" ht="14.45" customHeight="1">
+    <row r="120" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -5072,7 +5184,7 @@
       <c r="P120" s="4"/>
       <c r="Q120" s="4"/>
     </row>
-    <row r="121" ht="14.45" customHeight="1">
+    <row r="121" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -5091,7 +5203,7 @@
       <c r="P121" s="4"/>
       <c r="Q121" s="4"/>
     </row>
-    <row r="122" ht="14.45" customHeight="1">
+    <row r="122" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -5110,7 +5222,7 @@
       <c r="P122" s="4"/>
       <c r="Q122" s="4"/>
     </row>
-    <row r="123" ht="14.45" customHeight="1">
+    <row r="123" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -5129,7 +5241,7 @@
       <c r="P123" s="4"/>
       <c r="Q123" s="4"/>
     </row>
-    <row r="124" ht="14.45" customHeight="1">
+    <row r="124" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -5148,7 +5260,7 @@
       <c r="P124" s="4"/>
       <c r="Q124" s="4"/>
     </row>
-    <row r="125" ht="14.45" customHeight="1">
+    <row r="125" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -5167,7 +5279,7 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="4"/>
     </row>
-    <row r="126" ht="14.45" customHeight="1">
+    <row r="126" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -5186,7 +5298,7 @@
       <c r="P126" s="4"/>
       <c r="Q126" s="4"/>
     </row>
-    <row r="127" ht="14.45" customHeight="1">
+    <row r="127" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -5205,7 +5317,7 @@
       <c r="P127" s="4"/>
       <c r="Q127" s="4"/>
     </row>
-    <row r="128" ht="14.45" customHeight="1">
+    <row r="128" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -5224,7 +5336,7 @@
       <c r="P128" s="4"/>
       <c r="Q128" s="4"/>
     </row>
-    <row r="129" ht="14.45" customHeight="1">
+    <row r="129" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -5245,7 +5357,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hudson/Documents/GitHub/451-DBF-Team01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB30DBF-D90C-D04A-9CE1-D2D257DE167B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{8DB30DBF-D90C-D04A-9CE1-D2D257DE167B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08EDA64E-72B2-45A2-9A9B-BAEF15EC70EF}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="160">
   <si>
     <t>Parameter</t>
   </si>
@@ -514,6 +514,27 @@
   </si>
   <si>
     <t>CM_ac_w</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>Static Margin</t>
+  </si>
+  <si>
+    <t>Wingspan</t>
+  </si>
+  <si>
+    <t>Wing Span</t>
+  </si>
+  <si>
+    <t>Fuselage Thickness</t>
+  </si>
+  <si>
+    <t>t_fuselage</t>
   </si>
 </sst>
 </file>
@@ -695,7 +716,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -718,6 +739,7 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -856,16 +878,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>540205</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>131987</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>9151</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>141220</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>314597</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>99030</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>43963</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>67330</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -888,8 +910,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7449005" y="7472587"/>
-          <a:ext cx="4486093" cy="2536254"/>
+          <a:off x="8017478" y="6918624"/>
+          <a:ext cx="3639658" cy="2307360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2393,17 +2415,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q129"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.55" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" style="1" customWidth="1"/>
-    <col min="4" max="5" width="25.83203125" style="1" customWidth="1"/>
-    <col min="6" max="18" width="8.83203125" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="11.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" style="1" customWidth="1"/>
+    <col min="4" max="5" width="25.77734375" style="1" customWidth="1"/>
+    <col min="6" max="18" width="8.77734375" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2434,7 +2456,7 @@
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
     </row>
-    <row r="2" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -2465,7 +2487,7 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
     </row>
-    <row r="3" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -2494,7 +2516,7 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -2523,7 +2545,7 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
@@ -2554,7 +2576,7 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>23</v>
       </c>
@@ -2585,7 +2607,7 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
     </row>
-    <row r="7" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>26</v>
       </c>
@@ -2614,12 +2636,13 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B8" s="9">
-        <v>5</v>
+        <f>B51/B42</f>
+        <v>4.7168676768718001</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>19</v>
@@ -2645,13 +2668,13 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="10" cm="1">
         <f t="array" ref="B9">1/(PI()*B7*B8)</f>
-        <v>9.0945681766797334E-2</v>
+        <v>9.6404741448155279E-2</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>19</v>
@@ -2675,7 +2698,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>36</v>
       </c>
@@ -2704,7 +2727,7 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
     </row>
-    <row r="11" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
@@ -2735,7 +2758,7 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>43</v>
       </c>
@@ -2767,7 +2790,7 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
-    <row r="13" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>47</v>
       </c>
@@ -2799,7 +2822,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>51</v>
       </c>
@@ -2830,13 +2853,13 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
     </row>
-    <row r="15" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
         <v>151</v>
       </c>
       <c r="B15" s="10" cm="1">
         <f t="array" ref="B15">B14+B9*B10^2</f>
-        <v>4.8185111359011761E-2</v>
+        <v>4.8676426730333976E-2</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>19</v>
@@ -2860,13 +2883,13 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
     </row>
-    <row r="16" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>57</v>
       </c>
       <c r="B16" s="10" cm="1">
         <f t="array" ref="B16">B14+B9*B12^2</f>
-        <v>4.8185111359011761E-2</v>
+        <v>4.8676426730333976E-2</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>19</v>
@@ -2892,13 +2915,13 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
     </row>
-    <row r="17" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B17" s="10" cm="1">
         <f t="array" ref="B17">B16-B5*B12</f>
-        <v>3.3185111359011761E-2</v>
+        <v>3.3676426730333976E-2</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>19</v>
@@ -2922,13 +2945,13 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
     </row>
-    <row r="18" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B18" s="12" cm="1">
         <f t="array" ref="B18">B10/B15</f>
-        <v>6.2259895544247374</v>
+        <v>6.1631475470044563</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>19</v>
@@ -2952,7 +2975,7 @@
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
     </row>
-    <row r="19" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>66</v>
       </c>
@@ -2981,7 +3004,7 @@
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
     </row>
-    <row r="20" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>69</v>
       </c>
@@ -3010,7 +3033,7 @@
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
     </row>
-    <row r="21" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>71</v>
       </c>
@@ -3040,7 +3063,7 @@
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
     </row>
-    <row r="22" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>73</v>
       </c>
@@ -3070,7 +3093,7 @@
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
     </row>
-    <row r="23" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>76</v>
       </c>
@@ -3098,7 +3121,7 @@
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
     </row>
-    <row r="24" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>78</v>
       </c>
@@ -3128,7 +3151,7 @@
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
     </row>
-    <row r="25" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>81</v>
       </c>
@@ -3157,7 +3180,7 @@
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
     </row>
-    <row r="26" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>84</v>
       </c>
@@ -3186,7 +3209,7 @@
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
     </row>
-    <row r="27" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>87</v>
       </c>
@@ -3214,7 +3237,7 @@
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
     </row>
-    <row r="28" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>90</v>
       </c>
@@ -3243,7 +3266,7 @@
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
     </row>
-    <row r="29" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>93</v>
       </c>
@@ -3272,7 +3295,7 @@
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
     </row>
-    <row r="30" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>96</v>
       </c>
@@ -3301,7 +3324,7 @@
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
     </row>
-    <row r="31" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>98</v>
       </c>
@@ -3330,7 +3353,7 @@
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
     </row>
-    <row r="32" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>101</v>
       </c>
@@ -3359,7 +3382,7 @@
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
-    <row r="33" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>104</v>
       </c>
@@ -3387,7 +3410,7 @@
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
     </row>
-    <row r="34" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>106</v>
       </c>
@@ -3416,12 +3439,12 @@
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
     </row>
-    <row r="35" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>109</v>
       </c>
       <c r="B35" s="6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>110</v>
@@ -3443,7 +3466,7 @@
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
     </row>
-    <row r="36" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>112</v>
       </c>
@@ -3470,7 +3493,7 @@
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>115</v>
       </c>
@@ -3497,7 +3520,7 @@
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
     </row>
-    <row r="38" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>117</v>
       </c>
@@ -3526,7 +3549,7 @@
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
     </row>
-    <row r="39" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>121</v>
       </c>
@@ -3554,13 +3577,13 @@
       <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B40" s="17" cm="1">
-        <f t="array" ref="B40">B39/B35</f>
-        <v>0.43654500000000007</v>
+      <c r="B40" s="17">
+        <f>B39/B35</f>
+        <v>0.459521052631579</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>125</v>
@@ -3582,7 +3605,7 @@
       <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
     </row>
-    <row r="41" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
         <v>152</v>
       </c>
@@ -3611,12 +3634,13 @@
       <c r="P41" s="4"/>
       <c r="Q41" s="4"/>
     </row>
-    <row r="42" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B42" s="18">
-        <v>0.29099999999999998</v>
+        <f>B40/(B51-B52)</f>
+        <v>0.31800764887998545</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="2" t="s">
@@ -3636,7 +3660,7 @@
       <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
     </row>
-    <row r="43" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>131</v>
       </c>
@@ -3663,7 +3687,7 @@
       <c r="P43" s="4"/>
       <c r="Q43" s="4"/>
     </row>
-    <row r="44" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="19" t="s">
         <v>134</v>
       </c>
@@ -3690,12 +3714,12 @@
       <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
     </row>
-    <row r="45" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B45" s="18">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>19</v>
@@ -3719,7 +3743,7 @@
       <c r="P45" s="4"/>
       <c r="Q45" s="4"/>
     </row>
-    <row r="46" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>140</v>
       </c>
@@ -3748,7 +3772,7 @@
       <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
     </row>
-    <row r="47" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>142</v>
       </c>
@@ -3777,7 +3801,7 @@
       <c r="P47" s="4"/>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>145</v>
       </c>
@@ -3806,7 +3830,7 @@
       <c r="P48" s="4"/>
       <c r="Q48" s="4"/>
     </row>
-    <row r="49" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="20" t="s">
         <v>148</v>
       </c>
@@ -3835,11 +3859,19 @@
       <c r="P49" s="4"/>
       <c r="Q49" s="4"/>
     </row>
-    <row r="50" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
+    <row r="50" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>155</v>
+      </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
@@ -3854,11 +3886,19 @@
       <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
+    <row r="51" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B51" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>157</v>
+      </c>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
@@ -3873,11 +3913,19 @@
       <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
+    <row r="52" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B52" s="4">
+        <v>5.5E-2</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>158</v>
+      </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
@@ -3892,7 +3940,7 @@
       <c r="P52" s="4"/>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -3911,7 +3959,7 @@
       <c r="P53" s="4"/>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -3930,7 +3978,7 @@
       <c r="P54" s="4"/>
       <c r="Q54" s="4"/>
     </row>
-    <row r="55" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -3949,7 +3997,7 @@
       <c r="P55" s="4"/>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -3968,7 +4016,7 @@
       <c r="P56" s="4"/>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3987,7 +4035,7 @@
       <c r="P57" s="4"/>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -4006,7 +4054,7 @@
       <c r="P58" s="4"/>
       <c r="Q58" s="4"/>
     </row>
-    <row r="59" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -4025,7 +4073,7 @@
       <c r="P59" s="4"/>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -4044,7 +4092,7 @@
       <c r="P60" s="4"/>
       <c r="Q60" s="4"/>
     </row>
-    <row r="61" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -4063,7 +4111,7 @@
       <c r="P61" s="4"/>
       <c r="Q61" s="4"/>
     </row>
-    <row r="62" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -4082,7 +4130,7 @@
       <c r="P62" s="4"/>
       <c r="Q62" s="4"/>
     </row>
-    <row r="63" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -4101,7 +4149,7 @@
       <c r="P63" s="4"/>
       <c r="Q63" s="4"/>
     </row>
-    <row r="64" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -4120,7 +4168,7 @@
       <c r="P64" s="4"/>
       <c r="Q64" s="4"/>
     </row>
-    <row r="65" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -4139,7 +4187,7 @@
       <c r="P65" s="4"/>
       <c r="Q65" s="4"/>
     </row>
-    <row r="66" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -4158,7 +4206,7 @@
       <c r="P66" s="4"/>
       <c r="Q66" s="4"/>
     </row>
-    <row r="67" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -4177,7 +4225,7 @@
       <c r="P67" s="4"/>
       <c r="Q67" s="4"/>
     </row>
-    <row r="68" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -4196,7 +4244,7 @@
       <c r="P68" s="4"/>
       <c r="Q68" s="4"/>
     </row>
-    <row r="69" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -4215,7 +4263,7 @@
       <c r="P69" s="4"/>
       <c r="Q69" s="4"/>
     </row>
-    <row r="70" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -4234,7 +4282,7 @@
       <c r="P70" s="4"/>
       <c r="Q70" s="4"/>
     </row>
-    <row r="71" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -4253,7 +4301,7 @@
       <c r="P71" s="4"/>
       <c r="Q71" s="4"/>
     </row>
-    <row r="72" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -4272,7 +4320,7 @@
       <c r="P72" s="4"/>
       <c r="Q72" s="4"/>
     </row>
-    <row r="73" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -4291,7 +4339,7 @@
       <c r="P73" s="4"/>
       <c r="Q73" s="4"/>
     </row>
-    <row r="74" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -4310,7 +4358,7 @@
       <c r="P74" s="4"/>
       <c r="Q74" s="4"/>
     </row>
-    <row r="75" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -4329,7 +4377,7 @@
       <c r="P75" s="4"/>
       <c r="Q75" s="4"/>
     </row>
-    <row r="76" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -4348,7 +4396,7 @@
       <c r="P76" s="4"/>
       <c r="Q76" s="4"/>
     </row>
-    <row r="77" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -4367,7 +4415,7 @@
       <c r="P77" s="4"/>
       <c r="Q77" s="4"/>
     </row>
-    <row r="78" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -4386,7 +4434,7 @@
       <c r="P78" s="4"/>
       <c r="Q78" s="4"/>
     </row>
-    <row r="79" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -4405,7 +4453,7 @@
       <c r="P79" s="4"/>
       <c r="Q79" s="4"/>
     </row>
-    <row r="80" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -4424,7 +4472,7 @@
       <c r="P80" s="4"/>
       <c r="Q80" s="4"/>
     </row>
-    <row r="81" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -4443,7 +4491,7 @@
       <c r="P81" s="4"/>
       <c r="Q81" s="4"/>
     </row>
-    <row r="82" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -4462,7 +4510,7 @@
       <c r="P82" s="4"/>
       <c r="Q82" s="4"/>
     </row>
-    <row r="83" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -4481,7 +4529,7 @@
       <c r="P83" s="4"/>
       <c r="Q83" s="4"/>
     </row>
-    <row r="84" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -4500,7 +4548,7 @@
       <c r="P84" s="4"/>
       <c r="Q84" s="4"/>
     </row>
-    <row r="85" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -4519,7 +4567,7 @@
       <c r="P85" s="4"/>
       <c r="Q85" s="4"/>
     </row>
-    <row r="86" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -4538,7 +4586,7 @@
       <c r="P86" s="4"/>
       <c r="Q86" s="4"/>
     </row>
-    <row r="87" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -4557,7 +4605,7 @@
       <c r="P87" s="4"/>
       <c r="Q87" s="4"/>
     </row>
-    <row r="88" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -4576,7 +4624,7 @@
       <c r="P88" s="4"/>
       <c r="Q88" s="4"/>
     </row>
-    <row r="89" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -4595,7 +4643,7 @@
       <c r="P89" s="4"/>
       <c r="Q89" s="4"/>
     </row>
-    <row r="90" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -4614,7 +4662,7 @@
       <c r="P90" s="4"/>
       <c r="Q90" s="4"/>
     </row>
-    <row r="91" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -4633,7 +4681,7 @@
       <c r="P91" s="4"/>
       <c r="Q91" s="4"/>
     </row>
-    <row r="92" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -4652,7 +4700,7 @@
       <c r="P92" s="4"/>
       <c r="Q92" s="4"/>
     </row>
-    <row r="93" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -4671,7 +4719,7 @@
       <c r="P93" s="4"/>
       <c r="Q93" s="4"/>
     </row>
-    <row r="94" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -4690,7 +4738,7 @@
       <c r="P94" s="4"/>
       <c r="Q94" s="4"/>
     </row>
-    <row r="95" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -4709,7 +4757,7 @@
       <c r="P95" s="4"/>
       <c r="Q95" s="4"/>
     </row>
-    <row r="96" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -4728,7 +4776,7 @@
       <c r="P96" s="4"/>
       <c r="Q96" s="4"/>
     </row>
-    <row r="97" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -4747,7 +4795,7 @@
       <c r="P97" s="4"/>
       <c r="Q97" s="4"/>
     </row>
-    <row r="98" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -4766,7 +4814,7 @@
       <c r="P98" s="4"/>
       <c r="Q98" s="4"/>
     </row>
-    <row r="99" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -4785,7 +4833,7 @@
       <c r="P99" s="4"/>
       <c r="Q99" s="4"/>
     </row>
-    <row r="100" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -4804,7 +4852,7 @@
       <c r="P100" s="4"/>
       <c r="Q100" s="4"/>
     </row>
-    <row r="101" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -4823,7 +4871,7 @@
       <c r="P101" s="4"/>
       <c r="Q101" s="4"/>
     </row>
-    <row r="102" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -4842,7 +4890,7 @@
       <c r="P102" s="4"/>
       <c r="Q102" s="4"/>
     </row>
-    <row r="103" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -4861,7 +4909,7 @@
       <c r="P103" s="4"/>
       <c r="Q103" s="4"/>
     </row>
-    <row r="104" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -4880,7 +4928,7 @@
       <c r="P104" s="4"/>
       <c r="Q104" s="4"/>
     </row>
-    <row r="105" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -4899,7 +4947,7 @@
       <c r="P105" s="4"/>
       <c r="Q105" s="4"/>
     </row>
-    <row r="106" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -4918,7 +4966,7 @@
       <c r="P106" s="4"/>
       <c r="Q106" s="4"/>
     </row>
-    <row r="107" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -4937,7 +4985,7 @@
       <c r="P107" s="4"/>
       <c r="Q107" s="4"/>
     </row>
-    <row r="108" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -4956,7 +5004,7 @@
       <c r="P108" s="4"/>
       <c r="Q108" s="4"/>
     </row>
-    <row r="109" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -4975,7 +5023,7 @@
       <c r="P109" s="4"/>
       <c r="Q109" s="4"/>
     </row>
-    <row r="110" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -4994,7 +5042,7 @@
       <c r="P110" s="4"/>
       <c r="Q110" s="4"/>
     </row>
-    <row r="111" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -5013,7 +5061,7 @@
       <c r="P111" s="4"/>
       <c r="Q111" s="4"/>
     </row>
-    <row r="112" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -5032,7 +5080,7 @@
       <c r="P112" s="4"/>
       <c r="Q112" s="4"/>
     </row>
-    <row r="113" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -5051,7 +5099,7 @@
       <c r="P113" s="4"/>
       <c r="Q113" s="4"/>
     </row>
-    <row r="114" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -5070,7 +5118,7 @@
       <c r="P114" s="4"/>
       <c r="Q114" s="4"/>
     </row>
-    <row r="115" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -5089,7 +5137,7 @@
       <c r="P115" s="4"/>
       <c r="Q115" s="4"/>
     </row>
-    <row r="116" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -5108,7 +5156,7 @@
       <c r="P116" s="4"/>
       <c r="Q116" s="4"/>
     </row>
-    <row r="117" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -5127,7 +5175,7 @@
       <c r="P117" s="4"/>
       <c r="Q117" s="4"/>
     </row>
-    <row r="118" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -5146,7 +5194,7 @@
       <c r="P118" s="4"/>
       <c r="Q118" s="4"/>
     </row>
-    <row r="119" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -5165,7 +5213,7 @@
       <c r="P119" s="4"/>
       <c r="Q119" s="4"/>
     </row>
-    <row r="120" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -5184,7 +5232,7 @@
       <c r="P120" s="4"/>
       <c r="Q120" s="4"/>
     </row>
-    <row r="121" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -5203,7 +5251,7 @@
       <c r="P121" s="4"/>
       <c r="Q121" s="4"/>
     </row>
-    <row r="122" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -5222,7 +5270,7 @@
       <c r="P122" s="4"/>
       <c r="Q122" s="4"/>
     </row>
-    <row r="123" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -5241,7 +5289,7 @@
       <c r="P123" s="4"/>
       <c r="Q123" s="4"/>
     </row>
-    <row r="124" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -5260,7 +5308,7 @@
       <c r="P124" s="4"/>
       <c r="Q124" s="4"/>
     </row>
-    <row r="125" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -5279,7 +5327,7 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="4"/>
     </row>
-    <row r="126" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -5298,7 +5346,7 @@
       <c r="P126" s="4"/>
       <c r="Q126" s="4"/>
     </row>
-    <row r="127" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -5317,7 +5365,7 @@
       <c r="P127" s="4"/>
       <c r="Q127" s="4"/>
     </row>
-    <row r="128" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -5336,7 +5384,7 @@
       <c r="P128" s="4"/>
       <c r="Q128" s="4"/>
     </row>
-    <row r="129" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{8DB30DBF-D90C-D04A-9CE1-D2D257DE167B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08EDA64E-72B2-45A2-9A9B-BAEF15EC70EF}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{8DB30DBF-D90C-D04A-9CE1-D2D257DE167B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D62AE6AB-1151-4DD3-84AB-0C3CFAA60CD4}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3692,7 +3692,7 @@
         <v>134</v>
       </c>
       <c r="B44" s="18">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>135</v>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{8DB30DBF-D90C-D04A-9CE1-D2D257DE167B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D62AE6AB-1151-4DD3-84AB-0C3CFAA60CD4}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{8DB30DBF-D90C-D04A-9CE1-D2D257DE167B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{144341BB-1A2C-4E5A-9D4E-89E881CE32DC}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="164">
   <si>
     <t>Parameter</t>
   </si>
@@ -535,6 +535,18 @@
   </si>
   <si>
     <t>t_fuselage</t>
+  </si>
+  <si>
+    <t>St_S</t>
+  </si>
+  <si>
+    <t>Area of Tail</t>
+  </si>
+  <si>
+    <t>S_t</t>
+  </si>
+  <si>
+    <t>Size Ratio of Tail to Wing</t>
   </si>
 </sst>
 </file>
@@ -547,7 +559,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -572,8 +584,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -598,8 +617,13 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -712,11 +736,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -740,8 +780,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Input" xfId="1" builtinId="20"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2415,7 +2457,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q129"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.55" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.44140625" style="1" customWidth="1"/>
@@ -2425,7 +2467,7 @@
     <col min="19" max="16384" width="8.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="14.55" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2456,7 +2498,7 @@
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
     </row>
-    <row r="2" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="14.55" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -2487,7 +2529,7 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
     </row>
-    <row r="3" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="14.55" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -2516,7 +2558,7 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="14.55" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -2545,7 +2587,7 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="14.55" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>18</v>
       </c>
@@ -2576,7 +2618,7 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="14.55" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>23</v>
       </c>
@@ -2607,7 +2649,7 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
     </row>
-    <row r="7" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="14.55" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>26</v>
       </c>
@@ -2636,7 +2678,7 @@
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="14.55" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
@@ -2668,7 +2710,7 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="14.55" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>33</v>
       </c>
@@ -2698,7 +2740,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="14.55" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>36</v>
       </c>
@@ -2727,7 +2769,7 @@
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
     </row>
-    <row r="11" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="14.55" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
@@ -2758,7 +2800,7 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="14.55" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>43</v>
       </c>
@@ -2790,7 +2832,7 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
-    <row r="13" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="14.55" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>47</v>
       </c>
@@ -2822,7 +2864,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="14.55" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>51</v>
       </c>
@@ -2853,7 +2895,7 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
     </row>
-    <row r="15" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="14.55" customHeight="1">
       <c r="A15" s="21" t="s">
         <v>151</v>
       </c>
@@ -2883,7 +2925,7 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
     </row>
-    <row r="16" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="14.55" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>57</v>
       </c>
@@ -2915,7 +2957,7 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
     </row>
-    <row r="17" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="14.55" customHeight="1">
       <c r="A17" s="5" t="s">
         <v>60</v>
       </c>
@@ -2945,7 +2987,7 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
     </row>
-    <row r="18" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="14.55" customHeight="1">
       <c r="A18" s="5" t="s">
         <v>63</v>
       </c>
@@ -2975,7 +3017,7 @@
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
     </row>
-    <row r="19" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="14.55" customHeight="1">
       <c r="A19" s="5" t="s">
         <v>66</v>
       </c>
@@ -3004,7 +3046,7 @@
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
     </row>
-    <row r="20" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="14.55" customHeight="1">
       <c r="A20" s="5" t="s">
         <v>69</v>
       </c>
@@ -3033,7 +3075,7 @@
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
     </row>
-    <row r="21" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="14.55" customHeight="1">
       <c r="A21" s="5" t="s">
         <v>71</v>
       </c>
@@ -3063,7 +3105,7 @@
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
     </row>
-    <row r="22" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="14.55" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>73</v>
       </c>
@@ -3093,7 +3135,7 @@
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
     </row>
-    <row r="23" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="14.55" customHeight="1">
       <c r="A23" s="5" t="s">
         <v>76</v>
       </c>
@@ -3121,7 +3163,7 @@
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
     </row>
-    <row r="24" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="14.55" customHeight="1">
       <c r="A24" s="5" t="s">
         <v>78</v>
       </c>
@@ -3151,7 +3193,7 @@
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
     </row>
-    <row r="25" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="14.55" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>81</v>
       </c>
@@ -3180,7 +3222,7 @@
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
     </row>
-    <row r="26" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="14.55" customHeight="1">
       <c r="A26" s="5" t="s">
         <v>84</v>
       </c>
@@ -3209,7 +3251,7 @@
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
     </row>
-    <row r="27" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="14.55" customHeight="1">
       <c r="A27" s="5" t="s">
         <v>87</v>
       </c>
@@ -3237,7 +3279,7 @@
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
     </row>
-    <row r="28" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="14.55" customHeight="1">
       <c r="A28" s="5" t="s">
         <v>90</v>
       </c>
@@ -3266,7 +3308,7 @@
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
     </row>
-    <row r="29" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="14.55" customHeight="1">
       <c r="A29" s="5" t="s">
         <v>93</v>
       </c>
@@ -3295,7 +3337,7 @@
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
     </row>
-    <row r="30" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" ht="14.55" customHeight="1">
       <c r="A30" s="5" t="s">
         <v>96</v>
       </c>
@@ -3324,7 +3366,7 @@
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
     </row>
-    <row r="31" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" ht="14.55" customHeight="1">
       <c r="A31" s="5" t="s">
         <v>98</v>
       </c>
@@ -3353,7 +3395,7 @@
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
     </row>
-    <row r="32" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" ht="14.55" customHeight="1">
       <c r="A32" s="5" t="s">
         <v>101</v>
       </c>
@@ -3382,7 +3424,7 @@
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
-    <row r="33" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="14.55" customHeight="1">
       <c r="A33" s="5" t="s">
         <v>104</v>
       </c>
@@ -3410,7 +3452,7 @@
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
     </row>
-    <row r="34" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="14.55" customHeight="1">
       <c r="A34" s="5" t="s">
         <v>106</v>
       </c>
@@ -3439,7 +3481,7 @@
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
     </row>
-    <row r="35" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="14.55" customHeight="1">
       <c r="A35" s="5" t="s">
         <v>109</v>
       </c>
@@ -3466,7 +3508,7 @@
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
     </row>
-    <row r="36" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="14.55" customHeight="1">
       <c r="A36" s="5" t="s">
         <v>112</v>
       </c>
@@ -3493,7 +3535,7 @@
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" ht="14.55" customHeight="1">
       <c r="A37" s="5" t="s">
         <v>115</v>
       </c>
@@ -3520,7 +3562,7 @@
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
     </row>
-    <row r="38" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" ht="14.55" customHeight="1">
       <c r="A38" s="5" t="s">
         <v>117</v>
       </c>
@@ -3549,7 +3591,7 @@
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
     </row>
-    <row r="39" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" ht="14.55" customHeight="1">
       <c r="A39" s="5" t="s">
         <v>121</v>
       </c>
@@ -3577,7 +3619,7 @@
       <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" ht="14.55" customHeight="1">
       <c r="A40" s="5" t="s">
         <v>124</v>
       </c>
@@ -3605,7 +3647,7 @@
       <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
     </row>
-    <row r="41" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" ht="14.55" customHeight="1">
       <c r="A41" s="19" t="s">
         <v>152</v>
       </c>
@@ -3634,7 +3676,7 @@
       <c r="P41" s="4"/>
       <c r="Q41" s="4"/>
     </row>
-    <row r="42" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" ht="14.55" customHeight="1">
       <c r="A42" s="2" t="s">
         <v>129</v>
       </c>
@@ -3660,7 +3702,7 @@
       <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
     </row>
-    <row r="43" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" ht="14.55" customHeight="1">
       <c r="A43" s="2" t="s">
         <v>131</v>
       </c>
@@ -3687,7 +3729,7 @@
       <c r="P43" s="4"/>
       <c r="Q43" s="4"/>
     </row>
-    <row r="44" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" ht="14.55" customHeight="1">
       <c r="A44" s="19" t="s">
         <v>134</v>
       </c>
@@ -3714,7 +3756,7 @@
       <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
     </row>
-    <row r="45" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" ht="14.55" customHeight="1">
       <c r="A45" s="2" t="s">
         <v>137</v>
       </c>
@@ -3743,7 +3785,7 @@
       <c r="P45" s="4"/>
       <c r="Q45" s="4"/>
     </row>
-    <row r="46" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" ht="14.55" customHeight="1">
       <c r="A46" s="2" t="s">
         <v>140</v>
       </c>
@@ -3772,12 +3814,13 @@
       <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
     </row>
-    <row r="47" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" ht="14.55" customHeight="1">
       <c r="A47" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B47" s="18">
-        <v>0.12</v>
+      <c r="B47" s="4">
+        <f>SQRT(B54/B48)</f>
+        <v>0.19604252053179519</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>85</v>
@@ -3801,7 +3844,7 @@
       <c r="P47" s="4"/>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" ht="14.55" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>145</v>
       </c>
@@ -3830,7 +3873,7 @@
       <c r="P48" s="4"/>
       <c r="Q48" s="4"/>
     </row>
-    <row r="49" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" ht="14.55" customHeight="1">
       <c r="A49" s="20" t="s">
         <v>148</v>
       </c>
@@ -3859,7 +3902,7 @@
       <c r="P49" s="4"/>
       <c r="Q49" s="4"/>
     </row>
-    <row r="50" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" ht="14.55" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>153</v>
       </c>
@@ -3886,7 +3929,7 @@
       <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" ht="14.55" customHeight="1">
       <c r="A51" s="4" t="s">
         <v>156</v>
       </c>
@@ -3913,7 +3956,7 @@
       <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" ht="14.55" customHeight="1">
       <c r="A52" s="4" t="s">
         <v>159</v>
       </c>
@@ -3940,11 +3983,19 @@
       <c r="P52" s="4"/>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="4"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
+    <row r="53" spans="1:17" ht="14.55" customHeight="1">
+      <c r="A53" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B53" s="4">
+        <v>0.23</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>163</v>
+      </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
@@ -3959,11 +4010,20 @@
       <c r="P53" s="4"/>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="4"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
+    <row r="54" spans="1:17" ht="14.55" customHeight="1">
+      <c r="A54" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="B54" s="4">
+        <f>B53*B40</f>
+        <v>0.10568984210526318</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
@@ -3978,11 +4038,7 @@
       <c r="P54" s="4"/>
       <c r="Q54" s="4"/>
     </row>
-    <row r="55" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="4"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
+    <row r="55" spans="1:17" ht="14.55" customHeight="1">
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
@@ -3997,7 +4053,7 @@
       <c r="P55" s="4"/>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" ht="14.55" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -4016,9 +4072,8 @@
       <c r="P56" s="4"/>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" ht="14.55" customHeight="1">
       <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -4035,7 +4090,7 @@
       <c r="P57" s="4"/>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" ht="14.55" customHeight="1">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -4054,7 +4109,7 @@
       <c r="P58" s="4"/>
       <c r="Q58" s="4"/>
     </row>
-    <row r="59" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" ht="14.55" customHeight="1">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -4073,9 +4128,8 @@
       <c r="P59" s="4"/>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" ht="14.55" customHeight="1">
       <c r="A60" s="4"/>
-      <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -4092,7 +4146,7 @@
       <c r="P60" s="4"/>
       <c r="Q60" s="4"/>
     </row>
-    <row r="61" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" ht="14.55" customHeight="1">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -4111,7 +4165,7 @@
       <c r="P61" s="4"/>
       <c r="Q61" s="4"/>
     </row>
-    <row r="62" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" ht="14.55" customHeight="1">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -4130,7 +4184,7 @@
       <c r="P62" s="4"/>
       <c r="Q62" s="4"/>
     </row>
-    <row r="63" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" ht="14.55" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -4149,7 +4203,7 @@
       <c r="P63" s="4"/>
       <c r="Q63" s="4"/>
     </row>
-    <row r="64" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" ht="14.55" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -4168,7 +4222,7 @@
       <c r="P64" s="4"/>
       <c r="Q64" s="4"/>
     </row>
-    <row r="65" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" ht="14.55" customHeight="1">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -4187,7 +4241,7 @@
       <c r="P65" s="4"/>
       <c r="Q65" s="4"/>
     </row>
-    <row r="66" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" ht="14.55" customHeight="1">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -4206,7 +4260,7 @@
       <c r="P66" s="4"/>
       <c r="Q66" s="4"/>
     </row>
-    <row r="67" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" ht="14.55" customHeight="1">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -4225,7 +4279,7 @@
       <c r="P67" s="4"/>
       <c r="Q67" s="4"/>
     </row>
-    <row r="68" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" ht="14.55" customHeight="1">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -4244,7 +4298,7 @@
       <c r="P68" s="4"/>
       <c r="Q68" s="4"/>
     </row>
-    <row r="69" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" ht="14.55" customHeight="1">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -4263,7 +4317,7 @@
       <c r="P69" s="4"/>
       <c r="Q69" s="4"/>
     </row>
-    <row r="70" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" ht="14.55" customHeight="1">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -4282,7 +4336,7 @@
       <c r="P70" s="4"/>
       <c r="Q70" s="4"/>
     </row>
-    <row r="71" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" ht="14.55" customHeight="1">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -4301,7 +4355,7 @@
       <c r="P71" s="4"/>
       <c r="Q71" s="4"/>
     </row>
-    <row r="72" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" ht="14.55" customHeight="1">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -4320,7 +4374,7 @@
       <c r="P72" s="4"/>
       <c r="Q72" s="4"/>
     </row>
-    <row r="73" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" ht="14.55" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -4339,7 +4393,7 @@
       <c r="P73" s="4"/>
       <c r="Q73" s="4"/>
     </row>
-    <row r="74" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" ht="14.55" customHeight="1">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -4358,7 +4412,7 @@
       <c r="P74" s="4"/>
       <c r="Q74" s="4"/>
     </row>
-    <row r="75" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" ht="14.55" customHeight="1">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -4377,7 +4431,7 @@
       <c r="P75" s="4"/>
       <c r="Q75" s="4"/>
     </row>
-    <row r="76" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" ht="14.55" customHeight="1">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -4396,7 +4450,7 @@
       <c r="P76" s="4"/>
       <c r="Q76" s="4"/>
     </row>
-    <row r="77" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" ht="14.55" customHeight="1">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -4415,7 +4469,7 @@
       <c r="P77" s="4"/>
       <c r="Q77" s="4"/>
     </row>
-    <row r="78" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" ht="14.55" customHeight="1">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -4434,7 +4488,7 @@
       <c r="P78" s="4"/>
       <c r="Q78" s="4"/>
     </row>
-    <row r="79" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" ht="14.55" customHeight="1">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -4453,7 +4507,7 @@
       <c r="P79" s="4"/>
       <c r="Q79" s="4"/>
     </row>
-    <row r="80" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" ht="14.55" customHeight="1">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -4472,7 +4526,7 @@
       <c r="P80" s="4"/>
       <c r="Q80" s="4"/>
     </row>
-    <row r="81" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" ht="14.55" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -4491,7 +4545,7 @@
       <c r="P81" s="4"/>
       <c r="Q81" s="4"/>
     </row>
-    <row r="82" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" ht="14.55" customHeight="1">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -4510,7 +4564,7 @@
       <c r="P82" s="4"/>
       <c r="Q82" s="4"/>
     </row>
-    <row r="83" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" ht="14.55" customHeight="1">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -4529,7 +4583,7 @@
       <c r="P83" s="4"/>
       <c r="Q83" s="4"/>
     </row>
-    <row r="84" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" ht="14.55" customHeight="1">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -4548,7 +4602,7 @@
       <c r="P84" s="4"/>
       <c r="Q84" s="4"/>
     </row>
-    <row r="85" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" ht="14.55" customHeight="1">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -4567,7 +4621,7 @@
       <c r="P85" s="4"/>
       <c r="Q85" s="4"/>
     </row>
-    <row r="86" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" ht="14.55" customHeight="1">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -4586,7 +4640,7 @@
       <c r="P86" s="4"/>
       <c r="Q86" s="4"/>
     </row>
-    <row r="87" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" ht="14.55" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -4605,7 +4659,7 @@
       <c r="P87" s="4"/>
       <c r="Q87" s="4"/>
     </row>
-    <row r="88" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" ht="14.55" customHeight="1">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -4624,7 +4678,7 @@
       <c r="P88" s="4"/>
       <c r="Q88" s="4"/>
     </row>
-    <row r="89" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" ht="14.55" customHeight="1">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -4643,7 +4697,7 @@
       <c r="P89" s="4"/>
       <c r="Q89" s="4"/>
     </row>
-    <row r="90" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" ht="14.55" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -4662,7 +4716,7 @@
       <c r="P90" s="4"/>
       <c r="Q90" s="4"/>
     </row>
-    <row r="91" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" ht="14.55" customHeight="1">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -4681,7 +4735,7 @@
       <c r="P91" s="4"/>
       <c r="Q91" s="4"/>
     </row>
-    <row r="92" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" ht="14.55" customHeight="1">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -4700,7 +4754,7 @@
       <c r="P92" s="4"/>
       <c r="Q92" s="4"/>
     </row>
-    <row r="93" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" ht="14.55" customHeight="1">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -4719,7 +4773,7 @@
       <c r="P93" s="4"/>
       <c r="Q93" s="4"/>
     </row>
-    <row r="94" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" ht="14.55" customHeight="1">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -4738,7 +4792,7 @@
       <c r="P94" s="4"/>
       <c r="Q94" s="4"/>
     </row>
-    <row r="95" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" ht="14.55" customHeight="1">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -4757,7 +4811,7 @@
       <c r="P95" s="4"/>
       <c r="Q95" s="4"/>
     </row>
-    <row r="96" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" ht="14.55" customHeight="1">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -4776,7 +4830,7 @@
       <c r="P96" s="4"/>
       <c r="Q96" s="4"/>
     </row>
-    <row r="97" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" ht="14.55" customHeight="1">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -4795,7 +4849,7 @@
       <c r="P97" s="4"/>
       <c r="Q97" s="4"/>
     </row>
-    <row r="98" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" ht="14.55" customHeight="1">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -4814,7 +4868,7 @@
       <c r="P98" s="4"/>
       <c r="Q98" s="4"/>
     </row>
-    <row r="99" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" ht="14.55" customHeight="1">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -4833,7 +4887,7 @@
       <c r="P99" s="4"/>
       <c r="Q99" s="4"/>
     </row>
-    <row r="100" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" ht="14.55" customHeight="1">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -4852,7 +4906,7 @@
       <c r="P100" s="4"/>
       <c r="Q100" s="4"/>
     </row>
-    <row r="101" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" ht="14.55" customHeight="1">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -4871,7 +4925,7 @@
       <c r="P101" s="4"/>
       <c r="Q101" s="4"/>
     </row>
-    <row r="102" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" ht="14.55" customHeight="1">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -4890,7 +4944,7 @@
       <c r="P102" s="4"/>
       <c r="Q102" s="4"/>
     </row>
-    <row r="103" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" ht="14.55" customHeight="1">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -4909,7 +4963,7 @@
       <c r="P103" s="4"/>
       <c r="Q103" s="4"/>
     </row>
-    <row r="104" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" ht="14.55" customHeight="1">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -4928,7 +4982,7 @@
       <c r="P104" s="4"/>
       <c r="Q104" s="4"/>
     </row>
-    <row r="105" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" ht="14.55" customHeight="1">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -4947,7 +5001,7 @@
       <c r="P105" s="4"/>
       <c r="Q105" s="4"/>
     </row>
-    <row r="106" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" ht="14.55" customHeight="1">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -4966,7 +5020,7 @@
       <c r="P106" s="4"/>
       <c r="Q106" s="4"/>
     </row>
-    <row r="107" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" ht="14.55" customHeight="1">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -4985,7 +5039,7 @@
       <c r="P107" s="4"/>
       <c r="Q107" s="4"/>
     </row>
-    <row r="108" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" ht="14.55" customHeight="1">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -5004,7 +5058,7 @@
       <c r="P108" s="4"/>
       <c r="Q108" s="4"/>
     </row>
-    <row r="109" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" ht="14.55" customHeight="1">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -5023,7 +5077,7 @@
       <c r="P109" s="4"/>
       <c r="Q109" s="4"/>
     </row>
-    <row r="110" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" ht="14.55" customHeight="1">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -5042,7 +5096,7 @@
       <c r="P110" s="4"/>
       <c r="Q110" s="4"/>
     </row>
-    <row r="111" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" ht="14.55" customHeight="1">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -5061,7 +5115,7 @@
       <c r="P111" s="4"/>
       <c r="Q111" s="4"/>
     </row>
-    <row r="112" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" ht="14.55" customHeight="1">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -5080,7 +5134,7 @@
       <c r="P112" s="4"/>
       <c r="Q112" s="4"/>
     </row>
-    <row r="113" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" ht="14.55" customHeight="1">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -5099,7 +5153,7 @@
       <c r="P113" s="4"/>
       <c r="Q113" s="4"/>
     </row>
-    <row r="114" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" ht="14.55" customHeight="1">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -5118,7 +5172,7 @@
       <c r="P114" s="4"/>
       <c r="Q114" s="4"/>
     </row>
-    <row r="115" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" ht="14.55" customHeight="1">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -5137,7 +5191,7 @@
       <c r="P115" s="4"/>
       <c r="Q115" s="4"/>
     </row>
-    <row r="116" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" ht="14.55" customHeight="1">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -5156,7 +5210,7 @@
       <c r="P116" s="4"/>
       <c r="Q116" s="4"/>
     </row>
-    <row r="117" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" ht="14.55" customHeight="1">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -5175,7 +5229,7 @@
       <c r="P117" s="4"/>
       <c r="Q117" s="4"/>
     </row>
-    <row r="118" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" ht="14.55" customHeight="1">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -5194,7 +5248,7 @@
       <c r="P118" s="4"/>
       <c r="Q118" s="4"/>
     </row>
-    <row r="119" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" ht="14.55" customHeight="1">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -5213,7 +5267,7 @@
       <c r="P119" s="4"/>
       <c r="Q119" s="4"/>
     </row>
-    <row r="120" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" ht="14.55" customHeight="1">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -5232,7 +5286,7 @@
       <c r="P120" s="4"/>
       <c r="Q120" s="4"/>
     </row>
-    <row r="121" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" ht="14.55" customHeight="1">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -5251,7 +5305,7 @@
       <c r="P121" s="4"/>
       <c r="Q121" s="4"/>
     </row>
-    <row r="122" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" ht="14.55" customHeight="1">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -5270,7 +5324,7 @@
       <c r="P122" s="4"/>
       <c r="Q122" s="4"/>
     </row>
-    <row r="123" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" ht="14.55" customHeight="1">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -5289,7 +5343,7 @@
       <c r="P123" s="4"/>
       <c r="Q123" s="4"/>
     </row>
-    <row r="124" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" ht="14.55" customHeight="1">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -5308,7 +5362,7 @@
       <c r="P124" s="4"/>
       <c r="Q124" s="4"/>
     </row>
-    <row r="125" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" ht="14.55" customHeight="1">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -5327,7 +5381,7 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="4"/>
     </row>
-    <row r="126" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" ht="14.55" customHeight="1">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -5346,7 +5400,7 @@
       <c r="P126" s="4"/>
       <c r="Q126" s="4"/>
     </row>
-    <row r="127" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" ht="14.55" customHeight="1">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -5365,7 +5419,7 @@
       <c r="P127" s="4"/>
       <c r="Q127" s="4"/>
     </row>
-    <row r="128" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" ht="14.55" customHeight="1">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -5384,7 +5438,7 @@
       <c r="P128" s="4"/>
       <c r="Q128" s="4"/>
     </row>
-    <row r="129" spans="1:17" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:17" ht="14.55" customHeight="1">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EC9991-6063-4691-8624-8626F6AA939D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB223F66-9517-4EDD-BD92-D3E5CD30D508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="196">
   <si>
     <t>Parameter</t>
   </si>
@@ -441,9 +441,6 @@
     <t>Aerodynamic Center of Wing</t>
   </si>
   <si>
-    <t>Common Knowledge</t>
-  </si>
-  <si>
     <t>l_t</t>
   </si>
   <si>
@@ -495,9 +492,6 @@
     <t>SM</t>
   </si>
   <si>
-    <t>--</t>
-  </si>
-  <si>
     <t>Static Margin</t>
   </si>
   <si>
@@ -631,6 +625,24 @@
   </si>
   <si>
     <t>Drag code</t>
+  </si>
+  <si>
+    <t>K_hstab</t>
+  </si>
+  <si>
+    <t>Horizontal stab induced drag factor</t>
+  </si>
+  <si>
+    <t>Thin airfoil theory</t>
+  </si>
+  <si>
+    <t>St_S</t>
+  </si>
+  <si>
+    <t>Tail to wing area ratio</t>
+  </si>
+  <si>
+    <t>??</t>
   </si>
 </sst>
 </file>
@@ -805,7 +817,6 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -819,6 +830,7 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -965,7 +977,7 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>43963</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>67330</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1007,15 +1019,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>208817</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>164132</xdr:rowOff>
+      <xdr:colOff>142142</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>97457</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>24244</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>126033</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>605269</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>59358</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1038,8 +1050,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="208817" y="14085286"/>
-          <a:ext cx="4336139" cy="3075843"/>
+          <a:off x="142142" y="14937407"/>
+          <a:ext cx="5206577" cy="3038476"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1057,13 +1069,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>297995</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>108868</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>153761</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1106,13 +1118,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>254451</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>81649</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>475977</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>60011</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1155,13 +1167,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>175846</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>43014</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>575716</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>104</xdr:row>
       <xdr:rowOff>65005</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1204,13 +1216,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>278424</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>104</xdr:row>
       <xdr:rowOff>14660</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1516674</xdr:colOff>
-      <xdr:row>104</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>118773</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1253,13 +1265,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>142880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>244370</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>53886</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1302,13 +1314,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>498231</xdr:colOff>
-      <xdr:row>104</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>109907</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1281404</xdr:colOff>
-      <xdr:row>120</xdr:row>
+      <xdr:row>122</xdr:row>
       <xdr:rowOff>79550</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1351,13 +1363,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>685067</xdr:colOff>
-      <xdr:row>122</xdr:row>
+      <xdr:row>124</xdr:row>
       <xdr:rowOff>52020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1305657</xdr:colOff>
-      <xdr:row>137</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>59792</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1400,13 +1412,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>58615</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>130415</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>366931</xdr:colOff>
-      <xdr:row>137</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>25826</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1449,13 +1461,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>462644</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>54427</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>272143</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>87995</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2537,13 +2549,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R130"/>
+  <dimension ref="A1:R132"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.65" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.7109375" style="1" customWidth="1"/>
     <col min="7" max="19" width="8.7109375" style="1" customWidth="1"/>
@@ -2551,25 +2563,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="G1" s="17" t="s">
+      <c r="E1" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="G1" s="16" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3"/>
@@ -2588,7 +2600,7 @@
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>1.2250000000000001</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -2620,7 +2632,7 @@
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="12">
         <v>1.7960000000000001E-5</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -2650,7 +2662,7 @@
       <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>9.81</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -2680,7 +2692,7 @@
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>0.05</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -2712,7 +2724,7 @@
       <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>0.08</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -2742,9 +2754,9 @@
     </row>
     <row r="7" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="B7" s="14">
+        <v>182</v>
+      </c>
+      <c r="B7" s="13">
         <f>1.78*(1-0.045*B8^0.68)-0.64</f>
         <v>0.91000572412664693</v>
       </c>
@@ -2756,7 +2768,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -2775,8 +2787,8 @@
       <c r="A8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="14">
-        <f>B52/B42</f>
+      <c r="B8" s="13">
+        <f>B54/B42</f>
         <v>4.7168676768718001</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -2806,9 +2818,9 @@
     </row>
     <row r="9" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="B9" s="15" cm="1">
+        <v>187</v>
+      </c>
+      <c r="B9" s="14" cm="1">
         <f t="array" ref="B9">1/(PI()*B7*B8)</f>
         <v>7.4157026955488606E-2</v>
       </c>
@@ -2839,7 +2851,7 @@
       <c r="A10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>0.3</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -2869,7 +2881,7 @@
       <c r="A11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>1.43</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -2901,7 +2913,7 @@
       <c r="A12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="12" cm="1">
+      <c r="B12" s="11" cm="1">
         <f t="array" ref="B12">B10</f>
         <v>0.3</v>
       </c>
@@ -2934,7 +2946,7 @@
       <c r="A13" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="14" cm="1">
+      <c r="B13" s="13" cm="1">
         <f t="array" ref="B13">B11/B20^2</f>
         <v>1.1818181818181817</v>
       </c>
@@ -2967,7 +2979,7 @@
       <c r="A14" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="14">
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -2977,7 +2989,7 @@
         <v>48</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>49</v>
@@ -2999,9 +3011,9 @@
     </row>
     <row r="15" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B15" s="15" cm="1">
+        <v>142</v>
+      </c>
+      <c r="B15" s="14" cm="1">
         <f t="array" ref="B15">B14+B9*B10^2</f>
         <v>5.8674132425993973E-2</v>
       </c>
@@ -3032,7 +3044,7 @@
       <c r="A16" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="15" cm="1">
+      <c r="B16" s="14" cm="1">
         <f t="array" ref="B16">B14+B9*B12^2</f>
         <v>5.8674132425993973E-2</v>
       </c>
@@ -3065,7 +3077,7 @@
       <c r="A17" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="15" cm="1">
+      <c r="B17" s="14" cm="1">
         <f t="array" ref="B17">B16-B5*B12</f>
         <v>4.3674132425993974E-2</v>
       </c>
@@ -3096,7 +3108,7 @@
       <c r="A18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="14" cm="1">
+      <c r="B18" s="13" cm="1">
         <f t="array" ref="B18">B10/B15</f>
         <v>5.1129856990794327</v>
       </c>
@@ -3127,7 +3139,7 @@
       <c r="A19" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="13">
         <v>10.5</v>
       </c>
       <c r="C19" s="5" t="s">
@@ -3157,7 +3169,7 @@
       <c r="A20" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="15">
         <v>1.1000000000000001</v>
       </c>
       <c r="C20" s="5" t="s">
@@ -3187,7 +3199,7 @@
       <c r="A21" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="14" cm="1">
+      <c r="B21" s="13" cm="1">
         <f t="array" ref="B21">B20*B19</f>
         <v>11.55</v>
       </c>
@@ -3218,7 +3230,7 @@
       <c r="A22" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="14" cm="1">
+      <c r="B22" s="13" cm="1">
         <f t="array" ref="B22">SQRT(B19^2*B11/B10)</f>
         <v>22.924332051337942</v>
       </c>
@@ -3249,7 +3261,7 @@
       <c r="A23" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="14" cm="1">
+      <c r="B23" s="13" cm="1">
         <f t="array" ref="B23">SQRT(B26*B4*SQRT(B25^2-1))</f>
         <v>14.810748414335091</v>
       </c>
@@ -3278,7 +3290,7 @@
       <c r="A24" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="14" cm="1">
+      <c r="B24" s="13" cm="1">
         <f t="array" ref="B24">B19*SQRT(B25)</f>
         <v>12.859821149611683</v>
       </c>
@@ -3309,7 +3321,7 @@
       <c r="A25" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <v>1.5</v>
       </c>
       <c r="C25" s="5" t="s">
@@ -3339,7 +3351,7 @@
       <c r="A26" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="11">
         <v>20</v>
       </c>
       <c r="C26" s="5" t="s">
@@ -3369,7 +3381,7 @@
       <c r="A27" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B27" s="14" cm="1">
+      <c r="B27" s="13" cm="1">
         <f t="array" ref="B27">DEGREES(ACOS(1/B25))</f>
         <v>48.189685104221404</v>
       </c>
@@ -3398,7 +3410,7 @@
       <c r="A28" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="11">
         <v>0.75</v>
       </c>
       <c r="C28" s="5" t="s">
@@ -3428,7 +3440,7 @@
       <c r="A29" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="11">
         <v>0.75</v>
       </c>
       <c r="C29" s="5" t="s">
@@ -3458,7 +3470,7 @@
       <c r="A30" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="11">
         <v>0.45</v>
       </c>
       <c r="C30" s="5" t="s">
@@ -3488,7 +3500,7 @@
       <c r="A31" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="11">
         <v>30</v>
       </c>
       <c r="C31" s="5" t="s">
@@ -3518,7 +3530,7 @@
       <c r="A32" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="11">
         <v>100</v>
       </c>
       <c r="C32" s="5" t="s">
@@ -3548,7 +3560,7 @@
       <c r="A33" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B33" s="14" cm="1">
+      <c r="B33" s="13" cm="1">
         <f t="array" ref="B33">DEGREES(ATAN(30/100))</f>
         <v>16.699244233993621</v>
       </c>
@@ -3577,7 +3589,7 @@
       <c r="A34" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B34" s="14">
+      <c r="B34" s="13">
         <v>25</v>
       </c>
       <c r="C34" s="5" t="s">
@@ -3607,7 +3619,7 @@
       <c r="A35" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="11">
         <v>95</v>
       </c>
       <c r="C35" s="5" t="s">
@@ -3635,7 +3647,7 @@
       <c r="A36" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="11">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C36" s="5" t="s">
@@ -3663,7 +3675,7 @@
       <c r="A37" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="11">
         <v>0.8</v>
       </c>
       <c r="C37" s="5" t="s">
@@ -3691,7 +3703,7 @@
       <c r="A38" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B38" s="19">
+      <c r="B38" s="18">
         <v>4.45</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -3721,7 +3733,7 @@
       <c r="A39" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B39" s="20" cm="1">
+      <c r="B39" s="19" cm="1">
         <f t="array" ref="B39">B4*B38</f>
         <v>43.654500000000006</v>
       </c>
@@ -3750,7 +3762,7 @@
       <c r="A40" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B40" s="21">
+      <c r="B40" s="20">
         <f>B39/B35</f>
         <v>0.459521052631579</v>
       </c>
@@ -3777,9 +3789,9 @@
     </row>
     <row r="41" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B41" s="22">
+        <v>143</v>
+      </c>
+      <c r="B41" s="21">
         <v>-0.08</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -3807,10 +3819,10 @@
     </row>
     <row r="42" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="B42" s="11">
-        <f>B40/(B52-B53)</f>
+        <v>184</v>
+      </c>
+      <c r="B42" s="10">
+        <f>B40/(B54-B55)</f>
         <v>0.31800764887998545</v>
       </c>
       <c r="C42" s="3"/>
@@ -3844,8 +3856,8 @@
         <v>127</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="2" t="s">
-        <v>128</v>
+      <c r="F43" s="7" t="s">
+        <v>192</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
@@ -3862,16 +3874,16 @@
     </row>
     <row r="44" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B44" s="6">
         <v>0.7</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="3"/>
@@ -3889,22 +3901,20 @@
       <c r="R44" s="3"/>
     </row>
     <row r="45" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>132</v>
+      <c r="A45" s="7" t="s">
+        <v>193</v>
       </c>
       <c r="B45" s="6">
-        <v>0.3</v>
-      </c>
-      <c r="C45" s="2" t="s">
+        <v>0.23</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>133</v>
+      <c r="D45" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="E45" s="2"/>
-      <c r="F45" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
@@ -3920,20 +3930,20 @@
     </row>
     <row r="46" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B46" s="6">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
@@ -3949,21 +3959,21 @@
       <c r="R46" s="3"/>
     </row>
     <row r="47" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
-        <v>161</v>
+      <c r="A47" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="B47" s="6">
-        <v>0.12</v>
+        <v>0.43</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
@@ -3980,20 +3990,20 @@
     </row>
     <row r="48" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B48" s="6">
-        <v>2.75</v>
+        <v>0.12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
@@ -4010,18 +4020,21 @@
     </row>
     <row r="49" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B49" s="6">
-        <f>B48*B47</f>
-        <v>0.32999999999999996</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D49" s="2"/>
+        <v>2.75</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
+      <c r="F49" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -4036,23 +4049,19 @@
       <c r="R49" s="3"/>
     </row>
     <row r="50" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B50" s="23">
-        <f>1.78*(1-0.045*B48^0.68)-0.64</f>
-        <v>0.98064021032647342</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="E50" s="8"/>
-      <c r="F50" s="7" t="s">
-        <v>185</v>
-      </c>
+      <c r="A50" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B50" s="6">
+        <f>B49*B48</f>
+        <v>0.32999999999999996</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -4067,20 +4076,22 @@
       <c r="R50" s="3"/>
     </row>
     <row r="51" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B51" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
+      <c r="A51" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" s="22">
+        <v>0.65</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="F51" s="7"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
@@ -4096,19 +4107,20 @@
     </row>
     <row r="52" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="B52" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
+        <v>190</v>
+      </c>
+      <c r="B52" s="22">
+        <f>1/(PI()*B51*B49)</f>
+        <v>0.17807546080212067</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="E52" s="8"/>
+      <c r="F52" s="7"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -4123,19 +4135,19 @@
       <c r="R52" s="3"/>
     </row>
     <row r="53" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
-        <v>152</v>
+      <c r="A53" s="3" t="s">
+        <v>144</v>
       </c>
       <c r="B53" s="3">
-        <v>5.5E-2</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="E53" s="8"/>
+        <v>0.15</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
@@ -4152,18 +4164,18 @@
     </row>
     <row r="54" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B54" s="3">
-        <v>1</v>
-      </c>
-      <c r="C54" s="8" t="s">
+        <v>1.5</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D54" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="E54" s="8"/>
+      <c r="D54" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
@@ -4180,16 +4192,16 @@
     </row>
     <row r="55" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B55" s="3">
-        <v>0.127</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>121</v>
+        <v>5.5E-2</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E55" s="8"/>
       <c r="F55" s="3"/>
@@ -4208,16 +4220,16 @@
     </row>
     <row r="56" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B56" s="3">
-        <v>0.14000000000000001</v>
+        <v>1</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="3"/>
@@ -4236,16 +4248,16 @@
     </row>
     <row r="57" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B57" s="3">
-        <v>0.255</v>
+        <v>0.127</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>18</v>
+        <v>121</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E57" s="8"/>
       <c r="F57" s="3"/>
@@ -4264,16 +4276,16 @@
     </row>
     <row r="58" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B58" s="3">
-        <v>0.12</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>18</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="E58" s="8"/>
       <c r="F58" s="3"/>
@@ -4292,16 +4304,16 @@
     </row>
     <row r="59" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B59" s="3">
-        <v>0.3</v>
+        <v>0.255</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>18</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E59" s="8"/>
       <c r="F59" s="3"/>
@@ -4320,16 +4332,18 @@
     </row>
     <row r="60" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B60" s="3">
         <v>0.12</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E60" s="8"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
@@ -4346,16 +4360,18 @@
     </row>
     <row r="61" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B61" s="3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E61" s="8"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
@@ -4372,14 +4388,13 @@
     </row>
     <row r="62" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="B62" s="23">
-        <f>B61/B60</f>
-        <v>1.6666666666666667</v>
+        <v>165</v>
+      </c>
+      <c r="B62" s="3">
+        <v>0.12</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -4399,18 +4414,16 @@
     </row>
     <row r="63" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="B63" s="3">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="E63" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
@@ -4427,18 +4440,17 @@
     </row>
     <row r="64" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="B64" s="3">
-        <v>0.3</v>
+        <v>168</v>
+      </c>
+      <c r="B64" s="22">
+        <f>B63/B62</f>
+        <v>1.6666666666666667</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D64" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="E64" s="8"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
@@ -4455,16 +4467,18 @@
     </row>
     <row r="65" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="B65" s="3">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E65" s="8"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
@@ -4481,16 +4495,18 @@
     </row>
     <row r="66" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B66" s="3">
-        <v>1.4999999999999999E-2</v>
+        <v>0.3</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E66" s="8"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
@@ -4507,10 +4523,10 @@
     </row>
     <row r="67" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B67" s="3">
-        <v>0.155</v>
+        <v>0.05</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>81</v>
@@ -4533,10 +4549,10 @@
     </row>
     <row r="68" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B68" s="3">
-        <v>1.6E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>81</v>
@@ -4559,10 +4575,10 @@
     </row>
     <row r="69" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B69" s="3">
-        <v>0.05</v>
+        <v>0.155</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>81</v>
@@ -4585,10 +4601,10 @@
     </row>
     <row r="70" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B70" s="3">
-        <v>1.4999999999999999E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>81</v>
@@ -4611,10 +4627,10 @@
     </row>
     <row r="71" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B71" s="3">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>81</v>
@@ -4637,10 +4653,10 @@
     </row>
     <row r="72" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B72" s="3">
-        <v>0.01</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>81</v>
@@ -4663,18 +4679,16 @@
     </row>
     <row r="73" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B73" s="3">
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="E73" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
@@ -4691,18 +4705,16 @@
     </row>
     <row r="74" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B74" s="3">
-        <v>0.3</v>
+        <v>0.01</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="E74" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
@@ -4719,16 +4731,18 @@
     </row>
     <row r="75" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B75" s="3">
-        <v>1.1000000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
+      <c r="D75" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E75" s="8"/>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
@@ -4744,11 +4758,19 @@
       <c r="R75" s="3"/>
     </row>
     <row r="76" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
+      <c r="A76" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B76" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E76" s="8"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
@@ -4764,9 +4786,15 @@
       <c r="R76" s="3"/>
     </row>
     <row r="77" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
+      <c r="A77" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B77" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>18</v>
+      </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
@@ -5843,6 +5871,46 @@
       <c r="Q130" s="3"/>
       <c r="R130" s="3"/>
     </row>
+    <row r="131" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
+      <c r="I131" s="3"/>
+      <c r="J131" s="3"/>
+      <c r="K131" s="3"/>
+      <c r="L131" s="3"/>
+      <c r="M131" s="3"/>
+      <c r="N131" s="3"/>
+      <c r="O131" s="3"/>
+      <c r="P131" s="3"/>
+      <c r="Q131" s="3"/>
+      <c r="R131" s="3"/>
+    </row>
+    <row r="132" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="3"/>
+      <c r="J132" s="3"/>
+      <c r="K132" s="3"/>
+      <c r="L132" s="3"/>
+      <c r="M132" s="3"/>
+      <c r="N132" s="3"/>
+      <c r="O132" s="3"/>
+      <c r="P132" s="3"/>
+      <c r="Q132" s="3"/>
+      <c r="R132" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB223F66-9517-4EDD-BD92-D3E5CD30D508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90AE71A-0B5B-4B86-868D-16070F90B040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -600,9 +600,6 @@
     <t>Landing strut drag factor</t>
   </si>
   <si>
-    <t>CD_0_leak_factor</t>
-  </si>
-  <si>
     <t>e_wing</t>
   </si>
   <si>
@@ -643,6 +640,9 @@
   </si>
   <si>
     <t>??</t>
+  </si>
+  <si>
+    <t>CD_0_misc_factor</t>
   </si>
 </sst>
 </file>
@@ -1460,15 +1460,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>462644</xdr:colOff>
+      <xdr:colOff>443594</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>54427</xdr:rowOff>
+      <xdr:rowOff>92527</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>272143</xdr:colOff>
+      <xdr:colOff>253093</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>87995</xdr:rowOff>
+      <xdr:rowOff>126095</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1491,8 +1491,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6694715" y="9252856"/>
-          <a:ext cx="6245678" cy="1271818"/>
+          <a:off x="7549244" y="9865177"/>
+          <a:ext cx="6200774" cy="1300393"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2576,7 +2576,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F1" s="16" t="s">
         <v>147</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="7" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B7" s="13">
         <f>1.78*(1-0.045*B8^0.68)-0.64</f>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -2818,7 +2818,7 @@
     </row>
     <row r="9" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B9" s="14" cm="1">
         <f t="array" ref="B9">1/(PI()*B7*B8)</f>
@@ -2980,7 +2980,7 @@
         <v>47</v>
       </c>
       <c r="B14" s="14">
-        <v>5.1999999999999998E-2</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>18</v>
@@ -2989,7 +2989,7 @@
         <v>48</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>49</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="B15" s="14" cm="1">
         <f t="array" ref="B15">B14+B9*B10^2</f>
-        <v>5.8674132425993973E-2</v>
+        <v>3.3874132425993971E-2</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>18</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B16" s="14" cm="1">
         <f t="array" ref="B16">B14+B9*B12^2</f>
-        <v>5.8674132425993973E-2</v>
+        <v>3.3874132425993971E-2</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>18</v>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="B17" s="14" cm="1">
         <f t="array" ref="B17">B16-B5*B12</f>
-        <v>4.3674132425993974E-2</v>
+        <v>1.8874132425993971E-2</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>18</v>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="B18" s="13" cm="1">
         <f t="array" ref="B18">B10/B15</f>
-        <v>5.1129856990794327</v>
+        <v>8.856315380339872</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>18</v>
@@ -3819,7 +3819,7 @@
     </row>
     <row r="42" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B42" s="10">
         <f>B40/(B54-B55)</f>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="45" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B45" s="6">
         <v>0.23</v>
@@ -3911,7 +3911,7 @@
         <v>18</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="3"/>
@@ -4089,7 +4089,7 @@
         <v>141</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="3"/>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="52" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B52" s="22">
         <f>1/(PI()*B51*B49)</f>
@@ -4117,7 +4117,7 @@
         <v>18</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E52" s="8"/>
       <c r="F52" s="7"/>
@@ -4467,7 +4467,7 @@
     </row>
     <row r="65" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B65" s="3">
         <v>0.12</v>
@@ -4495,7 +4495,7 @@
     </row>
     <row r="66" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B66" s="3">
         <v>0.3</v>
@@ -4787,10 +4787,10 @@
     </row>
     <row r="77" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B77" s="3">
-        <v>1.1000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>18</v>

--- a/SizingParams.xlsx
+++ b/SizingParams.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Fall 2026\AAE 451\451-DBF-Team01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90AE71A-0B5B-4B86-868D-16070F90B040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{D90AE71A-0B5B-4B86-868D-16070F90B040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27328F69-6F6C-4A88-B232-EE2B8B09F70C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-23430" yWindow="3600" windowWidth="9255" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="203">
   <si>
     <t>Parameter</t>
   </si>
@@ -643,6 +643,27 @@
   </si>
   <si>
     <t>CD_0_misc_factor</t>
+  </si>
+  <si>
+    <t>V_v</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>Vertical Tail Coefficient</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>zw</t>
+  </si>
+  <si>
+    <t>Body Depth of Wing</t>
+  </si>
+  <si>
+    <t>Wing Root Height</t>
   </si>
 </sst>
 </file>
@@ -806,7 +827,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -831,6 +852,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1466,9 +1488,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>253093</xdr:colOff>
+      <xdr:colOff>249283</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>126095</xdr:rowOff>
+      <xdr:rowOff>129905</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2550,19 +2572,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R132"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.65" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.7" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="34.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.7109375" style="1" customWidth="1"/>
-    <col min="7" max="19" width="8.7109375" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" style="1" customWidth="1"/>
+    <col min="7" max="19" width="8.6640625" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -2596,7 +2618,7 @@
       <c r="Q1" s="3"/>
       <c r="R1" s="3"/>
     </row>
-    <row r="2" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -2628,7 +2650,7 @@
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
     </row>
-    <row r="3" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -2658,7 +2680,7 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
@@ -2688,7 +2710,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>17</v>
       </c>
@@ -2720,7 +2742,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
@@ -2752,7 +2774,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>181</v>
       </c>
@@ -2783,7 +2805,7 @@
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>26</v>
       </c>
@@ -2816,7 +2838,7 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>186</v>
       </c>
@@ -2847,7 +2869,7 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>32</v>
       </c>
@@ -2877,7 +2899,7 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>35</v>
       </c>
@@ -2909,7 +2931,7 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>39</v>
       </c>
@@ -2942,7 +2964,7 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>43</v>
       </c>
@@ -2975,7 +2997,7 @@
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>47</v>
       </c>
@@ -3009,7 +3031,7 @@
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>142</v>
       </c>
@@ -3040,7 +3062,7 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>53</v>
       </c>
@@ -3073,7 +3095,7 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
     </row>
-    <row r="17" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>56</v>
       </c>
@@ -3104,7 +3126,7 @@
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
     </row>
-    <row r="18" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>59</v>
       </c>
@@ -3135,7 +3157,7 @@
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
     </row>
-    <row r="19" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>62</v>
       </c>
@@ -3165,7 +3187,7 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
     </row>
-    <row r="20" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>65</v>
       </c>
@@ -3195,7 +3217,7 @@
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
     </row>
-    <row r="21" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>67</v>
       </c>
@@ -3226,7 +3248,7 @@
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
     </row>
-    <row r="22" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>69</v>
       </c>
@@ -3257,7 +3279,7 @@
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
     </row>
-    <row r="23" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>72</v>
       </c>
@@ -3286,7 +3308,7 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>74</v>
       </c>
@@ -3317,7 +3339,7 @@
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
     </row>
-    <row r="25" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>77</v>
       </c>
@@ -3347,7 +3369,7 @@
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
     </row>
-    <row r="26" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>80</v>
       </c>
@@ -3377,7 +3399,7 @@
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
     </row>
-    <row r="27" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>83</v>
       </c>
@@ -3406,7 +3428,7 @@
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
     </row>
-    <row r="28" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>86</v>
       </c>
@@ -3436,7 +3458,7 @@
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
     </row>
-    <row r="29" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>89</v>
       </c>
@@ -3466,7 +3488,7 @@
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
     </row>
-    <row r="30" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>92</v>
       </c>
@@ -3496,7 +3518,7 @@
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
     </row>
-    <row r="31" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>94</v>
       </c>
@@ -3526,7 +3548,7 @@
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
     </row>
-    <row r="32" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>97</v>
       </c>
@@ -3556,7 +3578,7 @@
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
     </row>
-    <row r="33" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>100</v>
       </c>
@@ -3585,7 +3607,7 @@
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
     </row>
-    <row r="34" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>102</v>
       </c>
@@ -3615,7 +3637,7 @@
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
     </row>
-    <row r="35" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>105</v>
       </c>
@@ -3643,7 +3665,7 @@
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
     </row>
-    <row r="36" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>108</v>
       </c>
@@ -3671,7 +3693,7 @@
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
     </row>
-    <row r="37" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>111</v>
       </c>
@@ -3699,7 +3721,7 @@
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
     </row>
-    <row r="38" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>113</v>
       </c>
@@ -3729,7 +3751,7 @@
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
     </row>
-    <row r="39" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>117</v>
       </c>
@@ -3758,7 +3780,7 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
     </row>
-    <row r="40" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>120</v>
       </c>
@@ -3787,7 +3809,7 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
     </row>
-    <row r="41" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>143</v>
       </c>
@@ -3817,7 +3839,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
     </row>
-    <row r="42" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>183</v>
       </c>
@@ -3844,7 +3866,7 @@
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
     </row>
-    <row r="43" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>126</v>
       </c>
@@ -3872,7 +3894,7 @@
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
     </row>
-    <row r="44" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>128</v>
       </c>
@@ -3900,7 +3922,7 @@
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
     </row>
-    <row r="45" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>192</v>
       </c>
@@ -3928,7 +3950,7 @@
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
     </row>
-    <row r="46" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>131</v>
       </c>
@@ -3958,7 +3980,7 @@
       <c r="Q46" s="3"/>
       <c r="R46" s="3"/>
     </row>
-    <row r="47" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>134</v>
       </c>
@@ -3988,7 +4010,7 @@
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
     </row>
-    <row r="48" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>159</v>
       </c>
@@ -4018,7 +4040,7 @@
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
     </row>
-    <row r="49" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>167</v>
       </c>
@@ -4048,7 +4070,7 @@
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
     </row>
-    <row r="50" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>158</v>
       </c>
@@ -4075,7 +4097,7 @@
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
     </row>
-    <row r="51" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>140</v>
       </c>
@@ -4105,7 +4127,7 @@
       <c r="Q51" s="3"/>
       <c r="R51" s="3"/>
     </row>
-    <row r="52" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>189</v>
       </c>
@@ -4134,7 +4156,7 @@
       <c r="Q52" s="3"/>
       <c r="R52" s="3"/>
     </row>
-    <row r="53" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>144</v>
       </c>
@@ -4162,7 +4184,7 @@
       <c r="Q53" s="3"/>
       <c r="R53" s="3"/>
     </row>
-    <row r="54" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>148</v>
       </c>
@@ -4190,7 +4212,7 @@
       <c r="Q54" s="3"/>
       <c r="R54" s="3"/>
     </row>
-    <row r="55" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>150</v>
       </c>
@@ -4218,7 +4240,7 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
     </row>
-    <row r="56" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>149</v>
       </c>
@@ -4246,7 +4268,7 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
     </row>
-    <row r="57" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>152</v>
       </c>
@@ -4274,7 +4296,7 @@
       <c r="Q57" s="3"/>
       <c r="R57" s="3"/>
     </row>
-    <row r="58" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>161</v>
       </c>
@@ -4302,7 +4324,7 @@
       <c r="Q58" s="3"/>
       <c r="R58" s="3"/>
     </row>
-    <row r="59" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>156</v>
       </c>
@@ -4330,7 +4352,7 @@
       <c r="Q59" s="3"/>
       <c r="R59" s="3"/>
     </row>
-    <row r="60" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>160</v>
       </c>
@@ -4358,7 +4380,7 @@
       <c r="Q60" s="3"/>
       <c r="R60" s="3"/>
     </row>
-    <row r="61" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
         <v>163</v>
       </c>
@@ -4386,7 +4408,7 @@
       <c r="Q61" s="3"/>
       <c r="R61" s="3"/>
     </row>
-    <row r="62" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
         <v>165</v>
       </c>
@@ -4412,7 +4434,7 @@
       <c r="Q62" s="3"/>
       <c r="R62" s="3"/>
     </row>
-    <row r="63" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
         <v>166</v>
       </c>
@@ -4438,7 +4460,7 @@
       <c r="Q63" s="3"/>
       <c r="R63" s="3"/>
     </row>
-    <row r="64" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>168</v>
       </c>
@@ -4465,7 +4487,7 @@
       <c r="Q64" s="3"/>
       <c r="R64" s="3"/>
     </row>
-    <row r="65" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
         <v>184</v>
       </c>
@@ -4493,7 +4515,7 @@
       <c r="Q65" s="3"/>
       <c r="R65" s="3"/>
     </row>
-    <row r="66" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
         <v>185</v>
       </c>
@@ -4521,7 +4543,7 @@
       <c r="Q66" s="3"/>
       <c r="R66" s="3"/>
     </row>
-    <row r="67" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>169</v>
       </c>
@@ -4547,7 +4569,7 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
     </row>
-    <row r="68" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>170</v>
       </c>
@@ -4573,7 +4595,7 @@
       <c r="Q68" s="3"/>
       <c r="R68" s="3"/>
     </row>
-    <row r="69" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
         <v>171</v>
       </c>
@@ -4599,7 +4621,7 @@
       <c r="Q69" s="3"/>
       <c r="R69" s="3"/>
     </row>
-    <row r="70" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
         <v>172</v>
       </c>
@@ -4625,7 +4647,7 @@
       <c r="Q70" s="3"/>
       <c r="R70" s="3"/>
     </row>
-    <row r="71" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
         <v>173</v>
       </c>
@@ -4651,7 +4673,7 @@
       <c r="Q71" s="3"/>
       <c r="R71" s="3"/>
     </row>
-    <row r="72" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>174</v>
       </c>
@@ -4677,7 +4699,7 @@
       <c r="Q72" s="3"/>
       <c r="R72" s="3"/>
     </row>
-    <row r="73" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
         <v>175</v>
       </c>
@@ -4703,7 +4725,7 @@
       <c r="Q73" s="3"/>
       <c r="R73" s="3"/>
     </row>
-    <row r="74" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>176</v>
       </c>
@@ -4729,7 +4751,7 @@
       <c r="Q74" s="3"/>
       <c r="R74" s="3"/>
     </row>
-    <row r="75" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>177</v>
       </c>
@@ -4757,7 +4779,7 @@
       <c r="Q75" s="3"/>
       <c r="R75" s="3"/>
     </row>
-    <row r="76" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
         <v>179</v>
       </c>
@@ -4785,7 +4807,7 @@
       <c r="Q76" s="3"/>
       <c r="R76" s="3"/>
     </row>
-    <row r="77" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
         <v>195</v>
       </c>
@@ -4811,11 +4833,19 @@
       <c r="Q77" s="3"/>
       <c r="R77" s="3"/>
     </row>
-    <row r="78" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
+    <row r="78" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B78" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
@@ -4831,11 +4861,19 @@
       <c r="Q78" s="3"/>
       <c r="R78" s="3"/>
     </row>
-    <row r="79" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
+    <row r="79" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B79" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C79" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
@@ -4851,11 +4889,19 @@
       <c r="Q79" s="3"/>
       <c r="R79" s="3"/>
     </row>
-    <row r="80" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
+    <row r="80" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B80" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="C80" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
@@ -4871,7 +4917,7 @@
       <c r="Q80" s="3"/>
       <c r="R80" s="3"/>
     </row>
-    <row r="81" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -4891,7 +4937,7 @@
       <c r="Q81" s="3"/>
       <c r="R81" s="3"/>
     </row>
-    <row r="82" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -4911,7 +4957,7 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
     </row>
-    <row r="83" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -4931,7 +4977,7 @@
       <c r="Q83" s="3"/>
       <c r="R83" s="3"/>
     </row>
-    <row r="84" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -4951,7 +4997,7 @@
       <c r="Q84" s="3"/>
       <c r="R84" s="3"/>
     </row>
-    <row r="85" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -4971,7 +5017,7 @@
       <c r="Q85" s="3"/>
       <c r="R85" s="3"/>
     </row>
-    <row r="86" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -4991,7 +5037,7 @@
       <c r="Q86" s="3"/>
       <c r="R86" s="3"/>
     </row>
-    <row r="87" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -5011,7 +5057,7 @@
       <c r="Q87" s="3"/>
       <c r="R87" s="3"/>
     </row>
-    <row r="88" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -5031,7 +5077,7 @@
       <c r="Q88" s="3"/>
       <c r="R88" s="3"/>
     </row>
-    <row r="89" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -5051,7 +5097,7 @@
       <c r="Q89" s="3"/>
       <c r="R89" s="3"/>
     </row>
-    <row r="90" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -5071,7 +5117,7 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
     </row>
-    <row r="91" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -5091,7 +5137,7 @@
       <c r="Q91" s="3"/>
       <c r="R91" s="3"/>
     </row>
-    <row r="92" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -5111,7 +5157,7 @@
       <c r="Q92" s="3"/>
       <c r="R92" s="3"/>
     </row>
-    <row r="93" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -5131,7 +5177,7 @@
       <c r="Q93" s="3"/>
       <c r="R93" s="3"/>
     </row>
-    <row r="94" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -5151,7 +5197,7 @@
       <c r="Q94" s="3"/>
       <c r="R94" s="3"/>
     </row>
-    <row r="95" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -5171,7 +5217,7 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
     </row>
-    <row r="96" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -5191,7 +5237,7 @@
       <c r="Q96" s="3"/>
       <c r="R96" s="3"/>
     </row>
-    <row r="97" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -5211,7 +5257,7 @@
       <c r="Q97" s="3"/>
       <c r="R97" s="3"/>
     </row>
-    <row r="98" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -5231,7 +5277,7 @@
       <c r="Q98" s="3"/>
       <c r="R98" s="3"/>
     </row>
-    <row r="99" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -5251,7 +5297,7 @@
       <c r="Q99" s="3"/>
       <c r="R99" s="3"/>
     </row>
-    <row r="100" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -5271,7 +5317,7 @@
       <c r="Q100" s="3"/>
       <c r="R100" s="3"/>
     </row>
-    <row r="101" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -5291,7 +5337,7 @@
       <c r="Q101" s="3"/>
       <c r="R101" s="3"/>
     </row>
-    <row r="102" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -5311,7 +5357,7 @@
       <c r="Q102" s="3"/>
       <c r="R102" s="3"/>
     </row>
-    <row r="103" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -5331,7 +5377,7 @@
       <c r="Q103" s="3"/>
       <c r="R103" s="3"/>
     </row>
-    <row r="104" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -5351,7 +5397,7 @@
       <c r="Q104" s="3"/>
       <c r="R104" s="3"/>
     </row>
-    <row r="105" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -5371,7 +5417,7 @@
       <c r="Q105" s="3"/>
       <c r="R105" s="3"/>
     </row>
-    <row r="106" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -5391,7 +5437,7 @@
       <c r="Q106" s="3"/>
       <c r="R106" s="3"/>
     </row>
-    <row r="107" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -5411,7 +5457,7 @@
       <c r="Q107" s="3"/>
       <c r="R107" s="3"/>
     </row>
-    <row r="108" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -5431,7 +5477,7 @@
       <c r="Q108" s="3"/>
       <c r="R108" s="3"/>
     </row>
-    <row r="109" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -5451,7 +5497,7 @@
       <c r="Q109" s="3"/>
       <c r="R109" s="3"/>
     </row>
-    <row r="110" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -5471,7 +5517,7 @@
       <c r="Q110" s="3"/>
       <c r="R110" s="3"/>
     </row>
-    <row r="111" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -5491,7 +5537,7 @@
       <c r="Q111" s="3"/>
       <c r="R111" s="3"/>
     </row>
-    <row r="112" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -5511,7 +5557,7 @@
       <c r="Q112" s="3"/>
       <c r="R112" s="3"/>
     </row>
-    <row r="113" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -5531,7 +5577,7 @@
       <c r="Q113" s="3"/>
       <c r="R113" s="3"/>
     </row>
-    <row r="114" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -5551,7 +5597,7 @@
       <c r="Q114" s="3"/>
       <c r="R114" s="3"/>
     </row>
-    <row r="115" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -5571,7 +5617,7 @@
       <c r="Q115" s="3"/>
       <c r="R115" s="3"/>
     </row>
-    <row r="116" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -5591,7 +5637,7 @@
       <c r="Q116" s="3"/>
       <c r="R116" s="3"/>
     </row>
-    <row r="117" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -5611,7 +5657,7 @@
       <c r="Q117" s="3"/>
       <c r="R117" s="3"/>
     </row>
-    <row r="118" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -5631,7 +5677,7 @@
       <c r="Q118" s="3"/>
       <c r="R118" s="3"/>
     </row>
-    <row r="119" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -5651,7 +5697,7 @@
       <c r="Q119" s="3"/>
       <c r="R119" s="3"/>
     </row>
-    <row r="120" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -5671,7 +5717,7 @@
       <c r="Q120" s="3"/>
       <c r="R120" s="3"/>
     </row>
-    <row r="121" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -5691,7 +5737,7 @@
       <c r="Q121" s="3"/>
       <c r="R121" s="3"/>
     </row>
-    <row r="122" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -5711,7 +5757,7 @@
       <c r="Q122" s="3"/>
       <c r="R122" s="3"/>
     </row>
-    <row r="123" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -5731,7 +5777,7 @@
       <c r="Q123" s="3"/>
       <c r="R123" s="3"/>
     </row>
-    <row r="124" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -5751,7 +5797,7 @@
       <c r="Q124" s="3"/>
       <c r="R124" s="3"/>
     </row>
-    <row r="125" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -5771,7 +5817,7 @@
       <c r="Q125" s="3"/>
       <c r="R125" s="3"/>
     </row>
-    <row r="126" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -5791,7 +5837,7 @@
       <c r="Q126" s="3"/>
       <c r="R126" s="3"/>
     </row>
-    <row r="127" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -5811,7 +5857,7 @@
       <c r="Q127" s="3"/>
       <c r="R127" s="3"/>
     </row>
-    <row r="128" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -5831,7 +5877,7 @@
       <c r="Q128" s="3"/>
       <c r="R128" s="3"/>
     </row>
-    <row r="129" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -5851,7 +5897,7 @@
       <c r="Q129" s="3"/>
       <c r="R129" s="3"/>
     </row>
-    <row r="130" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -5871,7 +5917,7 @@
       <c r="Q130" s="3"/>
       <c r="R130" s="3"/>
     </row>
-    <row r="131" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -5891,7 +5937,7 @@
       <c r="Q131" s="3"/>
       <c r="R131" s="3"/>
     </row>
-    <row r="132" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
